--- a/research/traditional_assets/database/data/denmark/denmark_green_renewable_energy.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_green_renewable_energy.xlsx
@@ -650,10 +650,10 @@
         <v>0.07779613003238815</v>
       </c>
       <c r="X2">
-        <v>0.08672233727328382</v>
+        <v>0.08669602784884385</v>
       </c>
       <c r="Y2">
-        <v>-0.00892620724089567</v>
+        <v>-0.008899897816455699</v>
       </c>
       <c r="Z2">
         <v>0.5015856633514731</v>
@@ -662,10 +662,10 @@
         <v>0.06243395073730177</v>
       </c>
       <c r="AB2">
-        <v>0.06805388134487678</v>
+        <v>0.06803936769238214</v>
       </c>
       <c r="AC2">
-        <v>-0.005619930607575006</v>
+        <v>-0.005605416955080371</v>
       </c>
       <c r="AD2">
         <v>15371.2</v>
@@ -787,10 +787,10 @@
         <v>0.07779613003238815</v>
       </c>
       <c r="X3">
-        <v>0.08672233727328382</v>
+        <v>0.08669602784884385</v>
       </c>
       <c r="Y3">
-        <v>-0.00892620724089567</v>
+        <v>-0.008899897816455699</v>
       </c>
       <c r="Z3">
         <v>0.5015856633514731</v>
@@ -799,10 +799,10 @@
         <v>0.06243395073730177</v>
       </c>
       <c r="AB3">
-        <v>0.06805388134487678</v>
+        <v>0.06803936769238214</v>
       </c>
       <c r="AC3">
-        <v>-0.005619930607575006</v>
+        <v>-0.005605416955080371</v>
       </c>
       <c r="AD3">
         <v>15371.2</v>
@@ -1139,49 +1139,49 @@
         <v>3.31541330018645</v>
       </c>
       <c r="F2">
-        <v>3.00616199433422</v>
+        <v>3.06467157155334</v>
       </c>
       <c r="G2">
         <v>4.23169254487391</v>
       </c>
       <c r="H2">
-        <v>3.49221368791983</v>
+        <v>3.5865978416474</v>
       </c>
       <c r="I2">
         <v>0.448347776374471</v>
       </c>
       <c r="J2">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="K2">
         <v>18912.9</v>
       </c>
       <c r="L2">
-        <v>20857.3293283489</v>
+        <v>21726.8539014755</v>
       </c>
       <c r="M2">
         <v>32687.2</v>
       </c>
       <c r="N2">
-        <v>31945.5463283489</v>
+        <v>33157.9119014755</v>
       </c>
       <c r="O2">
         <v>15371.2</v>
       </c>
       <c r="P2">
-        <v>12685.117</v>
+        <v>13027.958</v>
       </c>
       <c r="Q2">
-        <v>0.0680538813448768</v>
+        <v>0.0680393676923821</v>
       </c>
       <c r="R2">
-        <v>0.06857053154200519</v>
+        <v>0.0677236561637069</v>
       </c>
       <c r="S2">
         <v>0.045084</v>
       </c>
       <c r="T2">
-        <v>0.045162</v>
+        <v>0.043134</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.08672233727328379</v>
+        <v>0.08669602784884391</v>
       </c>
       <c r="X2">
-        <v>0.0823183992730241</v>
+        <v>0.08279473574791441</v>
       </c>
       <c r="Y2">
         <v>0.944481012675378</v>
       </c>
       <c r="Z2">
-        <v>0.842838826539534</v>
+        <v>0.854381887942595</v>
       </c>
       <c r="AA2">
         <v>15371.2</v>
@@ -1236,7 +1236,7 @@
         <v>18912.9</v>
       </c>
       <c r="AK2">
-        <v>0.043327855959079</v>
+        <v>0.0433</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.07084527709776309</v>
+        <v>0.07082917521137812</v>
       </c>
       <c r="C2">
-        <v>30640.98154307166</v>
+        <v>30640.71201119123</v>
       </c>
       <c r="D2">
-        <v>29044.08154307166</v>
+        <v>29043.81201119123</v>
       </c>
       <c r="E2">
         <v>-15371.2</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.07084527709776309</v>
+        <v>0.07082917521137812</v>
       </c>
       <c r="T2">
         <v>0.5780409979533053</v>
       </c>
       <c r="U2">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V2">
         <v>0.22</v>
       </c>
       <c r="W2">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.07073543748814802</v>
+        <v>0.0707084510259131</v>
       </c>
       <c r="C3">
-        <v>30426.07856620984</v>
+        <v>30438.63811646817</v>
       </c>
       <c r="D3">
-        <v>29172.01956620983</v>
+        <v>29184.57911646817</v>
       </c>
       <c r="E3">
         <v>-15028.359</v>
@@ -1539,37 +1539,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M3">
-        <v>17.72487970000001</v>
+        <v>17.2449023</v>
       </c>
       <c r="N3">
-        <v>2190.205732544898</v>
+        <v>2190.685709944898</v>
       </c>
       <c r="O3">
-        <v>481.8452611598776</v>
+        <v>481.9508561878777</v>
       </c>
       <c r="P3">
-        <v>1708.36047138502</v>
+        <v>1708.734853757021</v>
       </c>
       <c r="Q3">
-        <v>3206.96047138502</v>
+        <v>3207.334853757021</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.07104260352338183</v>
+        <v>0.07102637477364959</v>
       </c>
       <c r="T3">
         <v>0.5825952603614223</v>
       </c>
       <c r="U3">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V3">
         <v>0.22</v>
       </c>
       <c r="W3">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>124.5667473977213</v>
+        <v>128.0338139256897</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.07062559787853294</v>
+        <v>0.07058772684044805</v>
       </c>
       <c r="C4">
-        <v>30212.30770004966</v>
+        <v>30237.93538371044</v>
       </c>
       <c r="D4">
-        <v>29301.08970004966</v>
+        <v>29326.71738371044</v>
       </c>
       <c r="E4">
         <v>-14685.518</v>
@@ -1621,37 +1621,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M4">
-        <v>35.44975940000001</v>
+        <v>34.48980460000001</v>
       </c>
       <c r="N4">
-        <v>2172.480852844898</v>
+        <v>2173.440807644899</v>
       </c>
       <c r="O4">
-        <v>477.9457876258776</v>
+        <v>478.1569776818777</v>
       </c>
       <c r="P4">
-        <v>1694.535065219021</v>
+        <v>1695.283829963021</v>
       </c>
       <c r="Q4">
-        <v>3193.135065219021</v>
+        <v>3193.883829963021</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.07124395701891116</v>
+        <v>0.07122759881678373</v>
       </c>
       <c r="T4">
         <v>0.5872424669003171</v>
       </c>
       <c r="U4">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V4">
         <v>0.22</v>
       </c>
       <c r="W4">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>62.28337369886064</v>
+        <v>64.01690696284484</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.07051575826891786</v>
+        <v>0.07046700265498303</v>
       </c>
       <c r="C5">
-        <v>29999.684038273</v>
+        <v>30038.62394496405</v>
       </c>
       <c r="D5">
-        <v>29431.307038273</v>
+        <v>29470.24694496405</v>
       </c>
       <c r="E5">
         <v>-14342.677</v>
@@ -1703,37 +1703,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M5">
-        <v>53.17463910000001</v>
+        <v>51.73470690000001</v>
       </c>
       <c r="N5">
-        <v>2154.755973144898</v>
+        <v>2156.195905344898</v>
       </c>
       <c r="O5">
-        <v>474.0463140918776</v>
+        <v>474.3630991758776</v>
       </c>
       <c r="P5">
-        <v>1680.709659053021</v>
+        <v>1681.832806169021</v>
       </c>
       <c r="Q5">
-        <v>3179.30965905302</v>
+        <v>3180.43280616902</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.07144946213290501</v>
+        <v>0.07143297180926085</v>
       </c>
       <c r="T5">
         <v>0.5919854921307356</v>
       </c>
       <c r="U5">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V5">
         <v>0.22</v>
       </c>
       <c r="W5">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>41.52224913257376</v>
+        <v>42.67793797522989</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.07040591865930276</v>
+        <v>0.07034627846951799</v>
       </c>
       <c r="C6">
-        <v>29788.22294407155</v>
+        <v>29840.72432833107</v>
       </c>
       <c r="D6">
-        <v>29562.68694407155</v>
+        <v>29615.18832833107</v>
       </c>
       <c r="E6">
         <v>-13999.836</v>
@@ -1785,37 +1785,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M6">
-        <v>70.89951880000002</v>
+        <v>68.97960920000001</v>
       </c>
       <c r="N6">
-        <v>2137.031093444898</v>
+        <v>2138.951003044898</v>
       </c>
       <c r="O6">
-        <v>470.1468405578777</v>
+        <v>470.5692206698776</v>
       </c>
       <c r="P6">
-        <v>1666.884252887021</v>
+        <v>1668.381782375021</v>
       </c>
       <c r="Q6">
-        <v>3165.484252887021</v>
+        <v>3166.98178237502</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.07165924860344039</v>
+        <v>0.07164262340574791</v>
       </c>
       <c r="T6">
         <v>0.5968273303867877</v>
       </c>
       <c r="U6">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V6">
         <v>0.22</v>
       </c>
       <c r="W6">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>31.14168684943032</v>
+        <v>32.00845348142242</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.0702960790496877</v>
+        <v>0.07022555428405296</v>
       </c>
       <c r="C7">
-        <v>29577.94005618911</v>
+        <v>29644.25746775708</v>
       </c>
       <c r="D7">
-        <v>29695.24505618911</v>
+        <v>29761.56246775708</v>
       </c>
       <c r="E7">
         <v>-13656.995</v>
@@ -1867,37 +1867,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M7">
-        <v>88.62439850000004</v>
+        <v>86.22451150000002</v>
       </c>
       <c r="N7">
-        <v>2119.306213744898</v>
+        <v>2121.706100744898</v>
       </c>
       <c r="O7">
-        <v>466.2473670238776</v>
+        <v>466.7753421638776</v>
       </c>
       <c r="P7">
-        <v>1653.058846721021</v>
+        <v>1654.930758581021</v>
       </c>
       <c r="Q7">
-        <v>3151.65884672102</v>
+        <v>3153.530758581021</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.07187345163125021</v>
+        <v>0.07185668872005575</v>
       </c>
       <c r="T7">
         <v>0.6017711020798094</v>
       </c>
       <c r="U7">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V7">
         <v>0.22</v>
       </c>
       <c r="W7">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>24.91334947954425</v>
+        <v>25.60676278513793</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.07018623944007261</v>
+        <v>0.07010483009858792</v>
       </c>
       <c r="C8">
-        <v>29368.85129512745</v>
+        <v>29449.24471311048</v>
       </c>
       <c r="D8">
-        <v>29828.99729512744</v>
+        <v>29909.39071311048</v>
       </c>
       <c r="E8">
         <v>-13314.154</v>
@@ -1949,37 +1949,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M8">
-        <v>106.3492782</v>
+        <v>103.4694138</v>
       </c>
       <c r="N8">
-        <v>2101.581334044899</v>
+        <v>2104.461198444898</v>
       </c>
       <c r="O8">
-        <v>462.3478934898777</v>
+        <v>462.9814636578777</v>
       </c>
       <c r="P8">
-        <v>1639.233440555021</v>
+        <v>1641.479734787021</v>
       </c>
       <c r="Q8">
-        <v>3137.833440555021</v>
+        <v>3140.079734787021</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.07209221217029002</v>
+        <v>0.07207530861551907</v>
       </c>
       <c r="T8">
         <v>0.6068200604045976</v>
       </c>
       <c r="U8">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V8">
         <v>0.22</v>
       </c>
       <c r="W8">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>20.76112456628688</v>
+        <v>21.33896898761494</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.07007639983045755</v>
+        <v>0.0699841059131229</v>
       </c>
       <c r="C9">
-        <v>29160.97286952017</v>
+        <v>29255.70784056371</v>
       </c>
       <c r="D9">
-        <v>29963.95986952017</v>
+        <v>30058.69484056371</v>
       </c>
       <c r="E9">
         <v>-12971.313</v>
@@ -2031,37 +2031,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M9">
-        <v>124.0741579000001</v>
+        <v>120.7143161</v>
       </c>
       <c r="N9">
-        <v>2083.856454344898</v>
+        <v>2087.216296144898</v>
       </c>
       <c r="O9">
-        <v>458.4484199558776</v>
+        <v>459.1875851518777</v>
       </c>
       <c r="P9">
-        <v>1625.408034389021</v>
+        <v>1628.028710993021</v>
       </c>
       <c r="Q9">
-        <v>3124.00803438902</v>
+        <v>3126.628710993021</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.07231567723705112</v>
+        <v>0.07229863001411065</v>
       </c>
       <c r="T9">
         <v>0.6119775984783059</v>
       </c>
       <c r="U9">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V9">
         <v>0.22</v>
       </c>
       <c r="W9">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>17.79524962824589</v>
+        <v>18.29054484652709</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.06996656022084247</v>
+        <v>0.06986338172765787</v>
       </c>
       <c r="C10">
-        <v>28954.32128268091</v>
+        <v>29063.66906328697</v>
       </c>
       <c r="D10">
-        <v>30100.1492826809</v>
+        <v>30209.49706328697</v>
       </c>
       <c r="E10">
         <v>-12628.472</v>
@@ -2113,37 +2113,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M10">
-        <v>141.7990376</v>
+        <v>137.9592184</v>
       </c>
       <c r="N10">
-        <v>2066.131574644898</v>
+        <v>2069.971393844899</v>
       </c>
       <c r="O10">
-        <v>454.5489464218776</v>
+        <v>455.3937066458777</v>
       </c>
       <c r="P10">
-        <v>1611.58262822302</v>
+        <v>1614.577687199021</v>
       </c>
       <c r="Q10">
-        <v>3110.18262822302</v>
+        <v>3113.177687199021</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.07254400024004615</v>
+        <v>0.07252680622571507</v>
       </c>
       <c r="T10">
         <v>0.6172472569449208</v>
       </c>
       <c r="U10">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V10">
         <v>0.22</v>
       </c>
       <c r="W10">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>15.57084342471516</v>
+        <v>16.00422674071121</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.06985672061122739</v>
+        <v>0.06974265754219285</v>
       </c>
       <c r="C11">
-        <v>28748.91333933046</v>
+        <v>28873.1510424653</v>
       </c>
       <c r="D11">
-        <v>30237.58233933046</v>
+        <v>30361.8200424653</v>
       </c>
       <c r="E11">
         <v>-12285.631</v>
@@ -2195,37 +2195,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M11">
-        <v>159.5239173000001</v>
+        <v>155.2041207</v>
       </c>
       <c r="N11">
-        <v>2048.406694944898</v>
+        <v>2052.726491544898</v>
       </c>
       <c r="O11">
-        <v>450.6494728878777</v>
+        <v>451.5998281398776</v>
       </c>
       <c r="P11">
-        <v>1597.757222057021</v>
+        <v>1601.126663405021</v>
       </c>
       <c r="Q11">
-        <v>3096.35722205702</v>
+        <v>3099.72666340502</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.07277734133101911</v>
+        <v>0.07275999729911301</v>
       </c>
       <c r="T11">
         <v>0.6226327320811318</v>
       </c>
       <c r="U11">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V11">
         <v>0.22</v>
       </c>
       <c r="W11">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>13.84074971085792</v>
+        <v>14.22597932507663</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.0697468810016123</v>
+        <v>0.06962193335672781</v>
       </c>
       <c r="C12">
-        <v>28544.7661525094</v>
+        <v>28684.1768986509</v>
       </c>
       <c r="D12">
-        <v>30376.2761525094</v>
+        <v>30515.6868986509</v>
       </c>
       <c r="E12">
         <v>-11942.79</v>
@@ -2277,37 +2277,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M12">
-        <v>177.2487970000001</v>
+        <v>172.449023</v>
       </c>
       <c r="N12">
-        <v>2030.681815244898</v>
+        <v>2035.481589244898</v>
       </c>
       <c r="O12">
-        <v>446.7499993538776</v>
+        <v>447.8059496338776</v>
       </c>
       <c r="P12">
-        <v>1583.931815891021</v>
+        <v>1587.675639611021</v>
       </c>
       <c r="Q12">
-        <v>3082.53181589102</v>
+        <v>3086.275639611021</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.07301586777956923</v>
+        <v>0.07299837039636423</v>
       </c>
       <c r="T12">
         <v>0.6281378844425918</v>
       </c>
       <c r="U12">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V12">
         <v>0.22</v>
       </c>
       <c r="W12">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>12.45667473977213</v>
+        <v>12.80338139256897</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.06963704139199722</v>
+        <v>0.06950120917126276</v>
       </c>
       <c r="C13">
-        <v>28341.89715068161</v>
+        <v>28496.77022346218</v>
       </c>
       <c r="D13">
-        <v>30516.24815068161</v>
+        <v>30671.12122346217</v>
       </c>
       <c r="E13">
         <v>-11599.949</v>
@@ -2359,37 +2359,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M13">
-        <v>194.9736767000001</v>
+        <v>189.6939253</v>
       </c>
       <c r="N13">
-        <v>2012.956935544898</v>
+        <v>2018.236686944898</v>
       </c>
       <c r="O13">
-        <v>442.8505258198776</v>
+        <v>444.0120711278776</v>
       </c>
       <c r="P13">
-        <v>1570.106409725021</v>
+        <v>1574.224615817021</v>
       </c>
       <c r="Q13">
-        <v>3068.70640972502</v>
+        <v>3072.82461581702</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.07325975437303059</v>
+        <v>0.07324210019243008</v>
       </c>
       <c r="T13">
         <v>0.6337667480930734</v>
       </c>
       <c r="U13">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V13">
         <v>0.22</v>
       </c>
       <c r="W13">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.32424976342921</v>
+        <v>11.63943762960815</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.06952720178238214</v>
+        <v>0.06938048498579776</v>
       </c>
       <c r="C14">
-        <v>28140.32408503519</v>
+        <v>28310.9550916422</v>
       </c>
       <c r="D14">
-        <v>30657.51608503519</v>
+        <v>30828.1470916422</v>
       </c>
       <c r="E14">
         <v>-11257.108</v>
@@ -2441,37 +2441,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M14">
-        <v>212.6985564000001</v>
+        <v>206.9388276000001</v>
       </c>
       <c r="N14">
-        <v>1995.232055844898</v>
+        <v>2000.991784644898</v>
       </c>
       <c r="O14">
-        <v>438.9510522858776</v>
+        <v>440.2181926218777</v>
       </c>
       <c r="P14">
-        <v>1556.281003559021</v>
+        <v>1560.773592023021</v>
       </c>
       <c r="Q14">
-        <v>3054.88100355902</v>
+        <v>3059.373592023021</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.07350918384361607</v>
+        <v>0.07349136930204289</v>
       </c>
       <c r="T14">
         <v>0.6395235404628842</v>
       </c>
       <c r="U14">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V14">
         <v>0.22</v>
       </c>
       <c r="W14">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>10.38056228314344</v>
+        <v>10.66948449380747</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.06941736217276707</v>
+        <v>0.06925976080033269</v>
       </c>
       <c r="C15">
-        <v>27940.06503698709</v>
+        <v>28126.75607348981</v>
       </c>
       <c r="D15">
-        <v>30800.09803698708</v>
+        <v>30986.78907348981</v>
       </c>
       <c r="E15">
         <v>-10914.267</v>
@@ -2523,37 +2523,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M15">
-        <v>230.4234361000001</v>
+        <v>224.1837299000001</v>
       </c>
       <c r="N15">
-        <v>1977.507176144898</v>
+        <v>1983.746882344898</v>
       </c>
       <c r="O15">
-        <v>435.0515787518776</v>
+        <v>436.4243141158776</v>
       </c>
       <c r="P15">
-        <v>1542.455597393021</v>
+        <v>1547.322568229021</v>
       </c>
       <c r="Q15">
-        <v>3041.05559739302</v>
+        <v>3045.922568229021</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.07376434732501962</v>
+        <v>0.0737463687360146</v>
       </c>
       <c r="T15">
         <v>0.6454126728871733</v>
       </c>
       <c r="U15">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V15">
         <v>0.22</v>
       </c>
       <c r="W15">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>9.582057492132405</v>
+        <v>9.848754917360743</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.06930752256315199</v>
+        <v>0.06913903661486769</v>
       </c>
       <c r="C16">
-        <v>27741.13842589814</v>
+        <v>27944.19824767575</v>
       </c>
       <c r="D16">
-        <v>30944.01242589814</v>
+        <v>31147.07224767575</v>
       </c>
       <c r="E16">
         <v>-10571.426</v>
@@ -2605,37 +2605,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M16">
-        <v>248.1483158000001</v>
+        <v>241.4286322000001</v>
       </c>
       <c r="N16">
-        <v>1959.782296444898</v>
+        <v>1966.501980044898</v>
       </c>
       <c r="O16">
-        <v>431.1521052178776</v>
+        <v>432.6304356098776</v>
       </c>
       <c r="P16">
-        <v>1528.630191227021</v>
+        <v>1533.871544435021</v>
       </c>
       <c r="Q16">
-        <v>3027.23019122702</v>
+        <v>3032.47154443502</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.07402544484087441</v>
+        <v>0.07400729838938103</v>
       </c>
       <c r="T16">
         <v>0.6514387618794693</v>
       </c>
       <c r="U16">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V16">
         <v>0.22</v>
       </c>
       <c r="W16">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.897624814122947</v>
+        <v>9.145272423263547</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.06932638295353691</v>
+        <v>0.06919381242940265</v>
       </c>
       <c r="C17">
-        <v>27373.49054608238</v>
+        <v>27528.42743950984</v>
       </c>
       <c r="D17">
-        <v>30919.20554608238</v>
+        <v>31074.14243950984</v>
       </c>
       <c r="E17">
         <v>-10228.585</v>
@@ -2687,37 +2687,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M17">
-        <v>271.5300720000001</v>
+        <v>266.387457</v>
       </c>
       <c r="N17">
-        <v>1936.400540244898</v>
+        <v>1941.543155244898</v>
       </c>
       <c r="O17">
-        <v>426.0081188538776</v>
+        <v>427.1394941538776</v>
       </c>
       <c r="P17">
-        <v>1510.392421391021</v>
+        <v>1514.403661091021</v>
       </c>
       <c r="Q17">
-        <v>3008.992421391021</v>
+        <v>3013.003661091021</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.07429268582769048</v>
+        <v>0.07427436756400312</v>
       </c>
       <c r="T17">
         <v>0.6576066412009957</v>
       </c>
       <c r="U17">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V17">
         <v>0.22</v>
       </c>
       <c r="W17">
-        <v>0.04118400000000001</v>
+        <v>0.040404</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.131440455129027</v>
+        <v>8.288418070092909</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.06922512334392182</v>
+        <v>0.06908478824393763</v>
       </c>
       <c r="C18">
-        <v>27164.30377010666</v>
+        <v>27331.08198935121</v>
       </c>
       <c r="D18">
-        <v>31052.85977010666</v>
+        <v>31219.63798935121</v>
       </c>
       <c r="E18">
         <v>-9885.743999999999</v>
@@ -2769,37 +2769,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M18">
-        <v>289.6320768000001</v>
+        <v>284.1466208000001</v>
       </c>
       <c r="N18">
-        <v>1918.298535444898</v>
+        <v>1923.783991444898</v>
       </c>
       <c r="O18">
-        <v>422.0256777978776</v>
+        <v>423.2324781178776</v>
       </c>
       <c r="P18">
-        <v>1496.272857647021</v>
+        <v>1500.551513327021</v>
       </c>
       <c r="Q18">
-        <v>2994.872857647021</v>
+        <v>2999.15151332702</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.07456628969514503</v>
+        <v>0.07454779552849716</v>
       </c>
       <c r="T18">
         <v>0.6639213747920821</v>
       </c>
       <c r="U18">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V18">
         <v>0.22</v>
       </c>
       <c r="W18">
-        <v>0.04118400000000001</v>
+        <v>0.040404</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.623225426683463</v>
+        <v>7.770391940712101</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.06912386373430675</v>
+        <v>0.06897576405847257</v>
       </c>
       <c r="C19">
-        <v>26956.27750293017</v>
+        <v>27135.10542901825</v>
       </c>
       <c r="D19">
-        <v>31187.67450293017</v>
+        <v>31366.50242901825</v>
       </c>
       <c r="E19">
         <v>-9542.902999999998</v>
@@ -2851,37 +2851,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M19">
-        <v>307.7340816000001</v>
+        <v>301.9057846000001</v>
       </c>
       <c r="N19">
-        <v>1900.196530644898</v>
+        <v>1906.024827644898</v>
       </c>
       <c r="O19">
-        <v>418.0432367418776</v>
+        <v>419.3254620818776</v>
       </c>
       <c r="P19">
-        <v>1482.153293903021</v>
+        <v>1486.699365563021</v>
       </c>
       <c r="Q19">
-        <v>2980.753293903021</v>
+        <v>2985.299365563021</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.07484648642687561</v>
+        <v>0.07482781211864166</v>
       </c>
       <c r="T19">
         <v>0.6703882706383756</v>
       </c>
       <c r="U19">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V19">
         <v>0.22</v>
       </c>
       <c r="W19">
-        <v>0.04118400000000001</v>
+        <v>0.040404</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.174800401584435</v>
+        <v>7.313310061846684</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.06902260412469167</v>
+        <v>0.06886673987300755</v>
       </c>
       <c r="C20">
-        <v>26749.42692536565</v>
+        <v>26940.51716854872</v>
       </c>
       <c r="D20">
-        <v>31323.66492536565</v>
+        <v>31514.75516854872</v>
       </c>
       <c r="E20">
         <v>-9200.062</v>
@@ -2933,37 +2933,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M20">
-        <v>325.8360864000001</v>
+        <v>319.6649484000001</v>
       </c>
       <c r="N20">
-        <v>1882.094525844898</v>
+        <v>1888.265663844898</v>
       </c>
       <c r="O20">
-        <v>414.0607956858776</v>
+        <v>415.4184460458777</v>
       </c>
       <c r="P20">
-        <v>1468.033730159021</v>
+        <v>1472.847217799021</v>
       </c>
       <c r="Q20">
-        <v>2966.633730159021</v>
+        <v>2971.447217799021</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.07513351722523375</v>
+        <v>0.07511465838171652</v>
       </c>
       <c r="T20">
         <v>0.6770128956516517</v>
       </c>
       <c r="U20">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V20">
         <v>0.22</v>
       </c>
       <c r="W20">
-        <v>0.04118400000000001</v>
+        <v>0.040404</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.77620037927419</v>
+        <v>6.907015058410758</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.06924738451507662</v>
+        <v>0.06900965568754253</v>
       </c>
       <c r="C21">
-        <v>26106.29888799124</v>
+        <v>26403.62085961104</v>
       </c>
       <c r="D21">
-        <v>31023.37788799125</v>
+        <v>31320.69985961104</v>
       </c>
       <c r="E21">
         <v>-8857.221</v>
@@ -3015,37 +3015,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M21">
-        <v>358.2688450000001</v>
+        <v>348.4978765000001</v>
       </c>
       <c r="N21">
-        <v>1849.661767244898</v>
+        <v>1859.432735744898</v>
       </c>
       <c r="O21">
-        <v>406.9255887938776</v>
+        <v>409.0752018638776</v>
       </c>
       <c r="P21">
-        <v>1442.736178451021</v>
+        <v>1450.357533881021</v>
       </c>
       <c r="Q21">
-        <v>2941.336178451021</v>
+        <v>2948.95753388102</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.07542763520379828</v>
+        <v>0.07540858726857101</v>
       </c>
       <c r="T21">
         <v>0.6838010916529101</v>
       </c>
       <c r="U21">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V21">
         <v>0.22</v>
       </c>
       <c r="W21">
-        <v>0.04290000000000001</v>
+        <v>0.04173</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.162775923887263</v>
+        <v>6.335564033902795</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.06916328490546153</v>
+        <v>0.0689138915020775</v>
       </c>
       <c r="C22">
-        <v>25875.13113855848</v>
+        <v>26190.5460355049</v>
       </c>
       <c r="D22">
-        <v>31135.05113855848</v>
+        <v>31450.4660355049</v>
       </c>
       <c r="E22">
         <v>-8514.379999999999</v>
@@ -3097,37 +3097,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M22">
-        <v>377.1251000000001</v>
+        <v>366.8398700000001</v>
       </c>
       <c r="N22">
-        <v>1830.805512244898</v>
+        <v>1841.090742244898</v>
       </c>
       <c r="O22">
-        <v>402.7772126938776</v>
+        <v>405.0399632938776</v>
       </c>
       <c r="P22">
-        <v>1428.028299551021</v>
+        <v>1436.050778951021</v>
       </c>
       <c r="Q22">
-        <v>2926.628299551021</v>
+        <v>2934.650778951021</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.0757291061318269</v>
+        <v>0.07570986437759686</v>
       </c>
       <c r="T22">
         <v>0.6907589925541999</v>
       </c>
       <c r="U22">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V22">
         <v>0.22</v>
       </c>
       <c r="W22">
-        <v>0.04290000000000001</v>
+        <v>0.04173</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.854637127692899</v>
+        <v>6.018785832207653</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.06932488529584643</v>
+        <v>0.06881812731661245</v>
       </c>
       <c r="C23">
-        <v>25318.4129461569</v>
+        <v>25978.55096493082</v>
       </c>
       <c r="D23">
-        <v>30921.1739461569</v>
+        <v>31581.31196493081</v>
       </c>
       <c r="E23">
         <v>-8171.539</v>
@@ -3179,45 +3179,45 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M23">
-        <v>406.7808465000001</v>
+        <v>385.1818635000001</v>
       </c>
       <c r="N23">
-        <v>1801.149765744898</v>
+        <v>1822.748748744898</v>
       </c>
       <c r="O23">
-        <v>396.2529484638777</v>
+        <v>401.0047247238776</v>
       </c>
       <c r="P23">
-        <v>1404.896817281021</v>
+        <v>1421.744024021021</v>
       </c>
       <c r="Q23">
-        <v>2903.49681728102</v>
+        <v>2920.344024021021</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.07603820923524865</v>
+        <v>0.07601876875520563</v>
       </c>
       <c r="T23">
         <v>0.6978930428453957</v>
       </c>
       <c r="U23">
-        <v>0.05650000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V23">
         <v>0.22</v>
       </c>
       <c r="W23">
-        <v>0.04407000000000001</v>
+        <v>0.04173</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>5.427813603423675</v>
+        <v>5.732176983054909</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.06925248568623137</v>
+        <v>0.06885964313114742</v>
       </c>
       <c r="C24">
-        <v>25071.02796529672</v>
+        <v>25578.85202125621</v>
       </c>
       <c r="D24">
-        <v>31016.62996529672</v>
+        <v>31524.45402125621</v>
       </c>
       <c r="E24">
         <v>-7828.697999999999</v>
@@ -3261,37 +3261,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M24">
-        <v>426.1513630000001</v>
+        <v>409.5578586000001</v>
       </c>
       <c r="N24">
-        <v>1781.779249244898</v>
+        <v>1798.372753644898</v>
       </c>
       <c r="O24">
-        <v>391.9914348338776</v>
+        <v>395.6420058018776</v>
       </c>
       <c r="P24">
-        <v>1389.78781441102</v>
+        <v>1402.730747843021</v>
       </c>
       <c r="Q24">
-        <v>2888.38781441102</v>
+        <v>2901.330747843021</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.07635523805927097</v>
+        <v>0.07633559375788131</v>
       </c>
       <c r="T24">
         <v>0.7052100175030325</v>
       </c>
       <c r="U24">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V24">
         <v>0.22</v>
       </c>
       <c r="W24">
-        <v>0.04407000000000001</v>
+        <v>0.04235400000000001</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.181094803268053</v>
+        <v>5.391010246494383</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.06918008607661627</v>
+        <v>0.0687701189456824</v>
       </c>
       <c r="C25">
-        <v>24824.23416947315</v>
+        <v>25358.87503755305</v>
       </c>
       <c r="D25">
-        <v>31112.67716947315</v>
+        <v>31647.31803755305</v>
       </c>
       <c r="E25">
         <v>-7485.856999999999</v>
@@ -3343,37 +3343,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M25">
-        <v>445.5218795000002</v>
+        <v>428.1741249000002</v>
       </c>
       <c r="N25">
-        <v>1762.408732744898</v>
+        <v>1779.756487344898</v>
       </c>
       <c r="O25">
-        <v>387.7299212038776</v>
+        <v>391.5464272158776</v>
       </c>
       <c r="P25">
-        <v>1374.678811541021</v>
+        <v>1388.210060129021</v>
       </c>
       <c r="Q25">
-        <v>2873.27881154102</v>
+        <v>2886.810060129021</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.07668050139820295</v>
+        <v>0.07666064798140571</v>
       </c>
       <c r="T25">
         <v>0.712717043450478</v>
       </c>
       <c r="U25">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V25">
         <v>0.22</v>
       </c>
       <c r="W25">
-        <v>0.04407000000000001</v>
+        <v>0.04235400000000001</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.955829811821616</v>
+        <v>5.156618496646801</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.0691076864670012</v>
+        <v>0.06868059476021736</v>
       </c>
       <c r="C26">
-        <v>24578.03706779995</v>
+        <v>25139.85950621574</v>
       </c>
       <c r="D26">
-        <v>31209.32106779995</v>
+        <v>31771.14350621574</v>
       </c>
       <c r="E26">
         <v>-7143.016</v>
@@ -3425,37 +3425,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M26">
-        <v>464.8923960000001</v>
+        <v>446.7903912000001</v>
       </c>
       <c r="N26">
-        <v>1743.038216244898</v>
+        <v>1761.140221044898</v>
       </c>
       <c r="O26">
-        <v>383.4684075738776</v>
+        <v>387.4508486298776</v>
       </c>
       <c r="P26">
-        <v>1359.569808671021</v>
+        <v>1373.689372415021</v>
       </c>
       <c r="Q26">
-        <v>2858.16980867102</v>
+        <v>2872.289372415021</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.07701432429868579</v>
+        <v>0.07699425626344389</v>
       </c>
       <c r="T26">
         <v>0.72042162271233</v>
       </c>
       <c r="U26">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V26">
         <v>0.22</v>
       </c>
       <c r="W26">
-        <v>0.04407000000000001</v>
+        <v>0.04235400000000001</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.749336902995715</v>
+        <v>4.941759392619852</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.06903528685738614</v>
+        <v>0.06859107057475232</v>
       </c>
       <c r="C27">
-        <v>24332.44223805507</v>
+        <v>24921.81675710781</v>
       </c>
       <c r="D27">
-        <v>31306.56723805507</v>
+        <v>31895.94175710781</v>
       </c>
       <c r="E27">
         <v>-6800.174999999999</v>
@@ -3507,37 +3507,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M27">
-        <v>484.2629125000001</v>
+        <v>465.4066575000002</v>
       </c>
       <c r="N27">
-        <v>1723.667699744898</v>
+        <v>1742.523954744898</v>
       </c>
       <c r="O27">
-        <v>379.2068939438776</v>
+        <v>383.3552700438776</v>
       </c>
       <c r="P27">
-        <v>1344.460805801021</v>
+        <v>1359.168684701021</v>
       </c>
       <c r="Q27">
-        <v>2843.060805801021</v>
+        <v>2857.76868470102</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.07735704914318151</v>
+        <v>0.07733676076633643</v>
       </c>
       <c r="T27">
         <v>0.7283316574211647</v>
       </c>
       <c r="U27">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V27">
         <v>0.22</v>
       </c>
       <c r="W27">
-        <v>0.04407000000000001</v>
+        <v>0.04235400000000001</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.559363426875887</v>
+        <v>4.744089016915057</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.06896288724777105</v>
+        <v>0.06850154638928731</v>
       </c>
       <c r="C28">
-        <v>24087.45532775373</v>
+        <v>24704.75829881131</v>
       </c>
       <c r="D28">
-        <v>31404.42132775373</v>
+        <v>32021.72429881131</v>
       </c>
       <c r="E28">
         <v>-6457.333999999999</v>
@@ -3589,37 +3589,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M28">
-        <v>503.6334290000002</v>
+        <v>484.0229238000002</v>
       </c>
       <c r="N28">
-        <v>1704.297183244898</v>
+        <v>1723.907688444898</v>
       </c>
       <c r="O28">
-        <v>374.9453803138776</v>
+        <v>379.2596914578776</v>
       </c>
       <c r="P28">
-        <v>1329.351802931021</v>
+        <v>1344.647996987021</v>
       </c>
       <c r="Q28">
-        <v>2827.95180293102</v>
+        <v>2843.247996987021</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.07770903682131222</v>
+        <v>0.07768852214768554</v>
       </c>
       <c r="T28">
         <v>0.7364554768518599</v>
       </c>
       <c r="U28">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V28">
         <v>0.22</v>
       </c>
       <c r="W28">
-        <v>0.04407000000000001</v>
+        <v>0.04235400000000001</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.384003295072968</v>
+        <v>4.561624054726016</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.06918532763815596</v>
+        <v>0.06841202220382227</v>
       </c>
       <c r="C29">
-        <v>23445.89660833381</v>
+        <v>24488.69582216481</v>
       </c>
       <c r="D29">
-        <v>31105.70360833381</v>
+        <v>32148.50282216481</v>
       </c>
       <c r="E29">
         <v>-6114.492999999999</v>
@@ -3671,45 +3671,45 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M29">
-        <v>535.9633353000002</v>
+        <v>502.6391901000002</v>
       </c>
       <c r="N29">
-        <v>1671.967276944898</v>
+        <v>1705.291422144898</v>
       </c>
       <c r="O29">
-        <v>367.8328009278776</v>
+        <v>375.1641128718776</v>
       </c>
       <c r="P29">
-        <v>1304.134476017021</v>
+        <v>1330.127309273021</v>
       </c>
       <c r="Q29">
-        <v>2802.734476017021</v>
+        <v>2828.727309273021</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.07807066799747392</v>
+        <v>0.07804992082715378</v>
       </c>
       <c r="T29">
         <v>0.7448018666779165</v>
       </c>
       <c r="U29">
-        <v>0.05790000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V29">
         <v>0.22</v>
       </c>
       <c r="W29">
-        <v>0.04516200000000001</v>
+        <v>0.04235400000000001</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y29">
-        <v>4.11955532556911</v>
+        <v>4.39267501566209</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.06912384802854089</v>
+        <v>0.06854089801835724</v>
       </c>
       <c r="C30">
-        <v>23185.04750402367</v>
+        <v>23963.66480996997</v>
       </c>
       <c r="D30">
-        <v>31187.69550402368</v>
+        <v>31966.31280996997</v>
       </c>
       <c r="E30">
         <v>-5771.651999999998</v>
@@ -3753,37 +3753,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M30">
-        <v>555.8138292000002</v>
+        <v>530.8550044000002</v>
       </c>
       <c r="N30">
-        <v>1652.116783044898</v>
+        <v>1677.075607844898</v>
       </c>
       <c r="O30">
-        <v>363.4656922698776</v>
+        <v>368.9566337258776</v>
       </c>
       <c r="P30">
-        <v>1288.651090775021</v>
+        <v>1308.118974119021</v>
       </c>
       <c r="Q30">
-        <v>2787.25109077502</v>
+        <v>2806.71897411902</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.07844234448408458</v>
+        <v>0.07842135835882949</v>
       </c>
       <c r="T30">
         <v>0.753380100665808</v>
       </c>
       <c r="U30">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V30">
         <v>0.22</v>
       </c>
       <c r="W30">
-        <v>0.04516200000000001</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.972428349655927</v>
+        <v>4.15919713282239</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.06906236841892581</v>
+        <v>0.06845917383289218</v>
       </c>
       <c r="C31">
-        <v>22924.63178892379</v>
+        <v>23736.11578380723</v>
       </c>
       <c r="D31">
-        <v>31270.1207889238</v>
+        <v>32081.60478380723</v>
       </c>
       <c r="E31">
         <v>-5428.811</v>
@@ -3835,37 +3835,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M31">
-        <v>575.6643231000002</v>
+        <v>549.8141117000001</v>
       </c>
       <c r="N31">
-        <v>1632.266289144898</v>
+        <v>1658.116500544898</v>
       </c>
       <c r="O31">
-        <v>359.0985836118776</v>
+        <v>364.7856301198776</v>
       </c>
       <c r="P31">
-        <v>1273.167705533021</v>
+        <v>1293.330870425021</v>
       </c>
       <c r="Q31">
-        <v>2771.76770553302</v>
+        <v>2791.930870425021</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.07882449073088142</v>
+        <v>0.07880325891956647</v>
       </c>
       <c r="T31">
         <v>0.7621999750477246</v>
       </c>
       <c r="U31">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V31">
         <v>0.22</v>
       </c>
       <c r="W31">
-        <v>0.04516200000000001</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.835448061736758</v>
+        <v>4.015776542035413</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.06900088880931074</v>
+        <v>0.06837744964742716</v>
       </c>
       <c r="C32">
-        <v>22664.65290832447</v>
+        <v>23509.4014083955</v>
       </c>
       <c r="D32">
-        <v>31352.98290832448</v>
+        <v>32197.73140839551</v>
       </c>
       <c r="E32">
         <v>-5085.969999999999</v>
@@ -3917,37 +3917,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M32">
-        <v>595.5148170000001</v>
+        <v>568.7732190000002</v>
       </c>
       <c r="N32">
-        <v>1612.415795244898</v>
+        <v>1639.157393244898</v>
       </c>
       <c r="O32">
-        <v>354.7314749538776</v>
+        <v>360.6146265138776</v>
       </c>
       <c r="P32">
-        <v>1257.684320291021</v>
+        <v>1278.54276673102</v>
       </c>
       <c r="Q32">
-        <v>2756.284320291021</v>
+        <v>2777.14276673102</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.07921755544187248</v>
+        <v>0.07919607092489594</v>
       </c>
       <c r="T32">
         <v>0.7712718458405531</v>
       </c>
       <c r="U32">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V32">
         <v>0.22</v>
       </c>
       <c r="W32">
-        <v>0.04516200000000001</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.7075997930122</v>
+        <v>3.881917323967565</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.06893940919969566</v>
+        <v>0.06829572546196214</v>
       </c>
       <c r="C33">
-        <v>22405.11434413159</v>
+        <v>23283.53078028336</v>
       </c>
       <c r="D33">
-        <v>31436.28534413159</v>
+        <v>32314.70178028337</v>
       </c>
       <c r="E33">
         <v>-4743.128999999999</v>
@@ -3999,37 +3999,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M33">
-        <v>615.3653109000002</v>
+        <v>587.7323263000002</v>
       </c>
       <c r="N33">
-        <v>1592.565301344898</v>
+        <v>1620.198285944898</v>
       </c>
       <c r="O33">
-        <v>350.3643662958776</v>
+        <v>356.4436229078776</v>
       </c>
       <c r="P33">
-        <v>1242.200935049021</v>
+        <v>1263.75466303702</v>
       </c>
       <c r="Q33">
-        <v>2740.800935049021</v>
+        <v>2762.35466303702</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.07962201333289226</v>
+        <v>0.07960026878545237</v>
       </c>
       <c r="T33">
         <v>0.7806066694099855</v>
       </c>
       <c r="U33">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V33">
         <v>0.22</v>
       </c>
       <c r="W33">
-        <v>0.04516200000000001</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.587999799689225</v>
+        <v>3.75669418448474</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.06887792959008057</v>
+        <v>0.0682140012764971</v>
       </c>
       <c r="C34">
-        <v>22146.01961535413</v>
+        <v>23058.51312868784</v>
       </c>
       <c r="D34">
-        <v>31520.03161535413</v>
+        <v>32432.52512868784</v>
       </c>
       <c r="E34">
         <v>-4400.287999999999</v>
@@ -4081,37 +4081,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M34">
-        <v>635.2158048000002</v>
+        <v>606.6914336000002</v>
       </c>
       <c r="N34">
-        <v>1572.714807444898</v>
+        <v>1601.239178644898</v>
       </c>
       <c r="O34">
-        <v>345.9972576378776</v>
+        <v>352.2726193018776</v>
       </c>
       <c r="P34">
-        <v>1226.717549807021</v>
+        <v>1248.96655934302</v>
       </c>
       <c r="Q34">
-        <v>2725.31754980702</v>
+        <v>2747.56655934302</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.08003836704423614</v>
+        <v>0.0800163548183781</v>
       </c>
       <c r="T34">
         <v>0.7902160466138127</v>
       </c>
       <c r="U34">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V34">
         <v>0.22</v>
       </c>
       <c r="W34">
-        <v>0.04516200000000001</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.475874805948937</v>
+        <v>3.639297491219592</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.06881644998046549</v>
+        <v>0.06813227709103206</v>
       </c>
       <c r="C35">
-        <v>21887.37227859984</v>
+        <v>22834.35781792195</v>
       </c>
       <c r="D35">
-        <v>31604.22527859984</v>
+        <v>32551.21081792196</v>
       </c>
       <c r="E35">
         <v>-4057.446999999998</v>
@@ -4163,37 +4163,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M35">
-        <v>655.0662987000002</v>
+        <v>625.6505409000002</v>
       </c>
       <c r="N35">
-        <v>1552.864313544898</v>
+        <v>1582.280071344898</v>
       </c>
       <c r="O35">
-        <v>341.6301489798776</v>
+        <v>348.1016156958776</v>
       </c>
       <c r="P35">
-        <v>1211.234164565021</v>
+        <v>1234.178455649021</v>
       </c>
       <c r="Q35">
-        <v>2709.834164565021</v>
+        <v>2732.778455649021</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.08046714922457536</v>
+        <v>0.08044486132989861</v>
       </c>
       <c r="T35">
         <v>0.8001122708983512</v>
       </c>
       <c r="U35">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V35">
         <v>0.22</v>
       </c>
       <c r="W35">
-        <v>0.04516200000000001</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.370545266374727</v>
+        <v>3.529015749061422</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.06875497037085042</v>
+        <v>0.06805055290556704</v>
       </c>
       <c r="C36">
-        <v>21629.17592857867</v>
+        <v>22611.07434987566</v>
       </c>
       <c r="D36">
-        <v>31688.86992857868</v>
+        <v>32670.76834987567</v>
       </c>
       <c r="E36">
         <v>-3714.605999999998</v>
@@ -4245,37 +4245,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M36">
-        <v>674.9167926000002</v>
+        <v>644.6096482000003</v>
       </c>
       <c r="N36">
-        <v>1533.013819644898</v>
+        <v>1563.320964044898</v>
       </c>
       <c r="O36">
-        <v>337.2630403218776</v>
+        <v>343.9306120898776</v>
       </c>
       <c r="P36">
-        <v>1195.750779323021</v>
+        <v>1219.390351955021</v>
       </c>
       <c r="Q36">
-        <v>2694.350779323021</v>
+        <v>2717.990351955021</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.08090892480431881</v>
+        <v>0.08088635288722279</v>
       </c>
       <c r="T36">
         <v>0.8103083807672699</v>
       </c>
       <c r="U36">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V36">
         <v>0.22</v>
       </c>
       <c r="W36">
-        <v>0.04516200000000001</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.271411582069587</v>
+        <v>3.425221168206674</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.06869349076123533</v>
+        <v>0.067968828720102</v>
       </c>
       <c r="C37">
-        <v>21371.43419861446</v>
+        <v>22388.67236655179</v>
       </c>
       <c r="D37">
-        <v>31773.96919861446</v>
+        <v>32791.20736655179</v>
       </c>
       <c r="E37">
         <v>-3371.764999999998</v>
@@ -4327,37 +4327,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M37">
-        <v>694.7672865000003</v>
+        <v>663.5687555000003</v>
       </c>
       <c r="N37">
-        <v>1513.163325744898</v>
+        <v>1544.361856744898</v>
       </c>
       <c r="O37">
-        <v>332.8959316638775</v>
+        <v>339.7596084838776</v>
       </c>
       <c r="P37">
-        <v>1180.26739408102</v>
+        <v>1204.60224826102</v>
       </c>
       <c r="Q37">
-        <v>2678.86739408102</v>
+        <v>2703.20224826102</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.0813642934788236</v>
+        <v>0.08134142880015693</v>
       </c>
       <c r="T37">
         <v>0.8208182170936936</v>
       </c>
       <c r="U37">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V37">
         <v>0.22</v>
       </c>
       <c r="W37">
-        <v>0.04516200000000001</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.177942679724742</v>
+        <v>3.327357706257912</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.06863201115162026</v>
+        <v>0.06788710453463698</v>
       </c>
       <c r="C38">
-        <v>21114.15076116468</v>
+        <v>22167.16165265804</v>
       </c>
       <c r="D38">
-        <v>31859.52676116468</v>
+        <v>32912.53765265804</v>
       </c>
       <c r="E38">
         <v>-3028.923999999999</v>
@@ -4409,37 +4409,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M38">
-        <v>714.6177804000001</v>
+        <v>682.5278628000002</v>
       </c>
       <c r="N38">
-        <v>1493.312831844898</v>
+        <v>1525.402749444898</v>
       </c>
       <c r="O38">
-        <v>328.5288230058776</v>
+        <v>335.5886048778776</v>
       </c>
       <c r="P38">
-        <v>1164.784008839021</v>
+        <v>1189.814144567021</v>
       </c>
       <c r="Q38">
-        <v>2663.384008839021</v>
+        <v>2688.414144567021</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.08183389242440665</v>
+        <v>0.08181072583537027</v>
       </c>
       <c r="T38">
         <v>0.831656485805318</v>
       </c>
       <c r="U38">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V38">
         <v>0.22</v>
       </c>
       <c r="W38">
-        <v>0.04516200000000001</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.089666494176833</v>
+        <v>3.234931103306304</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.06857053154200518</v>
+        <v>0.06780538034917194</v>
       </c>
       <c r="C39">
-        <v>20857.32932834889</v>
+        <v>21946.55213825706</v>
       </c>
       <c r="D39">
-        <v>31945.54632834889</v>
+        <v>33034.76913825706</v>
       </c>
       <c r="E39">
         <v>-2686.082999999999</v>
@@ -4491,37 +4491,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M39">
-        <v>734.4682743000002</v>
+        <v>701.4869701000002</v>
       </c>
       <c r="N39">
-        <v>1473.462337944898</v>
+        <v>1506.443642144898</v>
       </c>
       <c r="O39">
-        <v>324.1617143478776</v>
+        <v>331.4176012718776</v>
       </c>
       <c r="P39">
-        <v>1149.300623597021</v>
+        <v>1175.026040873021</v>
       </c>
       <c r="Q39">
-        <v>2647.900623597021</v>
+        <v>2673.62604087302</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.08231839927302409</v>
+        <v>0.08229492118916182</v>
       </c>
       <c r="T39">
         <v>0.8428388265395338</v>
       </c>
       <c r="U39">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V39">
         <v>0.22</v>
       </c>
       <c r="W39">
-        <v>0.04516200000000001</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.006161994334215</v>
+        <v>3.147500532946674</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.0692796919323901</v>
+        <v>0.06772365616370692</v>
       </c>
       <c r="C40">
-        <v>19549.63256403541</v>
+        <v>21726.85390147547</v>
       </c>
       <c r="D40">
-        <v>30980.69056403541</v>
+        <v>33157.91190147547</v>
       </c>
       <c r="E40">
         <v>-2343.241999999998</v>
@@ -4573,45 +4573,45 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M40">
-        <v>788.1914590000002</v>
+        <v>720.4460774000003</v>
       </c>
       <c r="N40">
-        <v>1419.739153244898</v>
+        <v>1487.484534844898</v>
       </c>
       <c r="O40">
-        <v>312.3426137138776</v>
+        <v>327.2465976658776</v>
       </c>
       <c r="P40">
-        <v>1107.396539531021</v>
+        <v>1160.23793717902</v>
       </c>
       <c r="Q40">
-        <v>2605.996539531021</v>
+        <v>2658.837937179021</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.08281853537482274</v>
+        <v>0.08279473574791438</v>
       </c>
       <c r="T40">
         <v>0.8543818879425952</v>
       </c>
       <c r="U40">
-        <v>0.06050000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V40">
         <v>0.22</v>
       </c>
       <c r="W40">
-        <v>0.04719</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y40">
-        <v>2.80126178358512</v>
+        <v>3.06467157155334</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.06923849232277503</v>
+        <v>0.06840243197824188</v>
       </c>
       <c r="C41">
-        <v>19261.24866559579</v>
+        <v>20388.24445138707</v>
       </c>
       <c r="D41">
-        <v>31035.14766559579</v>
+        <v>32162.14345138707</v>
       </c>
       <c r="E41">
         <v>-2000.400999999998</v>
@@ -4655,37 +4655,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M41">
-        <v>808.9333395000002</v>
+        <v>772.8321822000003</v>
       </c>
       <c r="N41">
-        <v>1398.997272744898</v>
+        <v>1435.098430044898</v>
       </c>
       <c r="O41">
-        <v>307.7794000038776</v>
+        <v>315.7216546098776</v>
       </c>
       <c r="P41">
-        <v>1091.217872741021</v>
+        <v>1119.376775435021</v>
       </c>
       <c r="Q41">
-        <v>2589.81787274102</v>
+        <v>2617.97677543502</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.0833350693815984</v>
+        <v>0.08331093766924898</v>
       </c>
       <c r="T41">
         <v>0.8663034103752651</v>
       </c>
       <c r="U41">
-        <v>0.06050000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V41">
         <v>0.22</v>
       </c>
       <c r="W41">
-        <v>0.04719</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.729434558364988</v>
+        <v>2.856934096558509</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.06919729271315994</v>
+        <v>0.06834020779277684</v>
       </c>
       <c r="C42">
-        <v>18973.05655099653</v>
+        <v>20134.1898191735</v>
       </c>
       <c r="D42">
-        <v>31089.79655099654</v>
+        <v>32250.9298191735</v>
       </c>
       <c r="E42">
         <v>-1657.559999999998</v>
@@ -4737,37 +4737,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M42">
-        <v>829.6752200000003</v>
+        <v>792.6483920000003</v>
       </c>
       <c r="N42">
-        <v>1378.255392244898</v>
+        <v>1415.282220244898</v>
       </c>
       <c r="O42">
-        <v>303.2161862938776</v>
+        <v>311.3620884538776</v>
       </c>
       <c r="P42">
-        <v>1075.03920595102</v>
+        <v>1103.920131791021</v>
       </c>
       <c r="Q42">
-        <v>2573.63920595102</v>
+        <v>2602.520131791021</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.0838688211885999</v>
+        <v>0.08384434632129474</v>
       </c>
       <c r="T42">
         <v>0.8786223168890241</v>
       </c>
       <c r="U42">
-        <v>0.06050000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V42">
         <v>0.22</v>
       </c>
       <c r="W42">
-        <v>0.04719</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.661198694405863</v>
+        <v>2.785510744144545</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.06915609310354487</v>
+        <v>0.06827798360731181</v>
       </c>
       <c r="C43">
-        <v>18685.05723514441</v>
+        <v>19880.62674879327</v>
       </c>
       <c r="D43">
-        <v>31144.63823514442</v>
+        <v>32340.20774879327</v>
       </c>
       <c r="E43">
         <v>-1314.718999999997</v>
@@ -4819,37 +4819,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M43">
-        <v>850.4171005000003</v>
+        <v>812.4646018000003</v>
       </c>
       <c r="N43">
-        <v>1357.513511744898</v>
+        <v>1395.466010444898</v>
       </c>
       <c r="O43">
-        <v>298.6529725838776</v>
+        <v>307.0025222978776</v>
       </c>
       <c r="P43">
-        <v>1058.860539161021</v>
+        <v>1088.463488147021</v>
       </c>
       <c r="Q43">
-        <v>2557.46053916102</v>
+        <v>2587.063488147021</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.08442066627719469</v>
+        <v>0.08439583662256239</v>
       </c>
       <c r="T43">
         <v>0.891358813454097</v>
       </c>
       <c r="U43">
-        <v>0.06050000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V43">
         <v>0.22</v>
       </c>
       <c r="W43">
-        <v>0.04719</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.596291409176452</v>
+        <v>2.717571457701996</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.0691148934939298</v>
+        <v>0.06821575942184679</v>
       </c>
       <c r="C44">
-        <v>18397.25174012001</v>
+        <v>19627.55933384419</v>
       </c>
       <c r="D44">
-        <v>31199.67374012001</v>
+        <v>32429.98133384419</v>
       </c>
       <c r="E44">
         <v>-971.8779999999988</v>
@@ -4901,37 +4901,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M44">
-        <v>871.1589810000002</v>
+        <v>832.2808116000002</v>
       </c>
       <c r="N44">
-        <v>1336.771631244898</v>
+        <v>1375.649800644898</v>
       </c>
       <c r="O44">
-        <v>294.0897588738777</v>
+        <v>302.6429561418776</v>
       </c>
       <c r="P44">
-        <v>1042.681872371021</v>
+        <v>1073.006844503021</v>
       </c>
       <c r="Q44">
-        <v>2541.281872371021</v>
+        <v>2571.606844503021</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.08499154050677549</v>
+        <v>0.08496634383077031</v>
       </c>
       <c r="T44">
         <v>0.9045344995558964</v>
       </c>
       <c r="U44">
-        <v>0.06050000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V44">
         <v>0.22</v>
       </c>
       <c r="W44">
-        <v>0.04719</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.534474947053204</v>
+        <v>2.652867375375758</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.06997927388431471</v>
+        <v>0.06815353523638176</v>
       </c>
       <c r="C45">
-        <v>16939.05937363991</v>
+        <v>19374.99171350453</v>
       </c>
       <c r="D45">
-        <v>30084.32237363991</v>
+        <v>32520.25471350453</v>
       </c>
       <c r="E45">
         <v>-629.0369999999984</v>
@@ -4983,45 +4983,45 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M45">
-        <v>931.7047016000002</v>
+        <v>852.0970214000002</v>
       </c>
       <c r="N45">
-        <v>1276.225910644898</v>
+        <v>1355.833590844898</v>
       </c>
       <c r="O45">
-        <v>280.7697003418776</v>
+        <v>298.2833899858776</v>
       </c>
       <c r="P45">
-        <v>995.4562103030206</v>
+        <v>1057.55020085902</v>
       </c>
       <c r="Q45">
-        <v>2494.056210303021</v>
+        <v>2556.150200859021</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.08558244541107843</v>
+        <v>0.08555686883575746</v>
       </c>
       <c r="T45">
         <v>0.9181724904331976</v>
       </c>
       <c r="U45">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V45">
         <v>0.22</v>
       </c>
       <c r="W45">
-        <v>0.04929600000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.369775110561595</v>
+        <v>2.59117278525074</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.06995913427469963</v>
+        <v>0.06809131105091673</v>
       </c>
       <c r="C46">
-        <v>16621.29735624128</v>
+        <v>19122.92807316907</v>
       </c>
       <c r="D46">
-        <v>30109.40135624128</v>
+        <v>32611.03207316907</v>
       </c>
       <c r="E46">
         <v>-286.1959999999981</v>
@@ -5065,45 +5065,45 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M46">
-        <v>953.3722528000003</v>
+        <v>871.9132312000003</v>
       </c>
       <c r="N46">
-        <v>1254.558359444898</v>
+        <v>1336.017381044898</v>
       </c>
       <c r="O46">
-        <v>276.0028390778776</v>
+        <v>293.9238238298776</v>
       </c>
       <c r="P46">
-        <v>978.5555203670206</v>
+        <v>1042.093557215021</v>
       </c>
       <c r="Q46">
-        <v>2477.15552036702</v>
+        <v>2540.693557215021</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.08619445406196362</v>
+        <v>0.08616848401949415</v>
       </c>
       <c r="T46">
         <v>0.9322975524132596</v>
       </c>
       <c r="U46">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V46">
         <v>0.22</v>
       </c>
       <c r="W46">
-        <v>0.04929600000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>2.315916585321559</v>
+        <v>2.53228249467686</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.06993899466508455</v>
+        <v>0.06925758686545169</v>
       </c>
       <c r="C47">
-        <v>16303.57718656052</v>
+        <v>17158.7157781542</v>
       </c>
       <c r="D47">
-        <v>30134.52218656052</v>
+        <v>30989.66077815421</v>
       </c>
       <c r="E47">
         <v>56.64500000000226</v>
@@ -5147,37 +5147,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M47">
-        <v>975.0398040000002</v>
+        <v>945.7268985000003</v>
       </c>
       <c r="N47">
-        <v>1232.890808244898</v>
+        <v>1262.203713744898</v>
       </c>
       <c r="O47">
-        <v>271.2359778138776</v>
+        <v>277.6848170238776</v>
       </c>
       <c r="P47">
-        <v>961.6548304310206</v>
+        <v>984.5188967210205</v>
       </c>
       <c r="Q47">
-        <v>2460.25483043102</v>
+        <v>2483.118896721021</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.08682871757288099</v>
+        <v>0.08680233975536669</v>
       </c>
       <c r="T47">
         <v>0.9469362530107783</v>
       </c>
       <c r="U47">
-        <v>0.06320000000000001</v>
+        <v>0.06130000000000001</v>
       </c>
       <c r="V47">
         <v>0.22</v>
       </c>
       <c r="W47">
-        <v>0.04929600000000001</v>
+        <v>0.04781400000000001</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.264451772314413</v>
+        <v>2.334638695110455</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.07160521505546949</v>
+        <v>0.06922266267998667</v>
       </c>
       <c r="C48">
-        <v>14014.97618363769</v>
+        <v>16862.08167936357</v>
       </c>
       <c r="D48">
-        <v>28188.76218363769</v>
+        <v>31035.86767936357</v>
       </c>
       <c r="E48">
         <v>399.4860000000026</v>
@@ -5229,45 +5229,45 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M48">
-        <v>1070.829579400001</v>
+        <v>966.7430518000003</v>
       </c>
       <c r="N48">
-        <v>1137.101032844898</v>
+        <v>1241.187560444898</v>
       </c>
       <c r="O48">
-        <v>250.1622272258775</v>
+        <v>273.0612632978776</v>
       </c>
       <c r="P48">
-        <v>886.9388056190203</v>
+        <v>968.1262971470205</v>
       </c>
       <c r="Q48">
-        <v>2385.53880561902</v>
+        <v>2466.72629714702</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.08748647232494347</v>
+        <v>0.08745967162960491</v>
       </c>
       <c r="T48">
         <v>0.9621171277045015</v>
       </c>
       <c r="U48">
-        <v>0.06790000000000002</v>
+        <v>0.06130000000000001</v>
       </c>
       <c r="V48">
         <v>0.22</v>
       </c>
       <c r="W48">
-        <v>0.05296200000000002</v>
+        <v>0.04781400000000001</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y48">
-        <v>2.061887955581158</v>
+        <v>2.283885679999358</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.0716217354458544</v>
+        <v>0.07021421849452164</v>
       </c>
       <c r="C49">
-        <v>13654.10040217547</v>
+        <v>15258.75408776874</v>
       </c>
       <c r="D49">
-        <v>28170.72740217547</v>
+        <v>29775.38108776875</v>
       </c>
       <c r="E49">
         <v>742.327000000003</v>
@@ -5311,37 +5311,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M49">
-        <v>1094.1084833</v>
+        <v>1032.8770807</v>
       </c>
       <c r="N49">
-        <v>1113.822128944898</v>
+        <v>1175.053531544898</v>
       </c>
       <c r="O49">
-        <v>245.0408683678776</v>
+        <v>258.5117769398776</v>
       </c>
       <c r="P49">
-        <v>868.7812605770204</v>
+        <v>916.5417546050205</v>
       </c>
       <c r="Q49">
-        <v>2367.38126057702</v>
+        <v>2415.141754605021</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.08816904801104603</v>
+        <v>0.08814180848022948</v>
       </c>
       <c r="T49">
         <v>0.9778708655942143</v>
       </c>
       <c r="U49">
-        <v>0.06790000000000002</v>
+        <v>0.0641</v>
       </c>
       <c r="V49">
         <v>0.22</v>
       </c>
       <c r="W49">
-        <v>0.05296200000000002</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.018017999079431</v>
+        <v>2.137650891380552</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.07687985583623931</v>
+        <v>0.0702011343090566</v>
       </c>
       <c r="C50">
-        <v>8545.308203887122</v>
+        <v>14931.87900982426</v>
       </c>
       <c r="D50">
-        <v>23404.77620388712</v>
+        <v>29791.34700982427</v>
       </c>
       <c r="E50">
         <v>1085.168000000001</v>
@@ -5393,45 +5393,45 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M50">
-        <v>1347.7765392</v>
+        <v>1054.8531888</v>
       </c>
       <c r="N50">
-        <v>860.1540730448983</v>
+        <v>1153.077423444898</v>
       </c>
       <c r="O50">
-        <v>189.2338960698776</v>
+        <v>253.6770331578776</v>
       </c>
       <c r="P50">
-        <v>670.9201769750207</v>
+        <v>899.4003902870206</v>
       </c>
       <c r="Q50">
-        <v>2169.520176975021</v>
+        <v>2398.00039028702</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.08887787660815252</v>
+        <v>0.08885018136357037</v>
       </c>
       <c r="T50">
         <v>0.9942305164796852</v>
       </c>
       <c r="U50">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V50">
         <v>0.22</v>
       </c>
       <c r="W50">
-        <v>0.06388200000000001</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y50">
-        <v>1.638202289494859</v>
+        <v>2.093116497810124</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.07700557622662424</v>
+        <v>0.07018805012359156</v>
       </c>
       <c r="C51">
-        <v>8108.174517866668</v>
+        <v>14605.02106330966</v>
       </c>
       <c r="D51">
-        <v>23310.48351786667</v>
+        <v>29807.33006330967</v>
       </c>
       <c r="E51">
         <v>1428.009000000002</v>
@@ -5475,45 +5475,45 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M51">
-        <v>1375.8552171</v>
+        <v>1076.8292969</v>
       </c>
       <c r="N51">
-        <v>832.0753951448983</v>
+        <v>1131.101315344898</v>
       </c>
       <c r="O51">
-        <v>183.0565869318776</v>
+        <v>248.8422893758776</v>
       </c>
       <c r="P51">
-        <v>649.0188082130206</v>
+        <v>882.2590259690206</v>
       </c>
       <c r="Q51">
-        <v>2147.618808213021</v>
+        <v>2380.85902596902</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.08961450240514555</v>
+        <v>0.08958633357566972</v>
       </c>
       <c r="T51">
         <v>1.011231722301841</v>
       </c>
       <c r="U51">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V51">
         <v>0.22</v>
       </c>
       <c r="W51">
-        <v>0.06388200000000001</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y51">
-        <v>1.60476958970925</v>
+        <v>2.05039983458951</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.07713129661700915</v>
+        <v>0.07017496593812653</v>
       </c>
       <c r="C52">
-        <v>7671.797552095741</v>
+        <v>14278.18027581276</v>
       </c>
       <c r="D52">
-        <v>23216.94755209574</v>
+        <v>29823.33027581276</v>
       </c>
       <c r="E52">
         <v>1770.850000000002</v>
@@ -5557,45 +5557,45 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M52">
-        <v>1403.933895</v>
+        <v>1098.805405</v>
       </c>
       <c r="N52">
-        <v>803.996717244898</v>
+        <v>1109.125207244898</v>
       </c>
       <c r="O52">
-        <v>176.8792777938776</v>
+        <v>244.0075455938776</v>
       </c>
       <c r="P52">
-        <v>627.1174394510205</v>
+        <v>865.1176616510205</v>
       </c>
       <c r="Q52">
-        <v>2125.71743945102</v>
+        <v>2363.717661651021</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.0903805932340183</v>
+        <v>0.09035193187625305</v>
       </c>
       <c r="T52">
         <v>1.028912976356883</v>
       </c>
       <c r="U52">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V52">
         <v>0.22</v>
       </c>
       <c r="W52">
-        <v>0.06388200000000001</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y52">
-        <v>1.572674197915065</v>
+        <v>2.009391837897719</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.07725701700739407</v>
+        <v>0.07326472175266151</v>
       </c>
       <c r="C53">
-        <v>7236.168233702119</v>
+        <v>10580.24218222724</v>
       </c>
       <c r="D53">
-        <v>23124.15923370212</v>
+        <v>26468.23318222724</v>
       </c>
       <c r="E53">
         <v>2113.691000000003</v>
@@ -5639,45 +5639,45 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M53">
-        <v>1432.0125729</v>
+        <v>1257.1636629</v>
       </c>
       <c r="N53">
-        <v>775.918039344898</v>
+        <v>950.766949344898</v>
       </c>
       <c r="O53">
-        <v>170.7019686558776</v>
+        <v>209.1687288558776</v>
       </c>
       <c r="P53">
-        <v>605.2160706890204</v>
+        <v>741.5982204890204</v>
       </c>
       <c r="Q53">
-        <v>2103.81607068902</v>
+        <v>2240.19822048902</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.09117795307631443</v>
+        <v>0.09114877908706429</v>
       </c>
       <c r="T53">
         <v>1.047315914250907</v>
       </c>
       <c r="U53">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V53">
         <v>0.22</v>
       </c>
       <c r="W53">
-        <v>0.06388200000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y53">
-        <v>1.541837448936338</v>
+        <v>1.756279375074911</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.07738273739777901</v>
+        <v>0.07489431756719647</v>
       </c>
       <c r="C54">
-        <v>6801.277634277943</v>
+        <v>8754.894438005664</v>
       </c>
       <c r="D54">
-        <v>23032.10963427795</v>
+        <v>24985.72643800567</v>
       </c>
       <c r="E54">
         <v>2456.532000000003</v>
@@ -5721,37 +5721,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M54">
-        <v>1460.0912508</v>
+        <v>1351.3420856</v>
       </c>
       <c r="N54">
-        <v>747.839361444898</v>
+        <v>856.5885266448979</v>
       </c>
       <c r="O54">
-        <v>164.5246595178776</v>
+        <v>188.4494758618775</v>
       </c>
       <c r="P54">
-        <v>583.3147019270205</v>
+        <v>668.1390507830204</v>
       </c>
       <c r="Q54">
-        <v>2081.91470192702</v>
+        <v>2166.739050783021</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.09200853624537292</v>
+        <v>0.09197882826499262</v>
       </c>
       <c r="T54">
         <v>1.066485641223848</v>
       </c>
       <c r="U54">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V54">
         <v>0.22</v>
       </c>
       <c r="W54">
-        <v>0.06388200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.512186728764485</v>
+        <v>1.633879856013342</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.0990692298691343</v>
+        <v>0.07497249338173144</v>
       </c>
       <c r="C55">
-        <v>-2918.189861173132</v>
+        <v>8345.097230646916</v>
       </c>
       <c r="D55">
-        <v>13655.48313882687</v>
+        <v>24918.77023064692</v>
       </c>
       <c r="E55">
         <v>2799.373000000003</v>
@@ -5803,45 +5803,45 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M55">
-        <v>2378.528005700001</v>
+        <v>1377.3294334</v>
       </c>
       <c r="N55">
-        <v>-170.5973934551025</v>
+        <v>830.601178844898</v>
       </c>
       <c r="O55">
-        <v>-37.53142656012255</v>
+        <v>182.7322593458776</v>
       </c>
       <c r="P55">
-        <v>-133.06596689498</v>
+        <v>647.8689194990204</v>
       </c>
       <c r="Q55">
-        <v>1365.53403310502</v>
+        <v>2146.468919499021</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.0933201100386194</v>
+        <v>0.09284419868453497</v>
       </c>
       <c r="T55">
-        <v>1.096756555032397</v>
+        <v>1.086471101259468</v>
       </c>
       <c r="U55">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V55">
-        <v>0.2042207338025112</v>
+        <v>0.22</v>
       </c>
       <c r="W55">
-        <v>0.1041675059452513</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y55">
-        <v>0.9282760627386871</v>
+        <v>1.60305193420177</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.09992022986913431</v>
+        <v>0.07505066919626641</v>
       </c>
       <c r="C56">
-        <v>-3475.753085732073</v>
+        <v>7935.6579197871</v>
       </c>
       <c r="D56">
-        <v>13440.76091426793</v>
+        <v>24852.1719197871</v>
       </c>
       <c r="E56">
         <v>3142.214000000004</v>
@@ -5885,45 +5885,45 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M56">
-        <v>2423.405892600001</v>
+        <v>1403.3167812</v>
       </c>
       <c r="N56">
-        <v>-215.4752803551023</v>
+        <v>804.613831044898</v>
       </c>
       <c r="O56">
-        <v>-47.40456167812251</v>
+        <v>177.0150428298776</v>
       </c>
       <c r="P56">
-        <v>-168.0707186769798</v>
+        <v>627.5987882150205</v>
       </c>
       <c r="Q56">
-        <v>1330.52928132302</v>
+        <v>2126.198788215021</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.09435315590902417</v>
+        <v>0.09374719390492696</v>
       </c>
       <c r="T56">
-        <v>1.120599088837449</v>
+        <v>1.107325494340115</v>
       </c>
       <c r="U56">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V56">
-        <v>0.2004388683617239</v>
+        <v>0.22</v>
       </c>
       <c r="W56">
-        <v>0.1046625521314503</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y56">
-        <v>0.9110857652805634</v>
+        <v>1.573365787272107</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1007712298691343</v>
+        <v>0.07512884501080137</v>
       </c>
       <c r="C57">
-        <v>-4026.668155846057</v>
+        <v>7526.573643514992</v>
       </c>
       <c r="D57">
-        <v>13232.68684415395</v>
+        <v>24785.928643515</v>
       </c>
       <c r="E57">
         <v>3485.055000000004</v>
@@ -5967,45 +5967,45 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M57">
-        <v>2468.283779500001</v>
+        <v>1429.304129000001</v>
       </c>
       <c r="N57">
-        <v>-260.3531672551026</v>
+        <v>778.6264832448978</v>
       </c>
       <c r="O57">
-        <v>-57.27769679612256</v>
+        <v>171.2978263138775</v>
       </c>
       <c r="P57">
-        <v>-203.07547045898</v>
+        <v>607.3286569310203</v>
       </c>
       <c r="Q57">
-        <v>1295.52452954102</v>
+        <v>2105.92865693102</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.09543211492922471</v>
+        <v>0.09469032224622526</v>
       </c>
       <c r="T57">
-        <v>1.145501290811615</v>
+        <v>1.129106749335457</v>
       </c>
       <c r="U57">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V57">
-        <v>0.1967945253006017</v>
+        <v>0.22</v>
       </c>
       <c r="W57">
-        <v>0.1051395966381513</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y57">
-        <v>0.8945205695481894</v>
+        <v>1.544759136594433</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1016222298691343</v>
+        <v>0.07520702082533634</v>
       </c>
       <c r="C58">
-        <v>-4571.239121323506</v>
+        <v>7117.841570351848</v>
       </c>
       <c r="D58">
-        <v>13030.9568786765</v>
+        <v>24720.03757035185</v>
       </c>
       <c r="E58">
         <v>3827.896000000004</v>
@@ -6049,45 +6049,45 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M58">
-        <v>2513.161666400001</v>
+        <v>1455.291476800001</v>
       </c>
       <c r="N58">
-        <v>-305.2310541551028</v>
+        <v>752.6391354448979</v>
       </c>
       <c r="O58">
-        <v>-67.15083191412262</v>
+        <v>165.5806097978775</v>
       </c>
       <c r="P58">
-        <v>-238.0802222409802</v>
+        <v>587.0585256470204</v>
       </c>
       <c r="Q58">
-        <v>1260.51977775902</v>
+        <v>2085.65852564702</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.09656011754125254</v>
+        <v>0.09567632005758259</v>
       </c>
       <c r="T58">
-        <v>1.171535411057333</v>
+        <v>1.151878061376041</v>
       </c>
       <c r="U58">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V58">
-        <v>0.1932803373488052</v>
+        <v>0.22</v>
       </c>
       <c r="W58">
-        <v>0.1055996038410414</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y58">
-        <v>0.8785469879491146</v>
+        <v>1.517174152012389</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1024732298691343</v>
+        <v>0.08159851663987132</v>
       </c>
       <c r="C59">
-        <v>-5109.751769637194</v>
+        <v>2361.465276264335</v>
       </c>
       <c r="D59">
-        <v>12835.28523036281</v>
+        <v>20306.50227626434</v>
       </c>
       <c r="E59">
         <v>4170.737000000005</v>
@@ -6131,45 +6131,45 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M59">
-        <v>2558.039553300001</v>
+        <v>1758.774330000001</v>
       </c>
       <c r="N59">
-        <v>-350.1089410551026</v>
+        <v>449.1562822448977</v>
       </c>
       <c r="O59">
-        <v>-77.02396703212257</v>
+        <v>98.8143820938775</v>
       </c>
       <c r="P59">
-        <v>-273.08497402298</v>
+        <v>350.3419001510202</v>
       </c>
       <c r="Q59">
-        <v>1225.51502597702</v>
+        <v>1848.94190015102</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.09774058539104913</v>
+        <v>0.09670817823225886</v>
       </c>
       <c r="T59">
-        <v>1.198780420616806</v>
+        <v>1.175708504209211</v>
       </c>
       <c r="U59">
-        <v>0.1309</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V59">
-        <v>0.1898894542374227</v>
+        <v>0.22</v>
       </c>
       <c r="W59">
-        <v>0.1060434704403214</v>
+        <v>0.07020000000000001</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y59">
-        <v>0.8631338828973757</v>
+        <v>1.25538028079185</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1033242298691343</v>
+        <v>0.09589491198721191</v>
       </c>
       <c r="C60">
-        <v>-5642.474976767782</v>
+        <v>-3776.570747478916</v>
       </c>
       <c r="D60">
-        <v>12645.40302323222</v>
+        <v>14511.30725252109</v>
       </c>
       <c r="E60">
         <v>4513.578000000001</v>
@@ -6213,37 +6213,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M60">
-        <v>2602.917440200001</v>
+        <v>2358.3346708</v>
       </c>
       <c r="N60">
-        <v>-394.9868279551024</v>
+        <v>-150.404058555102</v>
       </c>
       <c r="O60">
-        <v>-86.89710215012254</v>
+        <v>-33.08889288212244</v>
       </c>
       <c r="P60">
-        <v>-308.0897258049799</v>
+        <v>-117.3151656729795</v>
       </c>
       <c r="Q60">
-        <v>1190.51027419502</v>
+        <v>1381.28483432702</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.09897726599559789</v>
+        <v>0.09827412818149697</v>
       </c>
       <c r="T60">
-        <v>1.227322811583873</v>
+        <v>1.211873630057667</v>
       </c>
       <c r="U60">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V60">
-        <v>0.1866154981298809</v>
+        <v>0.2059693820000119</v>
       </c>
       <c r="W60">
-        <v>0.1064720312947986</v>
+        <v>0.09417203129479859</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8482522642267314</v>
+        <v>0.9362244636364179</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1041752298691343</v>
+        <v>0.09662291198721192</v>
       </c>
       <c r="C61">
-        <v>-6169.661939891099</v>
+        <v>-4327.275312685366</v>
       </c>
       <c r="D61">
-        <v>12461.0570601089</v>
+        <v>14303.44368731464</v>
       </c>
       <c r="E61">
         <v>4856.419000000002</v>
@@ -6295,37 +6295,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M61">
-        <v>2647.795327100001</v>
+        <v>2398.9956134</v>
       </c>
       <c r="N61">
-        <v>-439.8647148551022</v>
+        <v>-191.065001155102</v>
       </c>
       <c r="O61">
-        <v>-96.77023726812249</v>
+        <v>-42.03430025412244</v>
       </c>
       <c r="P61">
-        <v>-343.0944775869797</v>
+        <v>-149.0307009009796</v>
       </c>
       <c r="Q61">
-        <v>1155.50552241302</v>
+        <v>1349.56929909902</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1002742724832954</v>
+        <v>0.09955398496641153</v>
       </c>
       <c r="T61">
-        <v>1.257257514305431</v>
+        <v>1.241431523473707</v>
       </c>
       <c r="U61">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V61">
-        <v>0.1834525235853067</v>
+        <v>0.2024783755254355</v>
       </c>
       <c r="W61">
-        <v>0.1068860646626834</v>
+        <v>0.09458606466268336</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8338751072059394</v>
+        <v>0.920356252388343</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1050262298691343</v>
+        <v>0.09735091198721191</v>
       </c>
       <c r="C62">
-        <v>-6691.551303793107</v>
+        <v>-4872.108995316239</v>
       </c>
       <c r="D62">
-        <v>12282.0086962069</v>
+        <v>14101.45100468376</v>
       </c>
       <c r="E62">
         <v>5199.260000000002</v>
@@ -6377,37 +6377,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M62">
-        <v>2692.673214000001</v>
+        <v>2439.656556</v>
       </c>
       <c r="N62">
-        <v>-484.7426017551024</v>
+        <v>-231.725943755102</v>
       </c>
       <c r="O62">
-        <v>-106.6433723861225</v>
+        <v>-50.97970762612243</v>
       </c>
       <c r="P62">
-        <v>-378.0992293689799</v>
+        <v>-180.7462361289795</v>
       </c>
       <c r="Q62">
-        <v>1120.50077063102</v>
+        <v>1317.85376387102</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1016361292953778</v>
+        <v>0.1008978345905718</v>
       </c>
       <c r="T62">
-        <v>1.288688952163066</v>
+        <v>1.27246731156055</v>
       </c>
       <c r="U62">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V62">
-        <v>0.1803949815255516</v>
+        <v>0.1991037359333449</v>
       </c>
       <c r="W62">
-        <v>0.1072862969183053</v>
+        <v>0.0949862969183053</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.819977188752507</v>
+        <v>0.9050169815152039</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1058772298691343</v>
+        <v>0.09807891198721191</v>
       </c>
       <c r="C63">
-        <v>-7208.36819155024</v>
+        <v>-5411.317056932232</v>
       </c>
       <c r="D63">
-        <v>12108.03280844976</v>
+        <v>13905.08394306777</v>
       </c>
       <c r="E63">
         <v>5542.101000000002</v>
@@ -6459,37 +6459,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M63">
-        <v>2737.551100900001</v>
+        <v>2480.317498600001</v>
       </c>
       <c r="N63">
-        <v>-529.6204886551022</v>
+        <v>-272.3868863551024</v>
       </c>
       <c r="O63">
-        <v>-116.5165075041225</v>
+        <v>-59.92511499812254</v>
       </c>
       <c r="P63">
-        <v>-413.1039811509797</v>
+        <v>-212.4617713569799</v>
       </c>
       <c r="Q63">
-        <v>1085.49601884902</v>
+        <v>1286.13822864302</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1030678249183362</v>
+        <v>0.1023105995800737</v>
       </c>
       <c r="T63">
-        <v>1.321732258628786</v>
+        <v>1.305094678523641</v>
       </c>
       <c r="U63">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V63">
-        <v>0.1774376867464441</v>
+        <v>0.1958397402623064</v>
       </c>
       <c r="W63">
-        <v>0.1076734068048905</v>
+        <v>0.09537340680489047</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8065349397565643</v>
+        <v>0.8901806375559381</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1604327223377583</v>
+        <v>0.09880691198721192</v>
       </c>
       <c r="C64">
-        <v>-13313.61000713006</v>
+        <v>-5945.131285348096</v>
       </c>
       <c r="D64">
-        <v>6345.631992869945</v>
+        <v>13714.11071465191</v>
       </c>
       <c r="E64">
         <v>5884.942000000003</v>
@@ -6541,45 +6541,45 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M64">
-        <v>4587.075443600002</v>
+        <v>2520.978441200001</v>
       </c>
       <c r="N64">
-        <v>-2379.144831355103</v>
+        <v>-313.0478289551024</v>
       </c>
       <c r="O64">
-        <v>-523.4118628981226</v>
+        <v>-68.87052237012253</v>
       </c>
       <c r="P64">
-        <v>-1855.73296845698</v>
+        <v>-244.1773065849799</v>
       </c>
       <c r="Q64">
-        <v>-357.1329684569805</v>
+        <v>1254.42269341502</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1073814320704608</v>
+        <v>0.1037977206216546</v>
       </c>
       <c r="T64">
-        <v>1.421289623207329</v>
+        <v>1.339439275326895</v>
       </c>
       <c r="U64">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V64">
-        <v>0.1058942109556102</v>
+        <v>0.1926810347742047</v>
       </c>
       <c r="W64">
-        <v>0.1929480292757793</v>
+        <v>0.09574802927577933</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y64">
-        <v>0.4813373225255008</v>
+        <v>0.875822885337294</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1621327223377583</v>
+        <v>0.09953491198721191</v>
       </c>
       <c r="C65">
-        <v>-13749.18135995855</v>
+        <v>-6473.770907343469</v>
       </c>
       <c r="D65">
-        <v>6252.901640041454</v>
+        <v>13528.31209265654</v>
       </c>
       <c r="E65">
         <v>6227.783000000003</v>
@@ -6623,45 +6623,45 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M65">
-        <v>4661.060531400001</v>
+        <v>2561.639383800001</v>
       </c>
       <c r="N65">
-        <v>-2453.129919155103</v>
+        <v>-353.7087715551024</v>
       </c>
       <c r="O65">
-        <v>-539.6885822141227</v>
+        <v>-77.81592974212253</v>
       </c>
       <c r="P65">
-        <v>-1913.44133694098</v>
+        <v>-275.8928418129799</v>
       </c>
       <c r="Q65">
-        <v>-414.8413369409805</v>
+        <v>1222.70715818702</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1090457950993922</v>
+        <v>0.105365226584402</v>
       </c>
       <c r="T65">
-        <v>1.459702856266986</v>
+        <v>1.375640336822217</v>
       </c>
       <c r="U65">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V65">
-        <v>0.1042133504642513</v>
+        <v>0.1896226056508046</v>
       </c>
       <c r="W65">
-        <v>0.1933107589698146</v>
+        <v>0.09611075896981458</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y65">
-        <v>0.4736970475647786</v>
+        <v>0.8619209347763845</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1638327223377583</v>
+        <v>0.1002629119872119</v>
       </c>
       <c r="C66">
-        <v>-14182.0815619962</v>
+        <v>-6997.443428173026</v>
       </c>
       <c r="D66">
-        <v>6162.8424380038</v>
+        <v>13347.48057182698</v>
       </c>
       <c r="E66">
         <v>6570.624000000003</v>
@@ -6705,45 +6705,45 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M66">
-        <v>4735.045619200001</v>
+        <v>2602.300326400001</v>
       </c>
       <c r="N66">
-        <v>-2527.115006955103</v>
+        <v>-394.3697141551024</v>
       </c>
       <c r="O66">
-        <v>-555.9653015301226</v>
+        <v>-86.76133711412254</v>
       </c>
       <c r="P66">
-        <v>-1971.14970542498</v>
+        <v>-307.6083770409799</v>
       </c>
       <c r="Q66">
-        <v>-472.5497054249802</v>
+        <v>1190.99162295902</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.110802622741042</v>
+        <v>0.1070198162117465</v>
       </c>
       <c r="T66">
-        <v>1.500250157829958</v>
+        <v>1.413852568400611</v>
       </c>
       <c r="U66">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V66">
-        <v>0.1025850168632474</v>
+        <v>0.1866597524375108</v>
       </c>
       <c r="W66">
-        <v>0.1936621533609112</v>
+        <v>0.09646215336091123</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.466295531196579</v>
+        <v>0.8484534201705035</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1655327223377583</v>
+        <v>0.1009909119872119</v>
       </c>
       <c r="C67">
-        <v>-14612.42439056945</v>
+        <v>-7516.345404634907</v>
       </c>
       <c r="D67">
-        <v>6075.340609430557</v>
+        <v>13171.4195953651</v>
       </c>
       <c r="E67">
         <v>6913.465000000004</v>
@@ -6787,45 +6787,45 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M67">
-        <v>4809.030707000002</v>
+        <v>2642.961269000001</v>
       </c>
       <c r="N67">
-        <v>-2601.100094755103</v>
+        <v>-435.0306567551024</v>
       </c>
       <c r="O67">
-        <v>-572.2420208461227</v>
+        <v>-95.70674448612253</v>
       </c>
       <c r="P67">
-        <v>-2028.858073908981</v>
+        <v>-339.3239122689799</v>
       </c>
       <c r="Q67">
-        <v>-530.2580739089808</v>
+        <v>1159.27608773102</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1126598405336432</v>
+        <v>0.1087689538177964</v>
       </c>
       <c r="T67">
-        <v>1.543114448053671</v>
+        <v>1.454248356069201</v>
       </c>
       <c r="U67">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V67">
-        <v>0.101006785834582</v>
+        <v>0.1837880639384722</v>
       </c>
       <c r="W67">
-        <v>0.1940027356168972</v>
+        <v>0.09680273561689721</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y67">
-        <v>0.4591217537935546</v>
+        <v>0.8354002906294189</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1672327223377583</v>
+        <v>0.1017189119872119</v>
       </c>
       <c r="C68">
-        <v>-15040.31725169223</v>
+        <v>-8030.663157752324</v>
       </c>
       <c r="D68">
-        <v>5990.288748307777</v>
+        <v>12999.94284224768</v>
       </c>
       <c r="E68">
         <v>7256.306000000004</v>
@@ -6869,45 +6869,45 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M68">
-        <v>4883.015794800001</v>
+        <v>2683.622211600001</v>
       </c>
       <c r="N68">
-        <v>-2675.085182555103</v>
+        <v>-475.6915993551024</v>
       </c>
       <c r="O68">
-        <v>-588.5187401621226</v>
+        <v>-104.6521518581225</v>
       </c>
       <c r="P68">
-        <v>-2086.56644239298</v>
+        <v>-371.0394474969799</v>
       </c>
       <c r="Q68">
-        <v>-587.9664423929803</v>
+        <v>1127.56055250302</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1146263064316915</v>
+        <v>0.110620981871261</v>
       </c>
       <c r="T68">
-        <v>1.588500167114073</v>
+        <v>1.497020366541824</v>
       </c>
       <c r="U68">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V68">
-        <v>0.09947637998860349</v>
+        <v>0.1810033963030408</v>
       </c>
       <c r="W68">
-        <v>0.1943329971984594</v>
+        <v>0.09713299719845937</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y68">
-        <v>0.4521653635845614</v>
+        <v>0.8227427104683671</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1689327223377583</v>
+        <v>0.1024469119872119</v>
       </c>
       <c r="C69">
-        <v>-15465.86161988537</v>
+        <v>-8540.573430500906</v>
       </c>
       <c r="D69">
-        <v>5907.585380114637</v>
+        <v>12832.8735694991</v>
       </c>
       <c r="E69">
         <v>7599.147000000004</v>
@@ -6951,45 +6951,45 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M69">
-        <v>4957.000882600001</v>
+        <v>2724.283154200001</v>
       </c>
       <c r="N69">
-        <v>-2749.070270355103</v>
+        <v>-516.3525419551024</v>
       </c>
       <c r="O69">
-        <v>-604.7954594781227</v>
+        <v>-113.5975592301225</v>
       </c>
       <c r="P69">
-        <v>-2144.27481087698</v>
+        <v>-402.7549827249799</v>
       </c>
       <c r="Q69">
-        <v>-645.6748108769802</v>
+        <v>1095.84501727502</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1167119520811367</v>
+        <v>0.112585254049178</v>
       </c>
       <c r="T69">
-        <v>1.6366365358145</v>
+        <v>1.542384620073394</v>
       </c>
       <c r="U69">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V69">
-        <v>0.09799165789922135</v>
+        <v>0.1783018530746372</v>
       </c>
       <c r="W69">
-        <v>0.194653400225348</v>
+        <v>0.09745340022534804</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y69">
-        <v>0.4454166268146426</v>
+        <v>0.810462968521078</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1706327223377583</v>
+        <v>0.160294922948553</v>
       </c>
       <c r="C70">
-        <v>-15889.15344205859</v>
+        <v>-15367.1622840844</v>
       </c>
       <c r="D70">
-        <v>5827.134557941412</v>
+        <v>6349.125715915604</v>
       </c>
       <c r="E70">
         <v>7941.988000000005</v>
@@ -7033,37 +7033,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M70">
-        <v>5030.985970400002</v>
+        <v>4681.288150400002</v>
       </c>
       <c r="N70">
-        <v>-2823.055358155103</v>
+        <v>-2473.357538155103</v>
       </c>
       <c r="O70">
-        <v>-621.0721787941228</v>
+        <v>-544.1386583941227</v>
       </c>
       <c r="P70">
-        <v>-2201.983179360981</v>
+        <v>-1929.218879760981</v>
       </c>
       <c r="Q70">
-        <v>-703.3831793609806</v>
+        <v>-430.6188797609807</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1189279505836722</v>
+        <v>0.1184973274924055</v>
       </c>
       <c r="T70">
-        <v>1.687781427558703</v>
+        <v>1.678922112988581</v>
       </c>
       <c r="U70">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.09655060410658574</v>
+        <v>0.1037630496324761</v>
       </c>
       <c r="W70">
-        <v>0.1949643796337988</v>
+        <v>0.1799643796337988</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4388663823026624</v>
+        <v>0.4716502256021642</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1723327223377583</v>
+        <v>0.161844922948553</v>
       </c>
       <c r="C71">
-        <v>-16310.28350883499</v>
+        <v>-15794.80789776002</v>
       </c>
       <c r="D71">
-        <v>5748.845491165011</v>
+        <v>6264.321102239984</v>
       </c>
       <c r="E71">
         <v>8284.829000000005</v>
@@ -7115,37 +7115,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M71">
-        <v>5104.971058200002</v>
+        <v>4750.130623200002</v>
       </c>
       <c r="N71">
-        <v>-2897.040445955103</v>
+        <v>-2542.200010955103</v>
       </c>
       <c r="O71">
-        <v>-637.3488981101227</v>
+        <v>-559.2840024101228</v>
       </c>
       <c r="P71">
-        <v>-2259.691547844981</v>
+        <v>-1982.91600854498</v>
       </c>
       <c r="Q71">
-        <v>-761.0915478449806</v>
+        <v>-484.3160085449804</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1212869167315326</v>
+        <v>0.1208424025728057</v>
       </c>
       <c r="T71">
-        <v>1.742225989738016</v>
+        <v>1.733080890826922</v>
       </c>
       <c r="U71">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.095151319989099</v>
+        <v>0.102259237318962</v>
       </c>
       <c r="W71">
-        <v>0.1952663451463525</v>
+        <v>0.1802663451463525</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4325059999504499</v>
+        <v>0.4648147150861908</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1740327223377583</v>
+        <v>0.163394922948553</v>
       </c>
       <c r="C72">
-        <v>-16729.33779633925</v>
+        <v>-16220.21791915153</v>
       </c>
       <c r="D72">
-        <v>5672.632203660759</v>
+        <v>6181.752080848476</v>
       </c>
       <c r="E72">
         <v>8627.670000000006</v>
@@ -7197,37 +7197,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M72">
-        <v>5178.956146000002</v>
+        <v>4818.973096000002</v>
       </c>
       <c r="N72">
-        <v>-2971.025533755104</v>
+        <v>-2611.042483755103</v>
       </c>
       <c r="O72">
-        <v>-653.6256174261229</v>
+        <v>-574.4293464261227</v>
       </c>
       <c r="P72">
-        <v>-2317.399916328981</v>
+        <v>-2036.61313732898</v>
       </c>
       <c r="Q72">
-        <v>-818.799916328981</v>
+        <v>-538.0131373289805</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1238031472892503</v>
+        <v>0.1233438159918992</v>
       </c>
       <c r="T72">
-        <v>1.80030018939595</v>
+        <v>1.790850253854486</v>
       </c>
       <c r="U72">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.09379201541782614</v>
+        <v>0.1007983910715482</v>
       </c>
       <c r="W72">
-        <v>0.1955596830728331</v>
+        <v>0.1805596830728331</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4263273428083006</v>
+        <v>0.4581745048706737</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1757327223377583</v>
+        <v>0.1649449229485529</v>
       </c>
       <c r="C73">
-        <v>-17146.39778115474</v>
+        <v>-16643.47959917876</v>
       </c>
       <c r="D73">
-        <v>5598.413218845256</v>
+        <v>6101.331400821241</v>
       </c>
       <c r="E73">
         <v>8970.511000000002</v>
@@ -7279,37 +7279,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M73">
-        <v>5252.941233800001</v>
+        <v>4887.815568800001</v>
       </c>
       <c r="N73">
-        <v>-3045.010621555103</v>
+        <v>-2679.884956555102</v>
       </c>
       <c r="O73">
-        <v>-669.9023367421227</v>
+        <v>-589.5746904421225</v>
       </c>
       <c r="P73">
-        <v>-2375.10828481298</v>
+        <v>-2090.31026611298</v>
       </c>
       <c r="Q73">
-        <v>-876.50828481298</v>
+        <v>-591.7102661129798</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1264929109888797</v>
+        <v>0.1260177406812751</v>
       </c>
       <c r="T73">
-        <v>1.862379506271672</v>
+        <v>1.85260371088395</v>
       </c>
       <c r="U73">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.09247100111616664</v>
+        <v>0.09937869542265319</v>
       </c>
       <c r="W73">
-        <v>0.1958447579591313</v>
+        <v>0.1808447579591312</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.420322732346212</v>
+        <v>0.4517213428302418</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1774327223377583</v>
+        <v>0.1664949229485529</v>
       </c>
       <c r="C74">
-        <v>-17561.54073087525</v>
+        <v>-17064.67570675279</v>
       </c>
       <c r="D74">
-        <v>5526.111269124756</v>
+        <v>6022.976293247214</v>
       </c>
       <c r="E74">
         <v>9313.352000000003</v>
@@ -7361,37 +7361,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M74">
-        <v>5326.926321600001</v>
+        <v>4956.658041600001</v>
       </c>
       <c r="N74">
-        <v>-3118.995709355102</v>
+        <v>-2748.727429355102</v>
       </c>
       <c r="O74">
-        <v>-686.1790560581226</v>
+        <v>-604.7200344581225</v>
       </c>
       <c r="P74">
-        <v>-2432.81665329698</v>
+        <v>-2144.00739489698</v>
       </c>
       <c r="Q74">
-        <v>-934.21665329698</v>
+        <v>-645.4073948969799</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.129374800667054</v>
+        <v>0.1288826599913206</v>
       </c>
       <c r="T74">
-        <v>1.928893060067089</v>
+        <v>1.918768129129806</v>
       </c>
       <c r="U74">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.09118668165621989</v>
+        <v>0.09799843576400524</v>
       </c>
       <c r="W74">
-        <v>0.1961219140985878</v>
+        <v>0.1811219140985877</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4144849166191813</v>
+        <v>0.4454474352909329</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1791327223377583</v>
+        <v>0.1680449229485529</v>
       </c>
       <c r="C75">
-        <v>-17974.83997242914</v>
+        <v>-17483.88481292324</v>
       </c>
       <c r="D75">
-        <v>5455.653027570864</v>
+        <v>5946.608187076767</v>
       </c>
       <c r="E75">
         <v>9656.193000000003</v>
@@ -7443,37 +7443,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M75">
-        <v>5400.911409400002</v>
+        <v>5025.500514400001</v>
       </c>
       <c r="N75">
-        <v>-3192.980797155103</v>
+        <v>-2817.569902155102</v>
       </c>
       <c r="O75">
-        <v>-702.4557753741227</v>
+        <v>-619.8653784741225</v>
       </c>
       <c r="P75">
-        <v>-2490.52502178098</v>
+        <v>-2197.70452368098</v>
       </c>
       <c r="Q75">
-        <v>-991.9250217809804</v>
+        <v>-699.10452368098</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1324701636547226</v>
+        <v>0.1319597955465547</v>
       </c>
       <c r="T75">
-        <v>2.000333543773277</v>
+        <v>1.989833615393872</v>
       </c>
       <c r="U75">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.08993754903079221</v>
+        <v>0.09665599143847092</v>
       </c>
       <c r="W75">
-        <v>0.1963914769191551</v>
+        <v>0.1813914769191551</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.4088070410490554</v>
+        <v>0.4393454156294132</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1808327223377583</v>
+        <v>0.169594922948553</v>
       </c>
       <c r="C76">
-        <v>-18386.36514013533</v>
+        <v>-17901.18155367926</v>
       </c>
       <c r="D76">
-        <v>5386.968859864667</v>
+        <v>5872.152446320743</v>
       </c>
       <c r="E76">
         <v>9999.034000000003</v>
@@ -7525,37 +7525,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M76">
-        <v>5474.896497200001</v>
+        <v>5094.342987200001</v>
       </c>
       <c r="N76">
-        <v>-3266.965884955103</v>
+        <v>-2886.412374955102</v>
       </c>
       <c r="O76">
-        <v>-718.7324946901226</v>
+        <v>-635.0107224901225</v>
       </c>
       <c r="P76">
-        <v>-2548.23339026498</v>
+        <v>-2251.40165246498</v>
       </c>
       <c r="Q76">
-        <v>-1049.63339026498</v>
+        <v>-752.8016524649797</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1358036314875966</v>
+        <v>0.1352736338368068</v>
       </c>
       <c r="T76">
-        <v>2.077269449303019</v>
+        <v>2.066365677524406</v>
       </c>
       <c r="U76">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.08872217674659232</v>
+        <v>0.09534982939200509</v>
       </c>
       <c r="W76">
-        <v>0.1966537542580854</v>
+        <v>0.1816537542580854</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4032826215754196</v>
+        <v>0.433408315418205</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1825327223377583</v>
+        <v>0.1711449229485529</v>
       </c>
       <c r="C77">
-        <v>-18796.18240525458</v>
+        <v>-18316.63687325192</v>
       </c>
       <c r="D77">
-        <v>5319.992594745422</v>
+        <v>5799.538126748084</v>
       </c>
       <c r="E77">
         <v>10341.875</v>
@@ -7607,37 +7607,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M77">
-        <v>5548.881585000001</v>
+        <v>5163.185460000001</v>
       </c>
       <c r="N77">
-        <v>-3340.950972755103</v>
+        <v>-2955.254847755102</v>
       </c>
       <c r="O77">
-        <v>-735.0092140061225</v>
+        <v>-650.1560665061224</v>
       </c>
       <c r="P77">
-        <v>-2605.94175874898</v>
+        <v>-2305.09878124898</v>
       </c>
       <c r="Q77">
-        <v>-1107.34175874898</v>
+        <v>-806.4987812489799</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1394037767471004</v>
+        <v>0.138852579190279</v>
       </c>
       <c r="T77">
-        <v>2.160360227275139</v>
+        <v>2.149020304625382</v>
       </c>
       <c r="U77">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.08753921438997109</v>
+        <v>0.09407849833344503</v>
       </c>
       <c r="W77">
-        <v>0.1969090375346443</v>
+        <v>0.1819090375346442</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.397905519954414</v>
+        <v>0.4276295378792956</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1842327223377583</v>
+        <v>0.1726949229485529</v>
       </c>
       <c r="C78">
-        <v>-19204.35468862703</v>
+        <v>-18730.31824958521</v>
       </c>
       <c r="D78">
-        <v>5254.661311372977</v>
+        <v>5728.697750414793</v>
       </c>
       <c r="E78">
         <v>10684.716</v>
@@ -7689,37 +7689,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M78">
-        <v>5622.866672800002</v>
+        <v>5232.027932800002</v>
       </c>
       <c r="N78">
-        <v>-3414.936060555103</v>
+        <v>-3024.097320555103</v>
       </c>
       <c r="O78">
-        <v>-751.2859333221227</v>
+        <v>-665.3014105221226</v>
       </c>
       <c r="P78">
-        <v>-2663.650127232981</v>
+        <v>-2358.79591003298</v>
       </c>
       <c r="Q78">
-        <v>-1165.050127232981</v>
+        <v>-860.1959100329805</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1433039341115629</v>
+        <v>0.142729769989874</v>
       </c>
       <c r="T78">
-        <v>2.250375236744937</v>
+        <v>2.238562817318107</v>
       </c>
       <c r="U78">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.08638738262168198</v>
+        <v>0.09284062335537337</v>
       </c>
       <c r="W78">
-        <v>0.197157602830241</v>
+        <v>0.182157602830241</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3926699210076454</v>
+        <v>0.4220028334335153</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.1859327223377583</v>
+        <v>0.174244922948553</v>
       </c>
       <c r="C79">
-        <v>-19610.94185783227</v>
+        <v>-19142.2899034819</v>
       </c>
       <c r="D79">
-        <v>5190.915142167734</v>
+        <v>5659.567096518105</v>
       </c>
       <c r="E79">
         <v>11027.557</v>
@@ -7771,37 +7771,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M79">
-        <v>5696.851760600001</v>
+        <v>5300.870405600002</v>
       </c>
       <c r="N79">
-        <v>-3488.921148355103</v>
+        <v>-3092.939793355103</v>
       </c>
       <c r="O79">
-        <v>-767.5626526381227</v>
+        <v>-680.4467545381227</v>
       </c>
       <c r="P79">
-        <v>-2721.358495716981</v>
+        <v>-2412.493038816981</v>
       </c>
       <c r="Q79">
-        <v>-1222.758495716981</v>
+        <v>-913.8930388169806</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1475432355946744</v>
+        <v>0.1469441078155207</v>
       </c>
       <c r="T79">
-        <v>2.348217638342543</v>
+        <v>2.335891635462373</v>
       </c>
       <c r="U79">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.08526546856166015</v>
+        <v>0.09163490097413475</v>
       </c>
       <c r="W79">
-        <v>0.1973997118843938</v>
+        <v>0.1823997118843937</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3875703116439098</v>
+        <v>0.416522277155158</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.1876327223377583</v>
+        <v>0.1757949229485529</v>
       </c>
       <c r="C80">
-        <v>-20016.00091017051</v>
+        <v>-19552.61299278684</v>
       </c>
       <c r="D80">
-        <v>5128.697089829498</v>
+        <v>5592.085007213164</v>
       </c>
       <c r="E80">
         <v>11370.398</v>
@@ -7853,37 +7853,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M80">
-        <v>5770.836848400002</v>
+        <v>5369.712878400002</v>
       </c>
       <c r="N80">
-        <v>-3562.906236155104</v>
+        <v>-3161.782266155103</v>
       </c>
       <c r="O80">
-        <v>-783.8393719541228</v>
+        <v>-695.5920985541227</v>
       </c>
       <c r="P80">
-        <v>-2779.066864200981</v>
+        <v>-2466.19016760098</v>
       </c>
       <c r="Q80">
-        <v>-1280.466864200981</v>
+        <v>-967.5901676009803</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.152167928121705</v>
+        <v>0.1515415672616807</v>
       </c>
       <c r="T80">
-        <v>2.454954803721749</v>
+        <v>2.442068527983389</v>
       </c>
       <c r="U80">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.08417232152881834</v>
+        <v>0.09046009455138944</v>
       </c>
       <c r="W80">
-        <v>0.197635613014081</v>
+        <v>0.182635613014081</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3826014614946288</v>
+        <v>0.4111822479608611</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.1893327223377583</v>
+        <v>0.177344922948553</v>
       </c>
       <c r="C81">
-        <v>-20419.58614264032</v>
+        <v>-19961.34579284187</v>
       </c>
       <c r="D81">
-        <v>5067.952857359684</v>
+        <v>5526.193207158132</v>
       </c>
       <c r="E81">
         <v>11713.23900000001</v>
@@ -7935,37 +7935,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M81">
-        <v>5844.821936200002</v>
+        <v>5438.555351200001</v>
       </c>
       <c r="N81">
-        <v>-3636.891323955103</v>
+        <v>-3230.624738955103</v>
       </c>
       <c r="O81">
-        <v>-800.1160912701228</v>
+        <v>-710.7374425701227</v>
       </c>
       <c r="P81">
-        <v>-2836.77523268498</v>
+        <v>-2519.88729638498</v>
       </c>
       <c r="Q81">
-        <v>-1338.175232684981</v>
+        <v>-1021.28729638498</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1572330675560719</v>
+        <v>0.1565768799884275</v>
       </c>
       <c r="T81">
-        <v>2.571857413422785</v>
+        <v>2.558357505506408</v>
       </c>
       <c r="U81">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.08310684910440291</v>
+        <v>0.08931503006339717</v>
       </c>
       <c r="W81">
-        <v>0.1978655419632699</v>
+        <v>0.1828655419632699</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3777584050200132</v>
+        <v>0.405977409379078</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.1910327223377583</v>
+        <v>0.178894922948553</v>
       </c>
       <c r="C82">
-        <v>-20821.74930997859</v>
+        <v>-20368.54386433142</v>
       </c>
       <c r="D82">
-        <v>5008.630690021422</v>
+        <v>5461.836135668589</v>
       </c>
       <c r="E82">
         <v>12056.08000000001</v>
@@ -8017,37 +8017,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M82">
-        <v>5918.807024000002</v>
+        <v>5507.397824000001</v>
       </c>
       <c r="N82">
-        <v>-3710.876411755103</v>
+        <v>-3299.467211755103</v>
       </c>
       <c r="O82">
-        <v>-816.3928105861227</v>
+        <v>-725.8827865861227</v>
       </c>
       <c r="P82">
-        <v>-2894.48360116898</v>
+        <v>-2573.58442516898</v>
       </c>
       <c r="Q82">
-        <v>-1395.88360116898</v>
+        <v>-1074.984425168981</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.1628047209338756</v>
+        <v>0.1621157239878488</v>
       </c>
       <c r="T82">
-        <v>2.700450284093925</v>
+        <v>2.686275380781729</v>
       </c>
       <c r="U82">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.08206801349059789</v>
+        <v>0.08819859218760469</v>
       </c>
       <c r="W82">
-        <v>0.198089722688729</v>
+        <v>0.183089722688729</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3730364249572631</v>
+        <v>0.4009026917618396</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1927327223377583</v>
+        <v>0.180444922948553</v>
       </c>
       <c r="C83">
-        <v>-21222.53977172927</v>
+        <v>-20774.2602095349</v>
       </c>
       <c r="D83">
-        <v>4950.681228270737</v>
+        <v>5398.96079046511</v>
       </c>
       <c r="E83">
         <v>12398.92100000001</v>
@@ -8099,37 +8099,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M83">
-        <v>5992.792111800002</v>
+        <v>5576.240296800001</v>
       </c>
       <c r="N83">
-        <v>-3784.861499555104</v>
+        <v>-3368.309684555103</v>
       </c>
       <c r="O83">
-        <v>-832.6695299021228</v>
+        <v>-741.0281306021227</v>
       </c>
       <c r="P83">
-        <v>-2952.191969652981</v>
+        <v>-2627.28155395298</v>
       </c>
       <c r="Q83">
-        <v>-1453.591969652981</v>
+        <v>-1128.68155395298</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.1689628641409217</v>
+        <v>0.1682376041977356</v>
       </c>
       <c r="T83">
-        <v>2.842579246414658</v>
+        <v>2.827658295559714</v>
       </c>
       <c r="U83">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.0810548281388621</v>
+        <v>0.08710972067911575</v>
       </c>
       <c r="W83">
-        <v>0.1983083680876336</v>
+        <v>0.1833083680876336</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3684310369948277</v>
+        <v>0.3959532758141625</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1944327223377583</v>
+        <v>0.1819949229485529</v>
       </c>
       <c r="C84">
-        <v>-21622.00462921965</v>
+        <v>-21178.54541790955</v>
       </c>
       <c r="D84">
-        <v>4894.057370780357</v>
+        <v>5337.516582090457</v>
       </c>
       <c r="E84">
         <v>12741.76200000001</v>
@@ -8181,37 +8181,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M84">
-        <v>6066.777199600002</v>
+        <v>5645.082769600001</v>
       </c>
       <c r="N84">
-        <v>-3858.846587355104</v>
+        <v>-3437.152157355103</v>
       </c>
       <c r="O84">
-        <v>-848.9462492181228</v>
+        <v>-756.1734746181227</v>
       </c>
       <c r="P84">
-        <v>-3009.900338136981</v>
+        <v>-2680.97868273698</v>
       </c>
       <c r="Q84">
-        <v>-1511.300338136981</v>
+        <v>-1182.37868273698</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.175805245482084</v>
+        <v>0.175039693319832</v>
       </c>
       <c r="T84">
-        <v>3.000500315659917</v>
+        <v>2.98475042309081</v>
       </c>
       <c r="U84">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.08006635462497355</v>
+        <v>0.08604740701229727</v>
       </c>
       <c r="W84">
-        <v>0.1985216806719307</v>
+        <v>0.1835216806719307</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3639379755680615</v>
+        <v>0.3911245773286239</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1961327223377583</v>
+        <v>0.183544922948553</v>
       </c>
       <c r="C85">
-        <v>-22020.18885324266</v>
+        <v>-21581.44780184404</v>
       </c>
       <c r="D85">
-        <v>4838.714146757351</v>
+        <v>5277.455198155963</v>
       </c>
       <c r="E85">
         <v>13084.60300000001</v>
@@ -8263,37 +8263,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M85">
-        <v>6140.762287400002</v>
+        <v>5713.925242400001</v>
       </c>
       <c r="N85">
-        <v>-3932.831675155103</v>
+        <v>-3505.994630155103</v>
       </c>
       <c r="O85">
-        <v>-865.2229685341227</v>
+        <v>-771.3188186341226</v>
       </c>
       <c r="P85">
-        <v>-3067.608706620981</v>
+        <v>-2734.67581152098</v>
       </c>
       <c r="Q85">
-        <v>-1569.008706620981</v>
+        <v>-1236.075811520981</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.183452612863383</v>
+        <v>0.1826420282209987</v>
       </c>
       <c r="T85">
-        <v>3.177000334228148</v>
+        <v>3.16032397739027</v>
       </c>
       <c r="U85">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.07910169974997387</v>
+        <v>0.08501069126516116</v>
       </c>
       <c r="W85">
-        <v>0.1987298531939557</v>
+        <v>0.1837298531939557</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3595531806816994</v>
+        <v>0.3864122330234598</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.1978327223377583</v>
+        <v>0.1850949229485529</v>
       </c>
       <c r="C86">
-        <v>-22417.13540317297</v>
+        <v>-21983.01352334852</v>
       </c>
       <c r="D86">
-        <v>4784.608596827036</v>
+        <v>5218.730476651483</v>
       </c>
       <c r="E86">
         <v>13427.444</v>
@@ -8345,37 +8345,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M86">
-        <v>6214.747375200001</v>
+        <v>5782.767715200001</v>
       </c>
       <c r="N86">
-        <v>-4006.816762955103</v>
+        <v>-3574.837102955102</v>
       </c>
       <c r="O86">
-        <v>-881.4996878501227</v>
+        <v>-786.4641626501225</v>
       </c>
       <c r="P86">
-        <v>-3125.31707510498</v>
+        <v>-2788.37294030498</v>
       </c>
       <c r="Q86">
-        <v>-1626.71707510498</v>
+        <v>-1289.77294030498</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.1920559011673444</v>
+        <v>0.191194654984811</v>
       </c>
       <c r="T86">
-        <v>3.375562855117405</v>
+        <v>3.357844225977159</v>
       </c>
       <c r="U86">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.07816001284818846</v>
+        <v>0.08399865922629021</v>
       </c>
       <c r="W86">
-        <v>0.1989330692273609</v>
+        <v>0.1839330692273609</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3552727856735839</v>
+        <v>0.3818120873922282</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.1995327223377583</v>
+        <v>0.1866449229485529</v>
       </c>
       <c r="C87">
-        <v>-22812.88533817989</v>
+        <v>-22383.28671237932</v>
       </c>
       <c r="D87">
-        <v>4731.699661820111</v>
+        <v>5161.298287620682</v>
       </c>
       <c r="E87">
         <v>13770.285</v>
@@ -8427,37 +8427,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M87">
-        <v>6288.732463000001</v>
+        <v>5851.610188000001</v>
       </c>
       <c r="N87">
-        <v>-4080.801850755103</v>
+        <v>-3643.679575755103</v>
       </c>
       <c r="O87">
-        <v>-897.7764071661226</v>
+        <v>-801.6095066661227</v>
       </c>
       <c r="P87">
-        <v>-3183.02544358898</v>
+        <v>-2842.07006908898</v>
       </c>
       <c r="Q87">
-        <v>-1684.42544358898</v>
+        <v>-1343.47006908898</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2018062945785007</v>
+        <v>0.2008876319837984</v>
       </c>
       <c r="T87">
-        <v>3.600600378791899</v>
+        <v>3.581700507708971</v>
       </c>
       <c r="U87">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.0772404832852686</v>
+        <v>0.08301043970598089</v>
       </c>
       <c r="W87">
-        <v>0.1991315037070391</v>
+        <v>0.184131503707039</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.35109310584213</v>
+        <v>0.3773201804817313</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2012327223377583</v>
+        <v>0.188194922948553</v>
       </c>
       <c r="C88">
-        <v>-23207.47792114204</v>
+        <v>-22782.30957743572</v>
       </c>
       <c r="D88">
-        <v>4679.948078857969</v>
+        <v>5105.116422564282</v>
       </c>
       <c r="E88">
         <v>14113.126</v>
@@ -8509,37 +8509,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M88">
-        <v>6362.717550800002</v>
+        <v>5920.452660800001</v>
       </c>
       <c r="N88">
-        <v>-4154.786938555104</v>
+        <v>-3712.522048555103</v>
       </c>
       <c r="O88">
-        <v>-914.0531264821228</v>
+        <v>-816.7548506821227</v>
       </c>
       <c r="P88">
-        <v>-3240.733812072981</v>
+        <v>-2895.76719787298</v>
       </c>
       <c r="Q88">
-        <v>-1742.133812072981</v>
+        <v>-1397.167197872981</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2129496013341079</v>
+        <v>0.2119653199826411</v>
       </c>
       <c r="T88">
-        <v>3.857786120134178</v>
+        <v>3.837536258259611</v>
       </c>
       <c r="U88">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.07634233813078872</v>
+        <v>0.08204520203498111</v>
       </c>
       <c r="W88">
-        <v>0.1993253234313758</v>
+        <v>0.1843253234313758</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3470106278672214</v>
+        <v>0.3729327365226415</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2029327223377583</v>
+        <v>0.1897449229485529</v>
       </c>
       <c r="C89">
-        <v>-23600.95071581659</v>
+        <v>-23180.12250901126</v>
       </c>
       <c r="D89">
-        <v>4629.316284183416</v>
+        <v>5050.14449098874</v>
       </c>
       <c r="E89">
         <v>14455.967</v>
@@ -8591,37 +8591,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M89">
-        <v>6436.702638600002</v>
+        <v>5989.295133600001</v>
       </c>
       <c r="N89">
-        <v>-4228.772026355104</v>
+        <v>-3781.364521355103</v>
       </c>
       <c r="O89">
-        <v>-930.3298457981228</v>
+        <v>-831.9001946981227</v>
       </c>
       <c r="P89">
-        <v>-3298.442180556981</v>
+        <v>-2949.46432665698</v>
       </c>
       <c r="Q89">
-        <v>-1799.842180556981</v>
+        <v>-1450.86432665698</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.2258072629751932</v>
+        <v>0.2247472676736136</v>
       </c>
       <c r="T89">
-        <v>4.154538898606038</v>
+        <v>4.132731355048812</v>
       </c>
       <c r="U89">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.07546483999135438</v>
+        <v>0.08110215373572846</v>
       </c>
       <c r="W89">
-        <v>0.1995146875298658</v>
+        <v>0.1845146875298657</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3430219999607016</v>
+        <v>0.3686461533442202</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2046327223377583</v>
+        <v>0.191294922948553</v>
       </c>
       <c r="C90">
-        <v>-23993.33967776851</v>
+        <v>-23576.76417643249</v>
       </c>
       <c r="D90">
-        <v>4579.768322231493</v>
+        <v>4996.343823567511</v>
       </c>
       <c r="E90">
         <v>14798.808</v>
@@ -8673,37 +8673,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M90">
-        <v>6510.687726400001</v>
+        <v>6058.137606400001</v>
       </c>
       <c r="N90">
-        <v>-4302.757114155103</v>
+        <v>-3850.206994155103</v>
       </c>
       <c r="O90">
-        <v>-946.6065651141228</v>
+        <v>-847.0455387141227</v>
       </c>
       <c r="P90">
-        <v>-3356.150549040981</v>
+        <v>-3003.16145544098</v>
       </c>
       <c r="Q90">
-        <v>-1857.550549040981</v>
+        <v>-1504.56145544098</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.2408078682231259</v>
+        <v>0.2396595399797481</v>
       </c>
       <c r="T90">
-        <v>4.500750473489874</v>
+        <v>4.477125634636214</v>
       </c>
       <c r="U90">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.07460728499145262</v>
+        <v>0.08018053835236791</v>
       </c>
       <c r="W90">
-        <v>0.1996997478988445</v>
+        <v>0.1846997478988445</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.339124022688421</v>
+        <v>0.3644569925107632</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2063327223377583</v>
+        <v>0.1928449229485529</v>
       </c>
       <c r="C91">
-        <v>-24384.67923952225</v>
+        <v>-23972.27161857303</v>
       </c>
       <c r="D91">
-        <v>4531.269760477757</v>
+        <v>4943.677381426975</v>
       </c>
       <c r="E91">
         <v>15141.649</v>
@@ -8755,37 +8755,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M91">
-        <v>6584.672814200002</v>
+        <v>6126.980079200001</v>
       </c>
       <c r="N91">
-        <v>-4376.742201955103</v>
+        <v>-3919.049466955103</v>
       </c>
       <c r="O91">
-        <v>-962.8832844301227</v>
+        <v>-862.1908827301227</v>
       </c>
       <c r="P91">
-        <v>-3413.85891752498</v>
+        <v>-3056.85858422498</v>
       </c>
       <c r="Q91">
-        <v>-1915.25891752498</v>
+        <v>-1558.25858422498</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.25853585624341</v>
+        <v>0.2572831345233615</v>
       </c>
       <c r="T91">
-        <v>4.909909607443499</v>
+        <v>4.884137055966779</v>
       </c>
       <c r="U91">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.07376900089042507</v>
+        <v>0.07927963342706042</v>
       </c>
       <c r="W91">
-        <v>0.1998806496078463</v>
+        <v>0.1848806496078463</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3353136404110231</v>
+        <v>0.3603619701230019</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2080327223377583</v>
+        <v>0.194394922948553</v>
       </c>
       <c r="C92">
-        <v>-24775.0023903597</v>
+        <v>-24366.68032889019</v>
       </c>
       <c r="D92">
-        <v>4483.787609640302</v>
+        <v>4892.109671109813</v>
       </c>
       <c r="E92">
         <v>15484.49000000001</v>
@@ -8837,37 +8837,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M92">
-        <v>6658.657902000002</v>
+        <v>6195.822552000001</v>
       </c>
       <c r="N92">
-        <v>-4450.727289755103</v>
+        <v>-3987.891939755103</v>
       </c>
       <c r="O92">
-        <v>-979.1600037461227</v>
+        <v>-877.3362267461226</v>
       </c>
       <c r="P92">
-        <v>-3471.56728600898</v>
+        <v>-3110.555713008981</v>
       </c>
       <c r="Q92">
-        <v>-1972.96728600898</v>
+        <v>-1611.955713008981</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.2798094418677511</v>
+        <v>0.2784314479756977</v>
       </c>
       <c r="T92">
-        <v>5.400900568187851</v>
+        <v>5.372550761563457</v>
       </c>
       <c r="U92">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.07294934532497589</v>
+        <v>0.07839874861120417</v>
       </c>
       <c r="W92">
-        <v>0.2000575312788702</v>
+        <v>0.1850575312788702</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3315879332953451</v>
+        <v>0.3563579482327462</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2097327223377583</v>
+        <v>0.195944922948553</v>
       </c>
       <c r="C93">
-        <v>-25164.34075115314</v>
+        <v>-24760.02433519443</v>
       </c>
       <c r="D93">
-        <v>4437.290248846868</v>
+        <v>4841.606664805574</v>
       </c>
       <c r="E93">
         <v>15827.33100000001</v>
@@ -8919,37 +8919,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M93">
-        <v>6732.642989800002</v>
+        <v>6264.665024800001</v>
       </c>
       <c r="N93">
-        <v>-4524.712377555104</v>
+        <v>-4056.734412555103</v>
       </c>
       <c r="O93">
-        <v>-995.436723062123</v>
+        <v>-892.4815707621227</v>
       </c>
       <c r="P93">
-        <v>-3529.275654492982</v>
+        <v>-3164.25284179298</v>
       </c>
       <c r="Q93">
-        <v>-2030.675654492982</v>
+        <v>-1665.65284179298</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.305810490964168</v>
+        <v>0.3042793866396641</v>
       </c>
       <c r="T93">
-        <v>6.001000631319834</v>
+        <v>5.96950084618162</v>
       </c>
       <c r="U93">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.07214770416755857</v>
+        <v>0.07753722390119094</v>
       </c>
       <c r="W93">
-        <v>0.2002305254406409</v>
+        <v>0.1852305254406409</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3279441098525389</v>
+        <v>0.3524419268235952</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2114327223377583</v>
+        <v>0.197494922948553</v>
       </c>
       <c r="C94">
-        <v>-25552.72464458972</v>
+        <v>-25152.33627452833</v>
       </c>
       <c r="D94">
-        <v>4391.747355410285</v>
+        <v>4792.135725471674</v>
       </c>
       <c r="E94">
         <v>16170.17200000001</v>
@@ -9001,37 +9001,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M94">
-        <v>6806.628077600002</v>
+        <v>6333.507497600001</v>
       </c>
       <c r="N94">
-        <v>-4598.697465355104</v>
+        <v>-4125.576885355104</v>
       </c>
       <c r="O94">
-        <v>-1011.713442378123</v>
+        <v>-907.6269147781228</v>
       </c>
       <c r="P94">
-        <v>-3586.984022976981</v>
+        <v>-3217.949970576981</v>
       </c>
       <c r="Q94">
-        <v>-2088.384022976981</v>
+        <v>-1719.349970576981</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.338311802334689</v>
+        <v>0.3365893099696222</v>
       </c>
       <c r="T94">
-        <v>6.751125710234815</v>
+        <v>6.715688451954324</v>
       </c>
       <c r="U94">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.07136348999182425</v>
+        <v>0.07669442798922148</v>
       </c>
       <c r="W94">
-        <v>0.2003997588597643</v>
+        <v>0.1853997588597643</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3243794999628374</v>
+        <v>0.348611036314643</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2131327223377583</v>
+        <v>0.199044922948553</v>
       </c>
       <c r="C95">
-        <v>-25940.18316111543</v>
+        <v>-25543.64746350141</v>
       </c>
       <c r="D95">
-        <v>4347.129838884573</v>
+        <v>4743.665536498595</v>
       </c>
       <c r="E95">
         <v>16513.01300000001</v>
@@ -9083,37 +9083,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M95">
-        <v>6880.613165400002</v>
+        <v>6402.349970400001</v>
       </c>
       <c r="N95">
-        <v>-4672.682553155104</v>
+        <v>-4194.419358155103</v>
       </c>
       <c r="O95">
-        <v>-1027.990161694123</v>
+        <v>-922.7722587941225</v>
       </c>
       <c r="P95">
-        <v>-3644.692391460981</v>
+        <v>-3271.64709936098</v>
       </c>
       <c r="Q95">
-        <v>-2146.092391460981</v>
+        <v>-1773.04709936098</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.3800992026682161</v>
+        <v>0.3781306399652826</v>
       </c>
       <c r="T95">
-        <v>7.715572240268362</v>
+        <v>7.675072516519228</v>
       </c>
       <c r="U95">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.07059614063707345</v>
+        <v>0.07586975672052017</v>
       </c>
       <c r="W95">
-        <v>0.2005653528505196</v>
+        <v>0.1855653528505196</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3208915483503338</v>
+        <v>0.344862530547819</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2148327223377583</v>
+        <v>0.200594922948553</v>
       </c>
       <c r="C96">
-        <v>-26326.7442208997</v>
+        <v>-25933.98796439923</v>
       </c>
       <c r="D96">
-        <v>4303.409779100308</v>
+        <v>4696.166035600776</v>
       </c>
       <c r="E96">
         <v>16855.85400000001</v>
@@ -9165,37 +9165,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M96">
-        <v>6954.598253200003</v>
+        <v>6471.192443200001</v>
       </c>
       <c r="N96">
-        <v>-4746.667640955104</v>
+        <v>-4263.261830955104</v>
       </c>
       <c r="O96">
-        <v>-1044.266881010123</v>
+        <v>-937.9176028101227</v>
       </c>
       <c r="P96">
-        <v>-3702.400759944981</v>
+        <v>-3325.344228144981</v>
       </c>
       <c r="Q96">
-        <v>-2203.800759944981</v>
+        <v>-1826.744228144981</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.4358157364462522</v>
+        <v>0.4335190799594964</v>
       </c>
       <c r="T96">
-        <v>9.001500946979757</v>
+        <v>8.954251269272435</v>
       </c>
       <c r="U96">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.06984511786433861</v>
+        <v>0.07506263164902528</v>
       </c>
       <c r="W96">
-        <v>0.2007274235648757</v>
+        <v>0.1857274235648757</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3174778084742665</v>
+        <v>0.3411937802228421</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2165327223377583</v>
+        <v>0.202144922948553</v>
       </c>
       <c r="C97">
-        <v>-26712.43463209809</v>
+        <v>-26323.38664736011</v>
       </c>
       <c r="D97">
-        <v>4260.56036790192</v>
+        <v>4649.608352639901</v>
       </c>
       <c r="E97">
         <v>17198.69500000001</v>
@@ -9247,37 +9247,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M97">
-        <v>7028.583341000002</v>
+        <v>6540.034916000001</v>
       </c>
       <c r="N97">
-        <v>-4820.652728755103</v>
+        <v>-4332.104303755103</v>
       </c>
       <c r="O97">
-        <v>-1060.543600326123</v>
+        <v>-953.0629468261226</v>
       </c>
       <c r="P97">
-        <v>-3760.109128428981</v>
+        <v>-3379.04135692898</v>
       </c>
       <c r="Q97">
-        <v>-2261.509128428981</v>
+        <v>-1880.44135692898</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.5138188837355028</v>
+        <v>0.511062895951396</v>
       </c>
       <c r="T97">
-        <v>10.80180113637571</v>
+        <v>10.74510152312693</v>
       </c>
       <c r="U97">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.06910990609734559</v>
+        <v>0.07427249868429869</v>
       </c>
       <c r="W97">
-        <v>0.2008860822641929</v>
+        <v>0.1858860822641928</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3141359368061164</v>
+        <v>0.3376022667468124</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2182327223377583</v>
+        <v>0.203694922948553</v>
       </c>
       <c r="C98">
-        <v>-27097.28014566857</v>
+        <v>-26711.87124888958</v>
       </c>
       <c r="D98">
-        <v>4218.555854331431</v>
+        <v>4603.964751110419</v>
       </c>
       <c r="E98">
         <v>17541.536</v>
@@ -9329,37 +9329,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M98">
-        <v>7102.568428800002</v>
+        <v>6608.877388800001</v>
       </c>
       <c r="N98">
-        <v>-4894.637816555103</v>
+        <v>-4400.946776555103</v>
       </c>
       <c r="O98">
-        <v>-1076.820319642123</v>
+        <v>-968.2082908421228</v>
       </c>
       <c r="P98">
-        <v>-3817.81749691298</v>
+        <v>-3432.738485712981</v>
       </c>
       <c r="Q98">
-        <v>-2319.217496912981</v>
+        <v>-1934.138485712981</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.630823604669377</v>
+        <v>0.6273786199392436</v>
       </c>
       <c r="T98">
-        <v>13.50225142046961</v>
+        <v>13.43137690390863</v>
       </c>
       <c r="U98">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.0683900112421649</v>
+        <v>0.07349882682300392</v>
       </c>
       <c r="W98">
-        <v>0.2010414355739408</v>
+        <v>0.1860414355739408</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.310863687464386</v>
+        <v>0.3340855764681996</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2199327223377583</v>
+        <v>0.2052449229485529</v>
       </c>
       <c r="C99">
-        <v>-27481.30550697692</v>
+        <v>-27099.46842696196</v>
       </c>
       <c r="D99">
-        <v>4177.371493023086</v>
+        <v>4559.208573038047</v>
       </c>
       <c r="E99">
         <v>17884.377</v>
@@ -9411,37 +9411,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M99">
-        <v>7176.553516600002</v>
+        <v>6677.719861600001</v>
       </c>
       <c r="N99">
-        <v>-4968.622904355103</v>
+        <v>-4469.789249355103</v>
       </c>
       <c r="O99">
-        <v>-1093.097038958123</v>
+        <v>-983.3536348581225</v>
       </c>
       <c r="P99">
-        <v>-3875.52586539698</v>
+        <v>-3486.43561449698</v>
       </c>
       <c r="Q99">
-        <v>-2376.92586539698</v>
+        <v>-1987.83561449698</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>0.8258314728925028</v>
+        <v>0.8212381599189915</v>
       </c>
       <c r="T99">
-        <v>18.00300189395948</v>
+        <v>17.90850253854484</v>
       </c>
       <c r="U99">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.06768495957987455</v>
+        <v>0.07274110695884924</v>
       </c>
       <c r="W99">
-        <v>0.2011935857226631</v>
+        <v>0.1861935857226631</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.307658907181248</v>
+        <v>0.3306413952674966</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2216327223377583</v>
+        <v>0.206794922948553</v>
       </c>
       <c r="C100">
-        <v>-27864.53450440835</v>
+        <v>-27486.20381293876</v>
       </c>
       <c r="D100">
-        <v>4136.983495591653</v>
+        <v>4515.314187061244</v>
       </c>
       <c r="E100">
         <v>18227.218</v>
@@ -9493,37 +9493,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M100">
-        <v>7250.538604400002</v>
+        <v>6746.562334400001</v>
       </c>
       <c r="N100">
-        <v>-5042.607992155103</v>
+        <v>-4538.631722155103</v>
       </c>
       <c r="O100">
-        <v>-1109.373758274123</v>
+        <v>-998.4989788741228</v>
       </c>
       <c r="P100">
-        <v>-3933.23423388098</v>
+        <v>-3540.132743280981</v>
       </c>
       <c r="Q100">
-        <v>-2434.63423388098</v>
+        <v>-2041.532743280981</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.215847209338754</v>
+        <v>1.208957239878487</v>
       </c>
       <c r="T100">
-        <v>27.00450284093922</v>
+        <v>26.86275380781726</v>
       </c>
       <c r="U100">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.06699429672701868</v>
+        <v>0.0719988507653916</v>
       </c>
       <c r="W100">
-        <v>0.2013426307663094</v>
+        <v>0.1863426307663094</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3045195305773577</v>
+        <v>0.3272675034790526</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2233327223377583</v>
+        <v>0.2083449229485529</v>
       </c>
       <c r="C101">
-        <v>-28246.9900151864</v>
+        <v>-27872.10206051677</v>
       </c>
       <c r="D101">
-        <v>4097.368984813604</v>
+        <v>4472.256939483234</v>
       </c>
       <c r="E101">
         <v>18570.059</v>
@@ -9575,37 +9575,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M101">
-        <v>7324.523692200002</v>
+        <v>6815.404807200001</v>
       </c>
       <c r="N101">
-        <v>-5116.593079955104</v>
+        <v>-4607.474194955103</v>
       </c>
       <c r="O101">
-        <v>-1125.650477590123</v>
+        <v>-1013.644322890123</v>
       </c>
       <c r="P101">
-        <v>-3990.942602364981</v>
+        <v>-3593.82987206498</v>
       </c>
       <c r="Q101">
-        <v>-2492.342602364981</v>
+        <v>-2095.22987206498</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>2.385894418677509</v>
+        <v>2.372114479756974</v>
       </c>
       <c r="T101">
-        <v>54.00900568187845</v>
+        <v>53.72550761563452</v>
       </c>
       <c r="U101">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V101">
-        <v>0.06631758665906899</v>
+        <v>0.07127158964654925</v>
       </c>
       <c r="W101">
-        <v>0.2014886647989729</v>
+        <v>0.1864886647989729</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.3014435757230408</v>
+        <v>0.3239617711206785</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/denmark/denmark_green_renewable_energy.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_green_renewable_energy.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07082917521137812</v>
+        <v>0.0707084510259131</v>
       </c>
       <c r="C2">
-        <v>30640.71201119123</v>
+        <v>30438.63811646817</v>
       </c>
       <c r="D2">
-        <v>29043.81201119123</v>
+        <v>29184.57911646817</v>
       </c>
       <c r="E2">
-        <v>-15371.2</v>
+        <v>-15028.359</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>342.8410000000001</v>
       </c>
       <c r="G2">
         <v>1596.9</v>
@@ -1457,28 +1457,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>17.2449023</v>
       </c>
       <c r="N2">
-        <v>2207.930612244898</v>
+        <v>2190.685709944898</v>
       </c>
       <c r="O2">
-        <v>485.7447346938777</v>
+        <v>481.9508561878777</v>
       </c>
       <c r="P2">
-        <v>1722.185877551021</v>
+        <v>1708.734853757021</v>
       </c>
       <c r="Q2">
-        <v>3220.78587755102</v>
+        <v>3207.334853757021</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07082917521137812</v>
+        <v>0.07102637477364959</v>
       </c>
       <c r="T2">
-        <v>0.5780409979533053</v>
+        <v>0.5825952603614223</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>128.0338139256897</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.0707084510259131</v>
+        <v>0.07058772684044805</v>
       </c>
       <c r="C3">
-        <v>30438.63811646817</v>
+        <v>30237.93538371044</v>
       </c>
       <c r="D3">
-        <v>29184.57911646817</v>
+        <v>29326.71738371044</v>
       </c>
       <c r="E3">
-        <v>-15028.359</v>
+        <v>-14685.518</v>
       </c>
       <c r="F3">
-        <v>342.8410000000001</v>
+        <v>685.6820000000001</v>
       </c>
       <c r="G3">
         <v>1596.9</v>
@@ -1539,28 +1539,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M3">
-        <v>17.2449023</v>
+        <v>34.48980460000001</v>
       </c>
       <c r="N3">
-        <v>2190.685709944898</v>
+        <v>2173.440807644899</v>
       </c>
       <c r="O3">
-        <v>481.9508561878777</v>
+        <v>478.1569776818777</v>
       </c>
       <c r="P3">
-        <v>1708.734853757021</v>
+        <v>1695.283829963021</v>
       </c>
       <c r="Q3">
-        <v>3207.334853757021</v>
+        <v>3193.883829963021</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07102637477364959</v>
+        <v>0.07122759881678373</v>
       </c>
       <c r="T3">
-        <v>0.5825952603614223</v>
+        <v>0.5872424669003171</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>128.0338139256897</v>
+        <v>64.01690696284484</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07058772684044805</v>
+        <v>0.07046700265498303</v>
       </c>
       <c r="C4">
-        <v>30237.93538371044</v>
+        <v>30038.62394496405</v>
       </c>
       <c r="D4">
-        <v>29326.71738371044</v>
+        <v>29470.24694496405</v>
       </c>
       <c r="E4">
-        <v>-14685.518</v>
+        <v>-14342.677</v>
       </c>
       <c r="F4">
-        <v>685.6820000000001</v>
+        <v>1028.523</v>
       </c>
       <c r="G4">
         <v>1596.9</v>
@@ -1621,28 +1621,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M4">
-        <v>34.48980460000001</v>
+        <v>51.73470690000001</v>
       </c>
       <c r="N4">
-        <v>2173.440807644899</v>
+        <v>2156.195905344898</v>
       </c>
       <c r="O4">
-        <v>478.1569776818777</v>
+        <v>474.3630991758776</v>
       </c>
       <c r="P4">
-        <v>1695.283829963021</v>
+        <v>1681.832806169021</v>
       </c>
       <c r="Q4">
-        <v>3193.883829963021</v>
+        <v>3180.43280616902</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07122759881678373</v>
+        <v>0.07143297180926085</v>
       </c>
       <c r="T4">
-        <v>0.5872424669003171</v>
+        <v>0.5919854921307356</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>64.01690696284484</v>
+        <v>42.67793797522989</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07046700265498303</v>
+        <v>0.07034627846951799</v>
       </c>
       <c r="C5">
-        <v>30038.62394496405</v>
+        <v>29840.72432833107</v>
       </c>
       <c r="D5">
-        <v>29470.24694496405</v>
+        <v>29615.18832833107</v>
       </c>
       <c r="E5">
-        <v>-14342.677</v>
+        <v>-13999.836</v>
       </c>
       <c r="F5">
-        <v>1028.523</v>
+        <v>1371.364</v>
       </c>
       <c r="G5">
         <v>1596.9</v>
@@ -1703,28 +1703,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M5">
-        <v>51.73470690000001</v>
+        <v>68.97960920000001</v>
       </c>
       <c r="N5">
-        <v>2156.195905344898</v>
+        <v>2138.951003044898</v>
       </c>
       <c r="O5">
-        <v>474.3630991758776</v>
+        <v>470.5692206698776</v>
       </c>
       <c r="P5">
-        <v>1681.832806169021</v>
+        <v>1668.381782375021</v>
       </c>
       <c r="Q5">
-        <v>3180.43280616902</v>
+        <v>3166.98178237502</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07143297180926085</v>
+        <v>0.07164262340574791</v>
       </c>
       <c r="T5">
-        <v>0.5919854921307356</v>
+        <v>0.5968273303867877</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>42.67793797522989</v>
+        <v>32.00845348142242</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07034627846951799</v>
+        <v>0.07022555428405296</v>
       </c>
       <c r="C6">
-        <v>29840.72432833107</v>
+        <v>29644.25746775708</v>
       </c>
       <c r="D6">
-        <v>29615.18832833107</v>
+        <v>29761.56246775708</v>
       </c>
       <c r="E6">
-        <v>-13999.836</v>
+        <v>-13656.995</v>
       </c>
       <c r="F6">
-        <v>1371.364</v>
+        <v>1714.205</v>
       </c>
       <c r="G6">
         <v>1596.9</v>
@@ -1785,28 +1785,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M6">
-        <v>68.97960920000001</v>
+        <v>86.22451150000002</v>
       </c>
       <c r="N6">
-        <v>2138.951003044898</v>
+        <v>2121.706100744898</v>
       </c>
       <c r="O6">
-        <v>470.5692206698776</v>
+        <v>466.7753421638776</v>
       </c>
       <c r="P6">
-        <v>1668.381782375021</v>
+        <v>1654.930758581021</v>
       </c>
       <c r="Q6">
-        <v>3166.98178237502</v>
+        <v>3153.530758581021</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07164262340574791</v>
+        <v>0.07185668872005575</v>
       </c>
       <c r="T6">
-        <v>0.5968273303867877</v>
+        <v>0.6017711020798094</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>32.00845348142242</v>
+        <v>25.60676278513793</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07022555428405296</v>
+        <v>0.07010483009858792</v>
       </c>
       <c r="C7">
-        <v>29644.25746775708</v>
+        <v>29449.24471311048</v>
       </c>
       <c r="D7">
-        <v>29761.56246775708</v>
+        <v>29909.39071311048</v>
       </c>
       <c r="E7">
-        <v>-13656.995</v>
+        <v>-13314.154</v>
       </c>
       <c r="F7">
-        <v>1714.205</v>
+        <v>2057.046000000001</v>
       </c>
       <c r="G7">
         <v>1596.9</v>
@@ -1867,28 +1867,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M7">
-        <v>86.22451150000002</v>
+        <v>103.4694138</v>
       </c>
       <c r="N7">
-        <v>2121.706100744898</v>
+        <v>2104.461198444898</v>
       </c>
       <c r="O7">
-        <v>466.7753421638776</v>
+        <v>462.9814636578777</v>
       </c>
       <c r="P7">
-        <v>1654.930758581021</v>
+        <v>1641.479734787021</v>
       </c>
       <c r="Q7">
-        <v>3153.530758581021</v>
+        <v>3140.079734787021</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07185668872005575</v>
+        <v>0.07207530861551907</v>
       </c>
       <c r="T7">
-        <v>0.6017711020798094</v>
+        <v>0.6068200604045976</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>25.60676278513793</v>
+        <v>21.33896898761494</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07010483009858792</v>
+        <v>0.0699841059131229</v>
       </c>
       <c r="C8">
-        <v>29449.24471311048</v>
+        <v>29255.70784056371</v>
       </c>
       <c r="D8">
-        <v>29909.39071311048</v>
+        <v>30058.69484056371</v>
       </c>
       <c r="E8">
-        <v>-13314.154</v>
+        <v>-12971.313</v>
       </c>
       <c r="F8">
-        <v>2057.046</v>
+        <v>2399.887</v>
       </c>
       <c r="G8">
         <v>1596.9</v>
@@ -1949,28 +1949,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M8">
-        <v>103.4694138</v>
+        <v>120.7143161</v>
       </c>
       <c r="N8">
-        <v>2104.461198444898</v>
+        <v>2087.216296144898</v>
       </c>
       <c r="O8">
-        <v>462.9814636578777</v>
+        <v>459.1875851518777</v>
       </c>
       <c r="P8">
-        <v>1641.479734787021</v>
+        <v>1628.028710993021</v>
       </c>
       <c r="Q8">
-        <v>3140.079734787021</v>
+        <v>3126.628710993021</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07207530861551907</v>
+        <v>0.07229863001411063</v>
       </c>
       <c r="T8">
-        <v>0.6068200604045976</v>
+        <v>0.6119775984783058</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>21.33896898761494</v>
+        <v>18.2905448465271</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0699841059131229</v>
+        <v>0.06986338172765787</v>
       </c>
       <c r="C9">
-        <v>29255.70784056371</v>
+        <v>29063.66906328697</v>
       </c>
       <c r="D9">
-        <v>30058.69484056371</v>
+        <v>30209.49706328697</v>
       </c>
       <c r="E9">
-        <v>-12971.313</v>
+        <v>-12628.472</v>
       </c>
       <c r="F9">
-        <v>2399.887000000001</v>
+        <v>2742.728000000001</v>
       </c>
       <c r="G9">
         <v>1596.9</v>
@@ -2031,28 +2031,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M9">
-        <v>120.7143161</v>
+        <v>137.9592184</v>
       </c>
       <c r="N9">
-        <v>2087.216296144898</v>
+        <v>2069.971393844899</v>
       </c>
       <c r="O9">
-        <v>459.1875851518777</v>
+        <v>455.3937066458777</v>
       </c>
       <c r="P9">
-        <v>1628.028710993021</v>
+        <v>1614.577687199021</v>
       </c>
       <c r="Q9">
-        <v>3126.628710993021</v>
+        <v>3113.177687199021</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07229863001411065</v>
+        <v>0.07252680622571507</v>
       </c>
       <c r="T9">
-        <v>0.6119775984783059</v>
+        <v>0.6172472569449208</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>18.29054484652709</v>
+        <v>16.00422674071121</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.06986338172765787</v>
+        <v>0.06974265754219285</v>
       </c>
       <c r="C10">
-        <v>29063.66906328697</v>
+        <v>28873.1510424653</v>
       </c>
       <c r="D10">
-        <v>30209.49706328697</v>
+        <v>30361.8200424653</v>
       </c>
       <c r="E10">
-        <v>-12628.472</v>
+        <v>-12285.631</v>
       </c>
       <c r="F10">
-        <v>2742.728000000001</v>
+        <v>3085.569</v>
       </c>
       <c r="G10">
         <v>1596.9</v>
@@ -2113,28 +2113,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M10">
-        <v>137.9592184</v>
+        <v>155.2041207</v>
       </c>
       <c r="N10">
-        <v>2069.971393844899</v>
+        <v>2052.726491544898</v>
       </c>
       <c r="O10">
-        <v>455.3937066458777</v>
+        <v>451.5998281398776</v>
       </c>
       <c r="P10">
-        <v>1614.577687199021</v>
+        <v>1601.126663405021</v>
       </c>
       <c r="Q10">
-        <v>3113.177687199021</v>
+        <v>3099.72666340502</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07252680622571507</v>
+        <v>0.07275999729911301</v>
       </c>
       <c r="T10">
-        <v>0.6172472569449208</v>
+        <v>0.6226327320811318</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>16.00422674071121</v>
+        <v>14.22597932507663</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.06974265754219285</v>
+        <v>0.06962193335672781</v>
       </c>
       <c r="C11">
-        <v>28873.1510424653</v>
+        <v>28684.1768986509</v>
       </c>
       <c r="D11">
-        <v>30361.8200424653</v>
+        <v>30515.6868986509</v>
       </c>
       <c r="E11">
-        <v>-12285.631</v>
+        <v>-11942.79</v>
       </c>
       <c r="F11">
-        <v>3085.569</v>
+        <v>3428.41</v>
       </c>
       <c r="G11">
         <v>1596.9</v>
@@ -2195,28 +2195,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M11">
-        <v>155.2041207</v>
+        <v>172.449023</v>
       </c>
       <c r="N11">
-        <v>2052.726491544898</v>
+        <v>2035.481589244898</v>
       </c>
       <c r="O11">
-        <v>451.5998281398776</v>
+        <v>447.8059496338776</v>
       </c>
       <c r="P11">
-        <v>1601.126663405021</v>
+        <v>1587.675639611021</v>
       </c>
       <c r="Q11">
-        <v>3099.72666340502</v>
+        <v>3086.275639611021</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07275999729911301</v>
+        <v>0.07299837039636423</v>
       </c>
       <c r="T11">
-        <v>0.6226327320811318</v>
+        <v>0.6281378844425918</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>14.22597932507663</v>
+        <v>12.80338139256897</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.06962193335672781</v>
+        <v>0.06950120917126276</v>
       </c>
       <c r="C12">
-        <v>28684.1768986509</v>
+        <v>28496.77022346218</v>
       </c>
       <c r="D12">
-        <v>30515.6868986509</v>
+        <v>30671.12122346217</v>
       </c>
       <c r="E12">
-        <v>-11942.79</v>
+        <v>-11599.949</v>
       </c>
       <c r="F12">
-        <v>3428.410000000001</v>
+        <v>3771.251000000001</v>
       </c>
       <c r="G12">
         <v>1596.9</v>
@@ -2277,28 +2277,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M12">
-        <v>172.449023</v>
+        <v>189.6939253</v>
       </c>
       <c r="N12">
-        <v>2035.481589244898</v>
+        <v>2018.236686944898</v>
       </c>
       <c r="O12">
-        <v>447.8059496338776</v>
+        <v>444.0120711278776</v>
       </c>
       <c r="P12">
-        <v>1587.675639611021</v>
+        <v>1574.224615817021</v>
       </c>
       <c r="Q12">
-        <v>3086.275639611021</v>
+        <v>3072.82461581702</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07299837039636423</v>
+        <v>0.07324210019243008</v>
       </c>
       <c r="T12">
-        <v>0.6281378844425918</v>
+        <v>0.6337667480930734</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>12.80338139256897</v>
+        <v>11.63943762960815</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.06950120917126276</v>
+        <v>0.06938048498579776</v>
       </c>
       <c r="C13">
-        <v>28496.77022346218</v>
+        <v>28310.9550916422</v>
       </c>
       <c r="D13">
-        <v>30671.12122346217</v>
+        <v>30828.1470916422</v>
       </c>
       <c r="E13">
-        <v>-11599.949</v>
+        <v>-11257.108</v>
       </c>
       <c r="F13">
-        <v>3771.251000000001</v>
+        <v>4114.092000000001</v>
       </c>
       <c r="G13">
         <v>1596.9</v>
@@ -2359,28 +2359,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M13">
-        <v>189.6939253</v>
+        <v>206.9388276000001</v>
       </c>
       <c r="N13">
-        <v>2018.236686944898</v>
+        <v>2000.991784644898</v>
       </c>
       <c r="O13">
-        <v>444.0120711278776</v>
+        <v>440.2181926218777</v>
       </c>
       <c r="P13">
-        <v>1574.224615817021</v>
+        <v>1560.773592023021</v>
       </c>
       <c r="Q13">
-        <v>3072.82461581702</v>
+        <v>3059.373592023021</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07324210019243008</v>
+        <v>0.07349136930204289</v>
       </c>
       <c r="T13">
-        <v>0.6337667480930734</v>
+        <v>0.6395235404628842</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.63943762960815</v>
+        <v>10.66948449380747</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.06938048498579776</v>
+        <v>0.06925976080033269</v>
       </c>
       <c r="C14">
-        <v>28310.9550916422</v>
+        <v>28126.75607348981</v>
       </c>
       <c r="D14">
-        <v>30828.1470916422</v>
+        <v>30986.78907348981</v>
       </c>
       <c r="E14">
-        <v>-11257.108</v>
+        <v>-10914.267</v>
       </c>
       <c r="F14">
-        <v>4114.092000000001</v>
+        <v>4456.933000000001</v>
       </c>
       <c r="G14">
         <v>1596.9</v>
@@ -2441,28 +2441,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M14">
-        <v>206.9388276000001</v>
+        <v>224.1837299000001</v>
       </c>
       <c r="N14">
-        <v>2000.991784644898</v>
+        <v>1983.746882344898</v>
       </c>
       <c r="O14">
-        <v>440.2181926218777</v>
+        <v>436.4243141158776</v>
       </c>
       <c r="P14">
-        <v>1560.773592023021</v>
+        <v>1547.322568229021</v>
       </c>
       <c r="Q14">
-        <v>3059.373592023021</v>
+        <v>3045.922568229021</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07349136930204289</v>
+        <v>0.0737463687360146</v>
       </c>
       <c r="T14">
-        <v>0.6395235404628842</v>
+        <v>0.6454126728871733</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>10.66948449380747</v>
+        <v>9.848754917360743</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06925976080033269</v>
+        <v>0.06913903661486769</v>
       </c>
       <c r="C15">
-        <v>28126.75607348981</v>
+        <v>27944.19824767575</v>
       </c>
       <c r="D15">
-        <v>30986.78907348981</v>
+        <v>31147.07224767575</v>
       </c>
       <c r="E15">
-        <v>-10914.267</v>
+        <v>-10571.426</v>
       </c>
       <c r="F15">
-        <v>4456.933000000001</v>
+        <v>4799.774000000001</v>
       </c>
       <c r="G15">
         <v>1596.9</v>
@@ -2523,28 +2523,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M15">
-        <v>224.1837299000001</v>
+        <v>241.4286322000001</v>
       </c>
       <c r="N15">
-        <v>1983.746882344898</v>
+        <v>1966.501980044898</v>
       </c>
       <c r="O15">
-        <v>436.4243141158776</v>
+        <v>432.6304356098776</v>
       </c>
       <c r="P15">
-        <v>1547.322568229021</v>
+        <v>1533.871544435021</v>
       </c>
       <c r="Q15">
-        <v>3045.922568229021</v>
+        <v>3032.47154443502</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.0737463687360146</v>
+        <v>0.07400729838938103</v>
       </c>
       <c r="T15">
-        <v>0.6454126728871733</v>
+        <v>0.6514387618794693</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>9.848754917360743</v>
+        <v>9.145272423263547</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06913903661486769</v>
+        <v>0.06919381242940265</v>
       </c>
       <c r="C16">
-        <v>27944.19824767575</v>
+        <v>27528.42743950984</v>
       </c>
       <c r="D16">
-        <v>31147.07224767575</v>
+        <v>31074.14243950984</v>
       </c>
       <c r="E16">
-        <v>-10571.426</v>
+        <v>-10228.585</v>
       </c>
       <c r="F16">
-        <v>4799.774000000001</v>
+        <v>5142.615000000002</v>
       </c>
       <c r="G16">
         <v>1596.9</v>
@@ -2605,45 +2605,45 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M16">
-        <v>241.4286322000001</v>
+        <v>266.3874570000001</v>
       </c>
       <c r="N16">
-        <v>1966.501980044898</v>
+        <v>1941.543155244898</v>
       </c>
       <c r="O16">
-        <v>432.6304356098776</v>
+        <v>427.1394941538776</v>
       </c>
       <c r="P16">
-        <v>1533.871544435021</v>
+        <v>1514.403661091021</v>
       </c>
       <c r="Q16">
-        <v>3032.47154443502</v>
+        <v>3013.003661091021</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07400729838938103</v>
+        <v>0.07427436756400312</v>
       </c>
       <c r="T16">
-        <v>0.6514387618794693</v>
+        <v>0.6576066412009957</v>
       </c>
       <c r="U16">
-        <v>0.0503</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V16">
         <v>0.22</v>
       </c>
       <c r="W16">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>9.145272423263547</v>
+        <v>8.288418070092909</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06919381242940265</v>
+        <v>0.06908478824393763</v>
       </c>
       <c r="C17">
-        <v>27528.42743950984</v>
+        <v>27331.08198935121</v>
       </c>
       <c r="D17">
-        <v>31074.14243950984</v>
+        <v>31219.63798935121</v>
       </c>
       <c r="E17">
-        <v>-10228.585</v>
+        <v>-9885.743999999999</v>
       </c>
       <c r="F17">
-        <v>5142.615000000001</v>
+        <v>5485.456000000001</v>
       </c>
       <c r="G17">
         <v>1596.9</v>
@@ -2687,28 +2687,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M17">
-        <v>266.387457</v>
+        <v>284.1466208000001</v>
       </c>
       <c r="N17">
-        <v>1941.543155244898</v>
+        <v>1923.783991444898</v>
       </c>
       <c r="O17">
-        <v>427.1394941538776</v>
+        <v>423.2324781178776</v>
       </c>
       <c r="P17">
-        <v>1514.403661091021</v>
+        <v>1500.551513327021</v>
       </c>
       <c r="Q17">
-        <v>3013.003661091021</v>
+        <v>2999.15151332702</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07427436756400312</v>
+        <v>0.07454779552849716</v>
       </c>
       <c r="T17">
-        <v>0.6576066412009957</v>
+        <v>0.6639213747920821</v>
       </c>
       <c r="U17">
         <v>0.05180000000000001</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.288418070092909</v>
+        <v>7.770391940712101</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06908478824393763</v>
+        <v>0.06897576405847257</v>
       </c>
       <c r="C18">
-        <v>27331.08198935121</v>
+        <v>27135.10542901825</v>
       </c>
       <c r="D18">
-        <v>31219.63798935121</v>
+        <v>31366.50242901825</v>
       </c>
       <c r="E18">
-        <v>-9885.743999999999</v>
+        <v>-9542.902999999998</v>
       </c>
       <c r="F18">
-        <v>5485.456000000001</v>
+        <v>5828.297000000001</v>
       </c>
       <c r="G18">
         <v>1596.9</v>
@@ -2769,28 +2769,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M18">
-        <v>284.1466208000001</v>
+        <v>301.9057846000001</v>
       </c>
       <c r="N18">
-        <v>1923.783991444898</v>
+        <v>1906.024827644898</v>
       </c>
       <c r="O18">
-        <v>423.2324781178776</v>
+        <v>419.3254620818776</v>
       </c>
       <c r="P18">
-        <v>1500.551513327021</v>
+        <v>1486.699365563021</v>
       </c>
       <c r="Q18">
-        <v>2999.15151332702</v>
+        <v>2985.299365563021</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07454779552849716</v>
+        <v>0.07482781211864166</v>
       </c>
       <c r="T18">
-        <v>0.6639213747920821</v>
+        <v>0.6703882706383756</v>
       </c>
       <c r="U18">
         <v>0.05180000000000001</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.770391940712101</v>
+        <v>7.313310061846684</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06897576405847257</v>
+        <v>0.06886673987300754</v>
       </c>
       <c r="C19">
-        <v>27135.10542901825</v>
+        <v>26940.51716854874</v>
       </c>
       <c r="D19">
-        <v>31366.50242901825</v>
+        <v>31514.75516854874</v>
       </c>
       <c r="E19">
-        <v>-9542.902999999998</v>
+        <v>-9200.061999999998</v>
       </c>
       <c r="F19">
-        <v>5828.297000000001</v>
+        <v>6171.138000000002</v>
       </c>
       <c r="G19">
         <v>1596.9</v>
@@ -2851,28 +2851,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M19">
-        <v>301.9057846000001</v>
+        <v>319.6649484000001</v>
       </c>
       <c r="N19">
-        <v>1906.024827644898</v>
+        <v>1888.265663844898</v>
       </c>
       <c r="O19">
-        <v>419.3254620818776</v>
+        <v>415.4184460458776</v>
       </c>
       <c r="P19">
-        <v>1486.699365563021</v>
+        <v>1472.847217799021</v>
       </c>
       <c r="Q19">
-        <v>2985.299365563021</v>
+        <v>2971.447217799021</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07482781211864166</v>
+        <v>0.07511465838171652</v>
       </c>
       <c r="T19">
-        <v>0.6703882706383756</v>
+        <v>0.6770128956516518</v>
       </c>
       <c r="U19">
         <v>0.05180000000000001</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.313310061846684</v>
+        <v>6.907015058410757</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06886673987300755</v>
+        <v>0.06900965568754253</v>
       </c>
       <c r="C20">
-        <v>26940.51716854872</v>
+        <v>26403.62085961104</v>
       </c>
       <c r="D20">
-        <v>31514.75516854872</v>
+        <v>31320.69985961104</v>
       </c>
       <c r="E20">
-        <v>-9200.062</v>
+        <v>-8857.221</v>
       </c>
       <c r="F20">
-        <v>6171.138000000001</v>
+        <v>6513.979000000001</v>
       </c>
       <c r="G20">
         <v>1596.9</v>
@@ -2933,45 +2933,45 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M20">
-        <v>319.6649484000001</v>
+        <v>348.4978765000001</v>
       </c>
       <c r="N20">
-        <v>1888.265663844898</v>
+        <v>1859.432735744898</v>
       </c>
       <c r="O20">
-        <v>415.4184460458777</v>
+        <v>409.0752018638776</v>
       </c>
       <c r="P20">
-        <v>1472.847217799021</v>
+        <v>1450.357533881021</v>
       </c>
       <c r="Q20">
-        <v>2971.447217799021</v>
+        <v>2948.95753388102</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07511465838171652</v>
+        <v>0.07540858726857101</v>
       </c>
       <c r="T20">
-        <v>0.6770128956516517</v>
+        <v>0.6838010916529101</v>
       </c>
       <c r="U20">
-        <v>0.05180000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V20">
         <v>0.22</v>
       </c>
       <c r="W20">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>6.907015058410758</v>
+        <v>6.335564033902795</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06900965568754253</v>
+        <v>0.0689138915020775</v>
       </c>
       <c r="C21">
-        <v>26403.62085961104</v>
+        <v>26190.5460355049</v>
       </c>
       <c r="D21">
-        <v>31320.69985961104</v>
+        <v>31450.4660355049</v>
       </c>
       <c r="E21">
-        <v>-8857.221</v>
+        <v>-8514.379999999999</v>
       </c>
       <c r="F21">
-        <v>6513.979000000001</v>
+        <v>6856.820000000002</v>
       </c>
       <c r="G21">
         <v>1596.9</v>
@@ -3015,28 +3015,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M21">
-        <v>348.4978765000001</v>
+        <v>366.8398700000001</v>
       </c>
       <c r="N21">
-        <v>1859.432735744898</v>
+        <v>1841.090742244898</v>
       </c>
       <c r="O21">
-        <v>409.0752018638776</v>
+        <v>405.0399632938776</v>
       </c>
       <c r="P21">
-        <v>1450.357533881021</v>
+        <v>1436.050778951021</v>
       </c>
       <c r="Q21">
-        <v>2948.95753388102</v>
+        <v>2934.650778951021</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07540858726857101</v>
+        <v>0.07570986437759686</v>
       </c>
       <c r="T21">
-        <v>0.6838010916529101</v>
+        <v>0.6907589925541999</v>
       </c>
       <c r="U21">
         <v>0.05350000000000001</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.335564033902795</v>
+        <v>6.018785832207653</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0689138915020775</v>
+        <v>0.06881812731661247</v>
       </c>
       <c r="C22">
-        <v>26190.5460355049</v>
+        <v>25978.55096493079</v>
       </c>
       <c r="D22">
-        <v>31450.4660355049</v>
+        <v>31581.3119649308</v>
       </c>
       <c r="E22">
-        <v>-8514.379999999999</v>
+        <v>-8171.538999999999</v>
       </c>
       <c r="F22">
-        <v>6856.820000000002</v>
+        <v>7199.661000000002</v>
       </c>
       <c r="G22">
         <v>1596.9</v>
@@ -3097,28 +3097,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M22">
-        <v>366.8398700000001</v>
+        <v>385.1818635000001</v>
       </c>
       <c r="N22">
-        <v>1841.090742244898</v>
+        <v>1822.748748744898</v>
       </c>
       <c r="O22">
-        <v>405.0399632938776</v>
+        <v>401.0047247238776</v>
       </c>
       <c r="P22">
-        <v>1436.050778951021</v>
+        <v>1421.744024021021</v>
       </c>
       <c r="Q22">
-        <v>2934.650778951021</v>
+        <v>2920.34402402102</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07570986437759686</v>
+        <v>0.07601876875520563</v>
       </c>
       <c r="T22">
-        <v>0.6907589925541999</v>
+        <v>0.6978930428453958</v>
       </c>
       <c r="U22">
         <v>0.05350000000000001</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.018785832207653</v>
+        <v>5.732176983054909</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06881812731661245</v>
+        <v>0.06885964313114742</v>
       </c>
       <c r="C23">
-        <v>25978.55096493082</v>
+        <v>25578.85202125621</v>
       </c>
       <c r="D23">
-        <v>31581.31196493081</v>
+        <v>31524.45402125621</v>
       </c>
       <c r="E23">
-        <v>-8171.539</v>
+        <v>-7828.697999999999</v>
       </c>
       <c r="F23">
-        <v>7199.661000000001</v>
+        <v>7542.502000000001</v>
       </c>
       <c r="G23">
         <v>1596.9</v>
@@ -3179,45 +3179,45 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M23">
-        <v>385.1818635000001</v>
+        <v>409.5578586000001</v>
       </c>
       <c r="N23">
-        <v>1822.748748744898</v>
+        <v>1798.372753644898</v>
       </c>
       <c r="O23">
-        <v>401.0047247238776</v>
+        <v>395.6420058018776</v>
       </c>
       <c r="P23">
-        <v>1421.744024021021</v>
+        <v>1402.730747843021</v>
       </c>
       <c r="Q23">
-        <v>2920.344024021021</v>
+        <v>2901.330747843021</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07601876875520563</v>
+        <v>0.07633559375788131</v>
       </c>
       <c r="T23">
-        <v>0.6978930428453957</v>
+        <v>0.7052100175030325</v>
       </c>
       <c r="U23">
-        <v>0.05350000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V23">
         <v>0.22</v>
       </c>
       <c r="W23">
-        <v>0.04173</v>
+        <v>0.04235400000000001</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y23">
-        <v>5.732176983054909</v>
+        <v>5.391010246494383</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06885964313114742</v>
+        <v>0.0687701189456824</v>
       </c>
       <c r="C24">
-        <v>25578.85202125621</v>
+        <v>25358.87503755305</v>
       </c>
       <c r="D24">
-        <v>31524.45402125621</v>
+        <v>31647.31803755305</v>
       </c>
       <c r="E24">
-        <v>-7828.697999999999</v>
+        <v>-7485.856999999999</v>
       </c>
       <c r="F24">
-        <v>7542.502000000001</v>
+        <v>7885.343000000002</v>
       </c>
       <c r="G24">
         <v>1596.9</v>
@@ -3261,28 +3261,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M24">
-        <v>409.5578586000001</v>
+        <v>428.1741249000002</v>
       </c>
       <c r="N24">
-        <v>1798.372753644898</v>
+        <v>1779.756487344898</v>
       </c>
       <c r="O24">
-        <v>395.6420058018776</v>
+        <v>391.5464272158776</v>
       </c>
       <c r="P24">
-        <v>1402.730747843021</v>
+        <v>1388.210060129021</v>
       </c>
       <c r="Q24">
-        <v>2901.330747843021</v>
+        <v>2886.810060129021</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07633559375788131</v>
+        <v>0.07666064798140571</v>
       </c>
       <c r="T24">
-        <v>0.7052100175030325</v>
+        <v>0.712717043450478</v>
       </c>
       <c r="U24">
         <v>0.05430000000000001</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.391010246494383</v>
+        <v>5.156618496646801</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0687701189456824</v>
+        <v>0.06868059476021736</v>
       </c>
       <c r="C25">
-        <v>25358.87503755305</v>
+        <v>25139.85950621574</v>
       </c>
       <c r="D25">
-        <v>31647.31803755305</v>
+        <v>31771.14350621574</v>
       </c>
       <c r="E25">
-        <v>-7485.856999999999</v>
+        <v>-7143.015999999998</v>
       </c>
       <c r="F25">
-        <v>7885.343000000002</v>
+        <v>8228.184000000003</v>
       </c>
       <c r="G25">
         <v>1596.9</v>
@@ -3343,28 +3343,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M25">
-        <v>428.1741249000002</v>
+        <v>446.7903912000002</v>
       </c>
       <c r="N25">
-        <v>1779.756487344898</v>
+        <v>1761.140221044898</v>
       </c>
       <c r="O25">
-        <v>391.5464272158776</v>
+        <v>387.4508486298776</v>
       </c>
       <c r="P25">
-        <v>1388.210060129021</v>
+        <v>1373.689372415021</v>
       </c>
       <c r="Q25">
-        <v>2886.810060129021</v>
+        <v>2872.289372415021</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07666064798140571</v>
+        <v>0.07699425626344389</v>
       </c>
       <c r="T25">
-        <v>0.712717043450478</v>
+        <v>0.72042162271233</v>
       </c>
       <c r="U25">
         <v>0.05430000000000001</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.156618496646801</v>
+        <v>4.941759392619851</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06868059476021736</v>
+        <v>0.06859107057475232</v>
       </c>
       <c r="C26">
-        <v>25139.85950621574</v>
+        <v>24921.81675710781</v>
       </c>
       <c r="D26">
-        <v>31771.14350621574</v>
+        <v>31895.94175710781</v>
       </c>
       <c r="E26">
-        <v>-7143.016</v>
+        <v>-6800.174999999999</v>
       </c>
       <c r="F26">
-        <v>8228.184000000001</v>
+        <v>8571.025000000001</v>
       </c>
       <c r="G26">
         <v>1596.9</v>
@@ -3425,28 +3425,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M26">
-        <v>446.7903912000001</v>
+        <v>465.4066575000002</v>
       </c>
       <c r="N26">
-        <v>1761.140221044898</v>
+        <v>1742.523954744898</v>
       </c>
       <c r="O26">
-        <v>387.4508486298776</v>
+        <v>383.3552700438776</v>
       </c>
       <c r="P26">
-        <v>1373.689372415021</v>
+        <v>1359.168684701021</v>
       </c>
       <c r="Q26">
-        <v>2872.289372415021</v>
+        <v>2857.76868470102</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07699425626344389</v>
+        <v>0.07733676076633643</v>
       </c>
       <c r="T26">
-        <v>0.72042162271233</v>
+        <v>0.7283316574211647</v>
       </c>
       <c r="U26">
         <v>0.05430000000000001</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.941759392619852</v>
+        <v>4.744089016915057</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06859107057475232</v>
+        <v>0.06850154638928731</v>
       </c>
       <c r="C27">
-        <v>24921.81675710781</v>
+        <v>24704.75829881131</v>
       </c>
       <c r="D27">
-        <v>31895.94175710781</v>
+        <v>32021.72429881131</v>
       </c>
       <c r="E27">
-        <v>-6800.174999999999</v>
+        <v>-6457.333999999999</v>
       </c>
       <c r="F27">
-        <v>8571.025000000001</v>
+        <v>8913.866000000002</v>
       </c>
       <c r="G27">
         <v>1596.9</v>
@@ -3507,28 +3507,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M27">
-        <v>465.4066575000002</v>
+        <v>484.0229238000002</v>
       </c>
       <c r="N27">
-        <v>1742.523954744898</v>
+        <v>1723.907688444898</v>
       </c>
       <c r="O27">
-        <v>383.3552700438776</v>
+        <v>379.2596914578776</v>
       </c>
       <c r="P27">
-        <v>1359.168684701021</v>
+        <v>1344.647996987021</v>
       </c>
       <c r="Q27">
-        <v>2857.76868470102</v>
+        <v>2843.247996987021</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07733676076633643</v>
+        <v>0.07768852214768554</v>
       </c>
       <c r="T27">
-        <v>0.7283316574211647</v>
+        <v>0.7364554768518599</v>
       </c>
       <c r="U27">
         <v>0.05430000000000001</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.744089016915057</v>
+        <v>4.561624054726016</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06850154638928731</v>
+        <v>0.06841202220382227</v>
       </c>
       <c r="C28">
-        <v>24704.75829881131</v>
+        <v>24488.69582216481</v>
       </c>
       <c r="D28">
-        <v>32021.72429881131</v>
+        <v>32148.50282216481</v>
       </c>
       <c r="E28">
-        <v>-6457.333999999999</v>
+        <v>-6114.492999999999</v>
       </c>
       <c r="F28">
-        <v>8913.866000000002</v>
+        <v>9256.707000000002</v>
       </c>
       <c r="G28">
         <v>1596.9</v>
@@ -3589,28 +3589,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M28">
-        <v>484.0229238000002</v>
+        <v>502.6391901000002</v>
       </c>
       <c r="N28">
-        <v>1723.907688444898</v>
+        <v>1705.291422144898</v>
       </c>
       <c r="O28">
-        <v>379.2596914578776</v>
+        <v>375.1641128718776</v>
       </c>
       <c r="P28">
-        <v>1344.647996987021</v>
+        <v>1330.127309273021</v>
       </c>
       <c r="Q28">
-        <v>2843.247996987021</v>
+        <v>2828.727309273021</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07768852214768554</v>
+        <v>0.07804992082715378</v>
       </c>
       <c r="T28">
-        <v>0.7364554768518599</v>
+        <v>0.7448018666779165</v>
       </c>
       <c r="U28">
         <v>0.05430000000000001</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.561624054726016</v>
+        <v>4.39267501566209</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06841202220382227</v>
+        <v>0.06854089801835724</v>
       </c>
       <c r="C29">
-        <v>24488.69582216481</v>
+        <v>23963.66480996997</v>
       </c>
       <c r="D29">
-        <v>32148.50282216481</v>
+        <v>31966.31280996997</v>
       </c>
       <c r="E29">
-        <v>-6114.492999999999</v>
+        <v>-5771.651999999998</v>
       </c>
       <c r="F29">
-        <v>9256.707000000002</v>
+        <v>9599.548000000003</v>
       </c>
       <c r="G29">
         <v>1596.9</v>
@@ -3671,45 +3671,45 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M29">
-        <v>502.6391901000002</v>
+        <v>530.8550044000002</v>
       </c>
       <c r="N29">
-        <v>1705.291422144898</v>
+        <v>1677.075607844898</v>
       </c>
       <c r="O29">
-        <v>375.1641128718776</v>
+        <v>368.9566337258776</v>
       </c>
       <c r="P29">
-        <v>1330.127309273021</v>
+        <v>1308.118974119021</v>
       </c>
       <c r="Q29">
-        <v>2828.727309273021</v>
+        <v>2806.71897411902</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07804992082715378</v>
+        <v>0.07842135835882949</v>
       </c>
       <c r="T29">
-        <v>0.7448018666779165</v>
+        <v>0.753380100665808</v>
       </c>
       <c r="U29">
-        <v>0.05430000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V29">
         <v>0.22</v>
       </c>
       <c r="W29">
-        <v>0.04235400000000001</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y29">
-        <v>4.39267501566209</v>
+        <v>4.15919713282239</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06854089801835724</v>
+        <v>0.06845917383289218</v>
       </c>
       <c r="C30">
-        <v>23963.66480996997</v>
+        <v>23736.11578380723</v>
       </c>
       <c r="D30">
-        <v>31966.31280996997</v>
+        <v>32081.60478380723</v>
       </c>
       <c r="E30">
-        <v>-5771.651999999998</v>
+        <v>-5428.810999999998</v>
       </c>
       <c r="F30">
-        <v>9599.548000000003</v>
+        <v>9942.389000000003</v>
       </c>
       <c r="G30">
         <v>1596.9</v>
@@ -3753,28 +3753,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M30">
-        <v>530.8550044000002</v>
+        <v>549.8141117000002</v>
       </c>
       <c r="N30">
-        <v>1677.075607844898</v>
+        <v>1658.116500544898</v>
       </c>
       <c r="O30">
-        <v>368.9566337258776</v>
+        <v>364.7856301198776</v>
       </c>
       <c r="P30">
-        <v>1308.118974119021</v>
+        <v>1293.330870425021</v>
       </c>
       <c r="Q30">
-        <v>2806.71897411902</v>
+        <v>2791.930870425021</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07842135835882949</v>
+        <v>0.07880325891956647</v>
       </c>
       <c r="T30">
-        <v>0.753380100665808</v>
+        <v>0.7621999750477246</v>
       </c>
       <c r="U30">
         <v>0.05530000000000001</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.15919713282239</v>
+        <v>4.015776542035411</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06845917383289218</v>
+        <v>0.06837744964742716</v>
       </c>
       <c r="C31">
-        <v>23736.11578380723</v>
+        <v>23509.4014083955</v>
       </c>
       <c r="D31">
-        <v>32081.60478380723</v>
+        <v>32197.73140839551</v>
       </c>
       <c r="E31">
-        <v>-5428.811</v>
+        <v>-5085.969999999999</v>
       </c>
       <c r="F31">
-        <v>9942.389000000001</v>
+        <v>10285.23</v>
       </c>
       <c r="G31">
         <v>1596.9</v>
@@ -3835,28 +3835,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M31">
-        <v>549.8141117000001</v>
+        <v>568.7732190000002</v>
       </c>
       <c r="N31">
-        <v>1658.116500544898</v>
+        <v>1639.157393244898</v>
       </c>
       <c r="O31">
-        <v>364.7856301198776</v>
+        <v>360.6146265138776</v>
       </c>
       <c r="P31">
-        <v>1293.330870425021</v>
+        <v>1278.54276673102</v>
       </c>
       <c r="Q31">
-        <v>2791.930870425021</v>
+        <v>2777.14276673102</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07880325891956647</v>
+        <v>0.07919607092489594</v>
       </c>
       <c r="T31">
-        <v>0.7621999750477246</v>
+        <v>0.7712718458405531</v>
       </c>
       <c r="U31">
         <v>0.05530000000000001</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.015776542035413</v>
+        <v>3.881917323967565</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06837744964742716</v>
+        <v>0.06829572546196214</v>
       </c>
       <c r="C32">
-        <v>23509.4014083955</v>
+        <v>23283.53078028336</v>
       </c>
       <c r="D32">
-        <v>32197.73140839551</v>
+        <v>32314.70178028337</v>
       </c>
       <c r="E32">
-        <v>-5085.969999999999</v>
+        <v>-4743.128999999999</v>
       </c>
       <c r="F32">
-        <v>10285.23</v>
+        <v>10628.071</v>
       </c>
       <c r="G32">
         <v>1596.9</v>
@@ -3917,28 +3917,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M32">
-        <v>568.7732190000002</v>
+        <v>587.7323263000002</v>
       </c>
       <c r="N32">
-        <v>1639.157393244898</v>
+        <v>1620.198285944898</v>
       </c>
       <c r="O32">
-        <v>360.6146265138776</v>
+        <v>356.4436229078776</v>
       </c>
       <c r="P32">
-        <v>1278.54276673102</v>
+        <v>1263.75466303702</v>
       </c>
       <c r="Q32">
-        <v>2777.14276673102</v>
+        <v>2762.35466303702</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07919607092489594</v>
+        <v>0.07960026878545237</v>
       </c>
       <c r="T32">
-        <v>0.7712718458405531</v>
+        <v>0.7806066694099855</v>
       </c>
       <c r="U32">
         <v>0.05530000000000001</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.881917323967565</v>
+        <v>3.75669418448474</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.06829572546196214</v>
+        <v>0.0682140012764971</v>
       </c>
       <c r="C33">
-        <v>23283.53078028336</v>
+        <v>23058.51312868784</v>
       </c>
       <c r="D33">
-        <v>32314.70178028337</v>
+        <v>32432.52512868784</v>
       </c>
       <c r="E33">
-        <v>-4743.128999999999</v>
+        <v>-4400.287999999999</v>
       </c>
       <c r="F33">
-        <v>10628.071</v>
+        <v>10970.912</v>
       </c>
       <c r="G33">
         <v>1596.9</v>
@@ -3999,28 +3999,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M33">
-        <v>587.7323263000002</v>
+        <v>606.6914336000002</v>
       </c>
       <c r="N33">
-        <v>1620.198285944898</v>
+        <v>1601.239178644898</v>
       </c>
       <c r="O33">
-        <v>356.4436229078776</v>
+        <v>352.2726193018776</v>
       </c>
       <c r="P33">
-        <v>1263.75466303702</v>
+        <v>1248.96655934302</v>
       </c>
       <c r="Q33">
-        <v>2762.35466303702</v>
+        <v>2747.56655934302</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.07960026878545237</v>
+        <v>0.0800163548183781</v>
       </c>
       <c r="T33">
-        <v>0.7806066694099855</v>
+        <v>0.7902160466138127</v>
       </c>
       <c r="U33">
         <v>0.05530000000000001</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.75669418448474</v>
+        <v>3.639297491219592</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0682140012764971</v>
+        <v>0.06813227709103206</v>
       </c>
       <c r="C34">
-        <v>23058.51312868784</v>
+        <v>22834.35781792195</v>
       </c>
       <c r="D34">
-        <v>32432.52512868784</v>
+        <v>32551.21081792196</v>
       </c>
       <c r="E34">
-        <v>-4400.287999999999</v>
+        <v>-4057.446999999998</v>
       </c>
       <c r="F34">
-        <v>10970.912</v>
+        <v>11313.753</v>
       </c>
       <c r="G34">
         <v>1596.9</v>
@@ -4081,28 +4081,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M34">
-        <v>606.6914336000002</v>
+        <v>625.6505409000002</v>
       </c>
       <c r="N34">
-        <v>1601.239178644898</v>
+        <v>1582.280071344898</v>
       </c>
       <c r="O34">
-        <v>352.2726193018776</v>
+        <v>348.1016156958776</v>
       </c>
       <c r="P34">
-        <v>1248.96655934302</v>
+        <v>1234.178455649021</v>
       </c>
       <c r="Q34">
-        <v>2747.56655934302</v>
+        <v>2732.778455649021</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.0800163548183781</v>
+        <v>0.08044486132989861</v>
       </c>
       <c r="T34">
-        <v>0.7902160466138127</v>
+        <v>0.8001122708983512</v>
       </c>
       <c r="U34">
         <v>0.05530000000000001</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.639297491219592</v>
+        <v>3.529015749061422</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.06813227709103206</v>
+        <v>0.06805055290556704</v>
       </c>
       <c r="C35">
-        <v>22834.35781792195</v>
+        <v>22611.07434987566</v>
       </c>
       <c r="D35">
-        <v>32551.21081792196</v>
+        <v>32670.76834987567</v>
       </c>
       <c r="E35">
-        <v>-4057.446999999998</v>
+        <v>-3714.605999999998</v>
       </c>
       <c r="F35">
-        <v>11313.753</v>
+        <v>11656.594</v>
       </c>
       <c r="G35">
         <v>1596.9</v>
@@ -4163,28 +4163,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M35">
-        <v>625.6505409000002</v>
+        <v>644.6096482000003</v>
       </c>
       <c r="N35">
-        <v>1582.280071344898</v>
+        <v>1563.320964044898</v>
       </c>
       <c r="O35">
-        <v>348.1016156958776</v>
+        <v>343.9306120898776</v>
       </c>
       <c r="P35">
-        <v>1234.178455649021</v>
+        <v>1219.390351955021</v>
       </c>
       <c r="Q35">
-        <v>2732.778455649021</v>
+        <v>2717.990351955021</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08044486132989861</v>
+        <v>0.08088635288722279</v>
       </c>
       <c r="T35">
-        <v>0.8001122708983512</v>
+        <v>0.8103083807672699</v>
       </c>
       <c r="U35">
         <v>0.05530000000000001</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.529015749061422</v>
+        <v>3.425221168206674</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.06805055290556704</v>
+        <v>0.067968828720102</v>
       </c>
       <c r="C36">
-        <v>22611.07434987566</v>
+        <v>22388.67236655179</v>
       </c>
       <c r="D36">
-        <v>32670.76834987567</v>
+        <v>32791.20736655179</v>
       </c>
       <c r="E36">
-        <v>-3714.605999999998</v>
+        <v>-3371.764999999998</v>
       </c>
       <c r="F36">
-        <v>11656.594</v>
+        <v>11999.435</v>
       </c>
       <c r="G36">
         <v>1596.9</v>
@@ -4245,28 +4245,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M36">
-        <v>644.6096482000003</v>
+        <v>663.5687555000003</v>
       </c>
       <c r="N36">
-        <v>1563.320964044898</v>
+        <v>1544.361856744898</v>
       </c>
       <c r="O36">
-        <v>343.9306120898776</v>
+        <v>339.7596084838776</v>
       </c>
       <c r="P36">
-        <v>1219.390351955021</v>
+        <v>1204.60224826102</v>
       </c>
       <c r="Q36">
-        <v>2717.990351955021</v>
+        <v>2703.20224826102</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08088635288722279</v>
+        <v>0.08134142880015693</v>
       </c>
       <c r="T36">
-        <v>0.8103083807672699</v>
+        <v>0.8208182170936936</v>
       </c>
       <c r="U36">
         <v>0.05530000000000001</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.425221168206674</v>
+        <v>3.327357706257912</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.067968828720102</v>
+        <v>0.06788710453463696</v>
       </c>
       <c r="C37">
-        <v>22388.67236655179</v>
+        <v>22167.16165265805</v>
       </c>
       <c r="D37">
-        <v>32791.20736655179</v>
+        <v>32912.53765265806</v>
       </c>
       <c r="E37">
-        <v>-3371.764999999998</v>
+        <v>-3028.923999999997</v>
       </c>
       <c r="F37">
-        <v>11999.435</v>
+        <v>12342.276</v>
       </c>
       <c r="G37">
         <v>1596.9</v>
@@ -4327,28 +4327,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M37">
-        <v>663.5687555000003</v>
+        <v>682.5278628000003</v>
       </c>
       <c r="N37">
-        <v>1544.361856744898</v>
+        <v>1525.402749444898</v>
       </c>
       <c r="O37">
-        <v>339.7596084838776</v>
+        <v>335.5886048778776</v>
       </c>
       <c r="P37">
-        <v>1204.60224826102</v>
+        <v>1189.814144567021</v>
       </c>
       <c r="Q37">
-        <v>2703.20224826102</v>
+        <v>2688.41414456702</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08134142880015693</v>
+        <v>0.08181072583537027</v>
       </c>
       <c r="T37">
-        <v>0.8208182170936936</v>
+        <v>0.8316564858053181</v>
       </c>
       <c r="U37">
         <v>0.05530000000000001</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.327357706257912</v>
+        <v>3.234931103306304</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.06788710453463698</v>
+        <v>0.06780538034917194</v>
       </c>
       <c r="C38">
-        <v>22167.16165265804</v>
+        <v>21946.55213825706</v>
       </c>
       <c r="D38">
-        <v>32912.53765265804</v>
+        <v>33034.76913825706</v>
       </c>
       <c r="E38">
-        <v>-3028.923999999999</v>
+        <v>-2686.082999999999</v>
       </c>
       <c r="F38">
-        <v>12342.276</v>
+        <v>12685.117</v>
       </c>
       <c r="G38">
         <v>1596.9</v>
@@ -4409,28 +4409,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M38">
-        <v>682.5278628000002</v>
+        <v>701.4869701000002</v>
       </c>
       <c r="N38">
-        <v>1525.402749444898</v>
+        <v>1506.443642144898</v>
       </c>
       <c r="O38">
-        <v>335.5886048778776</v>
+        <v>331.4176012718776</v>
       </c>
       <c r="P38">
-        <v>1189.814144567021</v>
+        <v>1175.026040873021</v>
       </c>
       <c r="Q38">
-        <v>2688.414144567021</v>
+        <v>2673.62604087302</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08181072583537027</v>
+        <v>0.08229492118916182</v>
       </c>
       <c r="T38">
-        <v>0.831656485805318</v>
+        <v>0.8428388265395338</v>
       </c>
       <c r="U38">
         <v>0.05530000000000001</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.234931103306304</v>
+        <v>3.147500532946674</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.06780538034917194</v>
+        <v>0.06772365616370692</v>
       </c>
       <c r="C39">
-        <v>21946.55213825706</v>
+        <v>21726.85390147547</v>
       </c>
       <c r="D39">
-        <v>33034.76913825706</v>
+        <v>33157.91190147547</v>
       </c>
       <c r="E39">
-        <v>-2686.082999999999</v>
+        <v>-2343.241999999998</v>
       </c>
       <c r="F39">
-        <v>12685.117</v>
+        <v>13027.958</v>
       </c>
       <c r="G39">
         <v>1596.9</v>
@@ -4491,28 +4491,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M39">
-        <v>701.4869701000002</v>
+        <v>720.4460774000003</v>
       </c>
       <c r="N39">
-        <v>1506.443642144898</v>
+        <v>1487.484534844898</v>
       </c>
       <c r="O39">
-        <v>331.4176012718776</v>
+        <v>327.2465976658776</v>
       </c>
       <c r="P39">
-        <v>1175.026040873021</v>
+        <v>1160.23793717902</v>
       </c>
       <c r="Q39">
-        <v>2673.62604087302</v>
+        <v>2658.837937179021</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08229492118916182</v>
+        <v>0.08279473574791438</v>
       </c>
       <c r="T39">
-        <v>0.8428388265395338</v>
+        <v>0.8543818879425952</v>
       </c>
       <c r="U39">
         <v>0.05530000000000001</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.147500532946674</v>
+        <v>3.06467157155334</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.06772365616370692</v>
+        <v>0.06840243197824188</v>
       </c>
       <c r="C40">
-        <v>21726.85390147547</v>
+        <v>20388.24445138707</v>
       </c>
       <c r="D40">
-        <v>33157.91190147547</v>
+        <v>32162.14345138707</v>
       </c>
       <c r="E40">
-        <v>-2343.241999999998</v>
+        <v>-2000.400999999998</v>
       </c>
       <c r="F40">
-        <v>13027.958</v>
+        <v>13370.799</v>
       </c>
       <c r="G40">
         <v>1596.9</v>
@@ -4573,45 +4573,45 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M40">
-        <v>720.4460774000003</v>
+        <v>772.8321822000003</v>
       </c>
       <c r="N40">
-        <v>1487.484534844898</v>
+        <v>1435.098430044898</v>
       </c>
       <c r="O40">
-        <v>327.2465976658776</v>
+        <v>315.7216546098776</v>
       </c>
       <c r="P40">
-        <v>1160.23793717902</v>
+        <v>1119.376775435021</v>
       </c>
       <c r="Q40">
-        <v>2658.837937179021</v>
+        <v>2617.97677543502</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08279473574791438</v>
+        <v>0.08331093766924898</v>
       </c>
       <c r="T40">
-        <v>0.8543818879425952</v>
+        <v>0.8663034103752651</v>
       </c>
       <c r="U40">
-        <v>0.05530000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V40">
         <v>0.22</v>
       </c>
       <c r="W40">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y40">
-        <v>3.06467157155334</v>
+        <v>2.856934096558509</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.06840243197824188</v>
+        <v>0.06834020779277684</v>
       </c>
       <c r="C41">
-        <v>20388.24445138707</v>
+        <v>20134.1898191735</v>
       </c>
       <c r="D41">
-        <v>32162.14345138707</v>
+        <v>32250.9298191735</v>
       </c>
       <c r="E41">
-        <v>-2000.400999999998</v>
+        <v>-1657.559999999998</v>
       </c>
       <c r="F41">
-        <v>13370.799</v>
+        <v>13713.64</v>
       </c>
       <c r="G41">
         <v>1596.9</v>
@@ -4655,28 +4655,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M41">
-        <v>772.8321822000003</v>
+        <v>792.6483920000003</v>
       </c>
       <c r="N41">
-        <v>1435.098430044898</v>
+        <v>1415.282220244898</v>
       </c>
       <c r="O41">
-        <v>315.7216546098776</v>
+        <v>311.3620884538776</v>
       </c>
       <c r="P41">
-        <v>1119.376775435021</v>
+        <v>1103.920131791021</v>
       </c>
       <c r="Q41">
-        <v>2617.97677543502</v>
+        <v>2602.520131791021</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08331093766924898</v>
+        <v>0.08384434632129474</v>
       </c>
       <c r="T41">
-        <v>0.8663034103752651</v>
+        <v>0.8786223168890241</v>
       </c>
       <c r="U41">
         <v>0.0578</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.856934096558509</v>
+        <v>2.785510744144545</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.06834020779277684</v>
+        <v>0.06827798360731181</v>
       </c>
       <c r="C42">
-        <v>20134.1898191735</v>
+        <v>19880.62674879327</v>
       </c>
       <c r="D42">
-        <v>32250.9298191735</v>
+        <v>32340.20774879327</v>
       </c>
       <c r="E42">
-        <v>-1657.559999999998</v>
+        <v>-1314.718999999997</v>
       </c>
       <c r="F42">
-        <v>13713.64</v>
+        <v>14056.481</v>
       </c>
       <c r="G42">
         <v>1596.9</v>
@@ -4737,28 +4737,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M42">
-        <v>792.6483920000003</v>
+        <v>812.4646018000003</v>
       </c>
       <c r="N42">
-        <v>1415.282220244898</v>
+        <v>1395.466010444898</v>
       </c>
       <c r="O42">
-        <v>311.3620884538776</v>
+        <v>307.0025222978776</v>
       </c>
       <c r="P42">
-        <v>1103.920131791021</v>
+        <v>1088.463488147021</v>
       </c>
       <c r="Q42">
-        <v>2602.520131791021</v>
+        <v>2587.063488147021</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08384434632129474</v>
+        <v>0.08439583662256239</v>
       </c>
       <c r="T42">
-        <v>0.8786223168890241</v>
+        <v>0.891358813454097</v>
       </c>
       <c r="U42">
         <v>0.0578</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.785510744144545</v>
+        <v>2.717571457701996</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.06827798360731181</v>
+        <v>0.06821575942184679</v>
       </c>
       <c r="C43">
-        <v>19880.62674879327</v>
+        <v>19627.55933384419</v>
       </c>
       <c r="D43">
-        <v>32340.20774879327</v>
+        <v>32429.98133384419</v>
       </c>
       <c r="E43">
-        <v>-1314.718999999997</v>
+        <v>-971.877999999997</v>
       </c>
       <c r="F43">
-        <v>14056.481</v>
+        <v>14399.322</v>
       </c>
       <c r="G43">
         <v>1596.9</v>
@@ -4819,28 +4819,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M43">
-        <v>812.4646018000003</v>
+        <v>832.2808116000002</v>
       </c>
       <c r="N43">
-        <v>1395.466010444898</v>
+        <v>1375.649800644898</v>
       </c>
       <c r="O43">
-        <v>307.0025222978776</v>
+        <v>302.6429561418776</v>
       </c>
       <c r="P43">
-        <v>1088.463488147021</v>
+        <v>1073.006844503021</v>
       </c>
       <c r="Q43">
-        <v>2587.063488147021</v>
+        <v>2571.606844503021</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08439583662256239</v>
+        <v>0.08496634383077031</v>
       </c>
       <c r="T43">
-        <v>0.891358813454097</v>
+        <v>0.9045344995558964</v>
       </c>
       <c r="U43">
         <v>0.0578</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.717571457701996</v>
+        <v>2.652867375375758</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.06821575942184679</v>
+        <v>0.06815353523638176</v>
       </c>
       <c r="C44">
-        <v>19627.55933384419</v>
+        <v>19374.99171350453</v>
       </c>
       <c r="D44">
-        <v>32429.98133384419</v>
+        <v>32520.25471350453</v>
       </c>
       <c r="E44">
-        <v>-971.8779999999988</v>
+        <v>-629.0369999999984</v>
       </c>
       <c r="F44">
-        <v>14399.322</v>
+        <v>14742.163</v>
       </c>
       <c r="G44">
         <v>1596.9</v>
@@ -4901,28 +4901,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M44">
-        <v>832.2808116000002</v>
+        <v>852.0970214000002</v>
       </c>
       <c r="N44">
-        <v>1375.649800644898</v>
+        <v>1355.833590844898</v>
       </c>
       <c r="O44">
-        <v>302.6429561418776</v>
+        <v>298.2833899858776</v>
       </c>
       <c r="P44">
-        <v>1073.006844503021</v>
+        <v>1057.55020085902</v>
       </c>
       <c r="Q44">
-        <v>2571.606844503021</v>
+        <v>2556.150200859021</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08496634383077031</v>
+        <v>0.08555686883575746</v>
       </c>
       <c r="T44">
-        <v>0.9045344995558964</v>
+        <v>0.9181724904331976</v>
       </c>
       <c r="U44">
         <v>0.0578</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.652867375375758</v>
+        <v>2.59117278525074</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.06815353523638176</v>
+        <v>0.06809131105091673</v>
       </c>
       <c r="C45">
-        <v>19374.99171350453</v>
+        <v>19122.92807316907</v>
       </c>
       <c r="D45">
-        <v>32520.25471350453</v>
+        <v>32611.03207316907</v>
       </c>
       <c r="E45">
-        <v>-629.0369999999984</v>
+        <v>-286.1959999999981</v>
       </c>
       <c r="F45">
-        <v>14742.163</v>
+        <v>15085.004</v>
       </c>
       <c r="G45">
         <v>1596.9</v>
@@ -4983,28 +4983,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M45">
-        <v>852.0970214000002</v>
+        <v>871.9132312000003</v>
       </c>
       <c r="N45">
-        <v>1355.833590844898</v>
+        <v>1336.017381044898</v>
       </c>
       <c r="O45">
-        <v>298.2833899858776</v>
+        <v>293.9238238298776</v>
       </c>
       <c r="P45">
-        <v>1057.55020085902</v>
+        <v>1042.093557215021</v>
       </c>
       <c r="Q45">
-        <v>2556.150200859021</v>
+        <v>2540.693557215021</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08555686883575746</v>
+        <v>0.08616848401949415</v>
       </c>
       <c r="T45">
-        <v>0.9181724904331976</v>
+        <v>0.9322975524132596</v>
       </c>
       <c r="U45">
         <v>0.0578</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.59117278525074</v>
+        <v>2.53228249467686</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.06809131105091673</v>
+        <v>0.06925758686545169</v>
       </c>
       <c r="C46">
-        <v>19122.92807316907</v>
+        <v>17158.7157781542</v>
       </c>
       <c r="D46">
-        <v>32611.03207316907</v>
+        <v>30989.66077815421</v>
       </c>
       <c r="E46">
-        <v>-286.1959999999981</v>
+        <v>56.64500000000226</v>
       </c>
       <c r="F46">
-        <v>15085.004</v>
+        <v>15427.845</v>
       </c>
       <c r="G46">
         <v>1596.9</v>
@@ -5065,45 +5065,45 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M46">
-        <v>871.9132312000003</v>
+        <v>945.7268985000003</v>
       </c>
       <c r="N46">
-        <v>1336.017381044898</v>
+        <v>1262.203713744898</v>
       </c>
       <c r="O46">
-        <v>293.9238238298776</v>
+        <v>277.6848170238776</v>
       </c>
       <c r="P46">
-        <v>1042.093557215021</v>
+        <v>984.5188967210205</v>
       </c>
       <c r="Q46">
-        <v>2540.693557215021</v>
+        <v>2483.118896721021</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08616848401949415</v>
+        <v>0.08680233975536669</v>
       </c>
       <c r="T46">
-        <v>0.9322975524132596</v>
+        <v>0.9469362530107783</v>
       </c>
       <c r="U46">
-        <v>0.0578</v>
+        <v>0.06130000000000001</v>
       </c>
       <c r="V46">
         <v>0.22</v>
       </c>
       <c r="W46">
-        <v>0.04508400000000001</v>
+        <v>0.04781400000000001</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y46">
-        <v>2.53228249467686</v>
+        <v>2.334638695110455</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.06925758686545169</v>
+        <v>0.06922266267998667</v>
       </c>
       <c r="C47">
-        <v>17158.7157781542</v>
+        <v>16862.08167936357</v>
       </c>
       <c r="D47">
-        <v>30989.66077815421</v>
+        <v>31035.86767936357</v>
       </c>
       <c r="E47">
-        <v>56.64500000000226</v>
+        <v>399.4860000000026</v>
       </c>
       <c r="F47">
-        <v>15427.845</v>
+        <v>15770.686</v>
       </c>
       <c r="G47">
         <v>1596.9</v>
@@ -5147,28 +5147,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M47">
-        <v>945.7268985000003</v>
+        <v>966.7430518000003</v>
       </c>
       <c r="N47">
-        <v>1262.203713744898</v>
+        <v>1241.187560444898</v>
       </c>
       <c r="O47">
-        <v>277.6848170238776</v>
+        <v>273.0612632978776</v>
       </c>
       <c r="P47">
-        <v>984.5188967210205</v>
+        <v>968.1262971470205</v>
       </c>
       <c r="Q47">
-        <v>2483.118896721021</v>
+        <v>2466.72629714702</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08680233975536669</v>
+        <v>0.08745967162960491</v>
       </c>
       <c r="T47">
-        <v>0.9469362530107783</v>
+        <v>0.9621171277045015</v>
       </c>
       <c r="U47">
         <v>0.06130000000000001</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.334638695110455</v>
+        <v>2.283885679999358</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.06922266267998667</v>
+        <v>0.07021421849452164</v>
       </c>
       <c r="C48">
-        <v>16862.08167936357</v>
+        <v>15258.75408776874</v>
       </c>
       <c r="D48">
-        <v>31035.86767936357</v>
+        <v>29775.38108776875</v>
       </c>
       <c r="E48">
-        <v>399.4860000000026</v>
+        <v>742.327000000003</v>
       </c>
       <c r="F48">
-        <v>15770.686</v>
+        <v>16113.527</v>
       </c>
       <c r="G48">
         <v>1596.9</v>
@@ -5229,45 +5229,45 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M48">
-        <v>966.7430518000003</v>
+        <v>1032.8770807</v>
       </c>
       <c r="N48">
-        <v>1241.187560444898</v>
+        <v>1175.053531544898</v>
       </c>
       <c r="O48">
-        <v>273.0612632978776</v>
+        <v>258.5117769398776</v>
       </c>
       <c r="P48">
-        <v>968.1262971470205</v>
+        <v>916.5417546050205</v>
       </c>
       <c r="Q48">
-        <v>2466.72629714702</v>
+        <v>2415.141754605021</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08745967162960491</v>
+        <v>0.08814180848022948</v>
       </c>
       <c r="T48">
-        <v>0.9621171277045015</v>
+        <v>0.9778708655942143</v>
       </c>
       <c r="U48">
-        <v>0.06130000000000001</v>
+        <v>0.0641</v>
       </c>
       <c r="V48">
         <v>0.22</v>
       </c>
       <c r="W48">
-        <v>0.04781400000000001</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y48">
-        <v>2.283885679999358</v>
+        <v>2.137650891380552</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07021421849452164</v>
+        <v>0.0702011343090566</v>
       </c>
       <c r="C49">
-        <v>15258.75408776874</v>
+        <v>14931.87900982426</v>
       </c>
       <c r="D49">
-        <v>29775.38108776875</v>
+        <v>29791.34700982427</v>
       </c>
       <c r="E49">
-        <v>742.327000000003</v>
+        <v>1085.168000000005</v>
       </c>
       <c r="F49">
-        <v>16113.527</v>
+        <v>16456.36800000001</v>
       </c>
       <c r="G49">
         <v>1596.9</v>
@@ -5311,28 +5311,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M49">
-        <v>1032.8770807</v>
+        <v>1054.8531888</v>
       </c>
       <c r="N49">
-        <v>1175.053531544898</v>
+        <v>1153.077423444898</v>
       </c>
       <c r="O49">
-        <v>258.5117769398776</v>
+        <v>253.6770331578776</v>
       </c>
       <c r="P49">
-        <v>916.5417546050205</v>
+        <v>899.4003902870204</v>
       </c>
       <c r="Q49">
-        <v>2415.141754605021</v>
+        <v>2398.00039028702</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08814180848022948</v>
+        <v>0.08885018136357037</v>
       </c>
       <c r="T49">
-        <v>0.9778708655942143</v>
+        <v>0.9942305164796853</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.137650891380552</v>
+        <v>2.093116497810124</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.0702011343090566</v>
+        <v>0.07018805012359156</v>
       </c>
       <c r="C50">
-        <v>14931.87900982426</v>
+        <v>14605.02106330966</v>
       </c>
       <c r="D50">
-        <v>29791.34700982427</v>
+        <v>29807.33006330967</v>
       </c>
       <c r="E50">
-        <v>1085.168000000001</v>
+        <v>1428.009000000002</v>
       </c>
       <c r="F50">
-        <v>16456.368</v>
+        <v>16799.209</v>
       </c>
       <c r="G50">
         <v>1596.9</v>
@@ -5393,28 +5393,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M50">
-        <v>1054.8531888</v>
+        <v>1076.8292969</v>
       </c>
       <c r="N50">
-        <v>1153.077423444898</v>
+        <v>1131.101315344898</v>
       </c>
       <c r="O50">
-        <v>253.6770331578776</v>
+        <v>248.8422893758776</v>
       </c>
       <c r="P50">
-        <v>899.4003902870206</v>
+        <v>882.2590259690206</v>
       </c>
       <c r="Q50">
-        <v>2398.00039028702</v>
+        <v>2380.85902596902</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08885018136357037</v>
+        <v>0.08958633357566972</v>
       </c>
       <c r="T50">
-        <v>0.9942305164796852</v>
+        <v>1.011231722301841</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.093116497810124</v>
+        <v>2.05039983458951</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07018805012359156</v>
+        <v>0.07017496593812653</v>
       </c>
       <c r="C51">
-        <v>14605.02106330966</v>
+        <v>14278.18027581276</v>
       </c>
       <c r="D51">
-        <v>29807.33006330967</v>
+        <v>29823.33027581276</v>
       </c>
       <c r="E51">
-        <v>1428.009000000002</v>
+        <v>1770.850000000002</v>
       </c>
       <c r="F51">
-        <v>16799.209</v>
+        <v>17142.05</v>
       </c>
       <c r="G51">
         <v>1596.9</v>
@@ -5475,28 +5475,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M51">
-        <v>1076.8292969</v>
+        <v>1098.805405</v>
       </c>
       <c r="N51">
-        <v>1131.101315344898</v>
+        <v>1109.125207244898</v>
       </c>
       <c r="O51">
-        <v>248.8422893758776</v>
+        <v>244.0075455938776</v>
       </c>
       <c r="P51">
-        <v>882.2590259690206</v>
+        <v>865.1176616510205</v>
       </c>
       <c r="Q51">
-        <v>2380.85902596902</v>
+        <v>2363.717661651021</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.08958633357566972</v>
+        <v>0.09035193187625305</v>
       </c>
       <c r="T51">
-        <v>1.011231722301841</v>
+        <v>1.028912976356883</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.05039983458951</v>
+        <v>2.009391837897719</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07017496593812653</v>
+        <v>0.07326472175266151</v>
       </c>
       <c r="C52">
-        <v>14278.18027581276</v>
+        <v>10580.24218222724</v>
       </c>
       <c r="D52">
-        <v>29823.33027581276</v>
+        <v>26468.23318222724</v>
       </c>
       <c r="E52">
-        <v>1770.850000000002</v>
+        <v>2113.691000000003</v>
       </c>
       <c r="F52">
-        <v>17142.05</v>
+        <v>17484.891</v>
       </c>
       <c r="G52">
         <v>1596.9</v>
@@ -5557,45 +5557,45 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M52">
-        <v>1098.805405</v>
+        <v>1257.1636629</v>
       </c>
       <c r="N52">
-        <v>1109.125207244898</v>
+        <v>950.766949344898</v>
       </c>
       <c r="O52">
-        <v>244.0075455938776</v>
+        <v>209.1687288558776</v>
       </c>
       <c r="P52">
-        <v>865.1176616510205</v>
+        <v>741.5982204890204</v>
       </c>
       <c r="Q52">
-        <v>2363.717661651021</v>
+        <v>2240.19822048902</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09035193187625305</v>
+        <v>0.09114877908706429</v>
       </c>
       <c r="T52">
-        <v>1.028912976356883</v>
+        <v>1.047315914250907</v>
       </c>
       <c r="U52">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V52">
         <v>0.22</v>
       </c>
       <c r="W52">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y52">
-        <v>2.009391837897719</v>
+        <v>1.756279375074911</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07326472175266151</v>
+        <v>0.07489431756719647</v>
       </c>
       <c r="C53">
-        <v>10580.24218222724</v>
+        <v>8754.894438005664</v>
       </c>
       <c r="D53">
-        <v>26468.23318222724</v>
+        <v>24985.72643800567</v>
       </c>
       <c r="E53">
-        <v>2113.691000000003</v>
+        <v>2456.532000000003</v>
       </c>
       <c r="F53">
-        <v>17484.891</v>
+        <v>17827.732</v>
       </c>
       <c r="G53">
         <v>1596.9</v>
@@ -5639,45 +5639,45 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M53">
-        <v>1257.1636629</v>
+        <v>1351.3420856</v>
       </c>
       <c r="N53">
-        <v>950.766949344898</v>
+        <v>856.5885266448979</v>
       </c>
       <c r="O53">
-        <v>209.1687288558776</v>
+        <v>188.4494758618775</v>
       </c>
       <c r="P53">
-        <v>741.5982204890204</v>
+        <v>668.1390507830204</v>
       </c>
       <c r="Q53">
-        <v>2240.19822048902</v>
+        <v>2166.739050783021</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09114877908706429</v>
+        <v>0.09197882826499262</v>
       </c>
       <c r="T53">
-        <v>1.047315914250907</v>
+        <v>1.066485641223848</v>
       </c>
       <c r="U53">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V53">
         <v>0.22</v>
       </c>
       <c r="W53">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y53">
-        <v>1.756279375074911</v>
+        <v>1.633879856013342</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07489431756719647</v>
+        <v>0.07497249338173144</v>
       </c>
       <c r="C54">
-        <v>8754.894438005664</v>
+        <v>8345.097230646916</v>
       </c>
       <c r="D54">
-        <v>24985.72643800567</v>
+        <v>24918.77023064692</v>
       </c>
       <c r="E54">
-        <v>2456.532000000003</v>
+        <v>2799.373000000003</v>
       </c>
       <c r="F54">
-        <v>17827.732</v>
+        <v>18170.573</v>
       </c>
       <c r="G54">
         <v>1596.9</v>
@@ -5721,28 +5721,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M54">
-        <v>1351.3420856</v>
+        <v>1377.3294334</v>
       </c>
       <c r="N54">
-        <v>856.5885266448979</v>
+        <v>830.601178844898</v>
       </c>
       <c r="O54">
-        <v>188.4494758618775</v>
+        <v>182.7322593458776</v>
       </c>
       <c r="P54">
-        <v>668.1390507830204</v>
+        <v>647.8689194990204</v>
       </c>
       <c r="Q54">
-        <v>2166.739050783021</v>
+        <v>2146.468919499021</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09197882826499262</v>
+        <v>0.09284419868453497</v>
       </c>
       <c r="T54">
-        <v>1.066485641223848</v>
+        <v>1.086471101259468</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.633879856013342</v>
+        <v>1.60305193420177</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07497249338173144</v>
+        <v>0.07505066919626641</v>
       </c>
       <c r="C55">
-        <v>8345.097230646916</v>
+        <v>7935.6579197871</v>
       </c>
       <c r="D55">
-        <v>24918.77023064692</v>
+        <v>24852.1719197871</v>
       </c>
       <c r="E55">
-        <v>2799.373000000003</v>
+        <v>3142.214000000004</v>
       </c>
       <c r="F55">
-        <v>18170.573</v>
+        <v>18513.414</v>
       </c>
       <c r="G55">
         <v>1596.9</v>
@@ -5803,28 +5803,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M55">
-        <v>1377.3294334</v>
+        <v>1403.3167812</v>
       </c>
       <c r="N55">
-        <v>830.601178844898</v>
+        <v>804.613831044898</v>
       </c>
       <c r="O55">
-        <v>182.7322593458776</v>
+        <v>177.0150428298776</v>
       </c>
       <c r="P55">
-        <v>647.8689194990204</v>
+        <v>627.5987882150205</v>
       </c>
       <c r="Q55">
-        <v>2146.468919499021</v>
+        <v>2126.198788215021</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09284419868453497</v>
+        <v>0.09374719390492696</v>
       </c>
       <c r="T55">
-        <v>1.086471101259468</v>
+        <v>1.107325494340115</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.60305193420177</v>
+        <v>1.573365787272107</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07505066919626641</v>
+        <v>0.07512884501080137</v>
       </c>
       <c r="C56">
-        <v>7935.6579197871</v>
+        <v>7526.573643514992</v>
       </c>
       <c r="D56">
-        <v>24852.1719197871</v>
+        <v>24785.928643515</v>
       </c>
       <c r="E56">
-        <v>3142.214000000004</v>
+        <v>3485.055000000004</v>
       </c>
       <c r="F56">
-        <v>18513.414</v>
+        <v>18856.255</v>
       </c>
       <c r="G56">
         <v>1596.9</v>
@@ -5885,28 +5885,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M56">
-        <v>1403.3167812</v>
+        <v>1429.304129000001</v>
       </c>
       <c r="N56">
-        <v>804.613831044898</v>
+        <v>778.6264832448978</v>
       </c>
       <c r="O56">
-        <v>177.0150428298776</v>
+        <v>171.2978263138775</v>
       </c>
       <c r="P56">
-        <v>627.5987882150205</v>
+        <v>607.3286569310203</v>
       </c>
       <c r="Q56">
-        <v>2126.198788215021</v>
+        <v>2105.92865693102</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09374719390492696</v>
+        <v>0.09469032224622526</v>
       </c>
       <c r="T56">
-        <v>1.107325494340115</v>
+        <v>1.129106749335457</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.573365787272107</v>
+        <v>1.544759136594433</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07512884501080137</v>
+        <v>0.07520702082533634</v>
       </c>
       <c r="C57">
-        <v>7526.573643514992</v>
+        <v>7117.841570351848</v>
       </c>
       <c r="D57">
-        <v>24785.928643515</v>
+        <v>24720.03757035185</v>
       </c>
       <c r="E57">
-        <v>3485.055000000004</v>
+        <v>3827.896000000004</v>
       </c>
       <c r="F57">
-        <v>18856.255</v>
+        <v>19199.09600000001</v>
       </c>
       <c r="G57">
         <v>1596.9</v>
@@ -5967,28 +5967,28 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M57">
-        <v>1429.304129000001</v>
+        <v>1455.291476800001</v>
       </c>
       <c r="N57">
-        <v>778.6264832448978</v>
+        <v>752.6391354448979</v>
       </c>
       <c r="O57">
-        <v>171.2978263138775</v>
+        <v>165.5806097978775</v>
       </c>
       <c r="P57">
-        <v>607.3286569310203</v>
+        <v>587.0585256470204</v>
       </c>
       <c r="Q57">
-        <v>2105.92865693102</v>
+        <v>2085.65852564702</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09469032224622526</v>
+        <v>0.09567632005758259</v>
       </c>
       <c r="T57">
-        <v>1.129106749335457</v>
+        <v>1.151878061376041</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.544759136594433</v>
+        <v>1.517174152012389</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07520702082533634</v>
+        <v>0.08159851663987132</v>
       </c>
       <c r="C58">
-        <v>7117.841570351848</v>
+        <v>2361.465276264335</v>
       </c>
       <c r="D58">
-        <v>24720.03757035185</v>
+        <v>20306.50227626434</v>
       </c>
       <c r="E58">
-        <v>3827.896000000004</v>
+        <v>4170.737000000005</v>
       </c>
       <c r="F58">
-        <v>19199.09600000001</v>
+        <v>19541.93700000001</v>
       </c>
       <c r="G58">
         <v>1596.9</v>
@@ -6049,45 +6049,45 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M58">
-        <v>1455.291476800001</v>
+        <v>1758.774330000001</v>
       </c>
       <c r="N58">
-        <v>752.6391354448979</v>
+        <v>449.1562822448977</v>
       </c>
       <c r="O58">
-        <v>165.5806097978775</v>
+        <v>98.8143820938775</v>
       </c>
       <c r="P58">
-        <v>587.0585256470204</v>
+        <v>350.3419001510202</v>
       </c>
       <c r="Q58">
-        <v>2085.65852564702</v>
+        <v>1848.94190015102</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09567632005758259</v>
+        <v>0.09670817823225886</v>
       </c>
       <c r="T58">
-        <v>1.151878061376041</v>
+        <v>1.175708504209211</v>
       </c>
       <c r="U58">
-        <v>0.07580000000000001</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V58">
         <v>0.22</v>
       </c>
       <c r="W58">
-        <v>0.05912400000000001</v>
+        <v>0.07020000000000001</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y58">
-        <v>1.517174152012389</v>
+        <v>1.25538028079185</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08159851663987132</v>
+        <v>0.09589491198721192</v>
       </c>
       <c r="C59">
-        <v>2361.465276264335</v>
+        <v>-3776.570747478927</v>
       </c>
       <c r="D59">
-        <v>20306.50227626434</v>
+        <v>14511.30725252108</v>
       </c>
       <c r="E59">
-        <v>4170.737000000005</v>
+        <v>4513.578000000005</v>
       </c>
       <c r="F59">
-        <v>19541.93700000001</v>
+        <v>19884.77800000001</v>
       </c>
       <c r="G59">
         <v>1596.9</v>
@@ -6131,45 +6131,45 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M59">
-        <v>1758.774330000001</v>
+        <v>2358.334670800001</v>
       </c>
       <c r="N59">
-        <v>449.1562822448977</v>
+        <v>-150.4040585551024</v>
       </c>
       <c r="O59">
-        <v>98.8143820938775</v>
+        <v>-33.08889288212254</v>
       </c>
       <c r="P59">
-        <v>350.3419001510202</v>
+        <v>-117.3151656729799</v>
       </c>
       <c r="Q59">
-        <v>1848.94190015102</v>
+        <v>1381.28483432702</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09670817823225886</v>
+        <v>0.09827412818149699</v>
       </c>
       <c r="T59">
-        <v>1.175708504209211</v>
+        <v>1.211873630057667</v>
       </c>
       <c r="U59">
-        <v>0.09000000000000001</v>
+        <v>0.1186</v>
       </c>
       <c r="V59">
-        <v>0.22</v>
+        <v>0.2059693820000119</v>
       </c>
       <c r="W59">
-        <v>0.07020000000000001</v>
+        <v>0.09417203129479859</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y59">
-        <v>1.25538028079185</v>
+        <v>0.9362244636364176</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09589491198721191</v>
+        <v>0.09662291198721192</v>
       </c>
       <c r="C60">
-        <v>-3776.570747478916</v>
+        <v>-4327.275312685366</v>
       </c>
       <c r="D60">
-        <v>14511.30725252109</v>
+        <v>14303.44368731464</v>
       </c>
       <c r="E60">
-        <v>4513.578000000001</v>
+        <v>4856.419000000002</v>
       </c>
       <c r="F60">
-        <v>19884.778</v>
+        <v>20227.619</v>
       </c>
       <c r="G60">
         <v>1596.9</v>
@@ -6213,37 +6213,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M60">
-        <v>2358.3346708</v>
+        <v>2398.9956134</v>
       </c>
       <c r="N60">
-        <v>-150.404058555102</v>
+        <v>-191.065001155102</v>
       </c>
       <c r="O60">
-        <v>-33.08889288212244</v>
+        <v>-42.03430025412244</v>
       </c>
       <c r="P60">
-        <v>-117.3151656729795</v>
+        <v>-149.0307009009796</v>
       </c>
       <c r="Q60">
-        <v>1381.28483432702</v>
+        <v>1349.56929909902</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.09827412818149697</v>
+        <v>0.09955398496641153</v>
       </c>
       <c r="T60">
-        <v>1.211873630057667</v>
+        <v>1.241431523473707</v>
       </c>
       <c r="U60">
         <v>0.1186</v>
       </c>
       <c r="V60">
-        <v>0.2059693820000119</v>
+        <v>0.2024783755254355</v>
       </c>
       <c r="W60">
-        <v>0.09417203129479859</v>
+        <v>0.09458606466268336</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.9362244636364179</v>
+        <v>0.920356252388343</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09662291198721192</v>
+        <v>0.09735091198721191</v>
       </c>
       <c r="C61">
-        <v>-4327.275312685366</v>
+        <v>-4872.108995316239</v>
       </c>
       <c r="D61">
-        <v>14303.44368731464</v>
+        <v>14101.45100468376</v>
       </c>
       <c r="E61">
-        <v>4856.419000000002</v>
+        <v>5199.260000000002</v>
       </c>
       <c r="F61">
-        <v>20227.619</v>
+        <v>20570.46</v>
       </c>
       <c r="G61">
         <v>1596.9</v>
@@ -6295,37 +6295,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M61">
-        <v>2398.9956134</v>
+        <v>2439.656556</v>
       </c>
       <c r="N61">
-        <v>-191.065001155102</v>
+        <v>-231.725943755102</v>
       </c>
       <c r="O61">
-        <v>-42.03430025412244</v>
+        <v>-50.97970762612243</v>
       </c>
       <c r="P61">
-        <v>-149.0307009009796</v>
+        <v>-180.7462361289795</v>
       </c>
       <c r="Q61">
-        <v>1349.56929909902</v>
+        <v>1317.85376387102</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.09955398496641153</v>
+        <v>0.1008978345905718</v>
       </c>
       <c r="T61">
-        <v>1.241431523473707</v>
+        <v>1.27246731156055</v>
       </c>
       <c r="U61">
         <v>0.1186</v>
       </c>
       <c r="V61">
-        <v>0.2024783755254355</v>
+        <v>0.1991037359333449</v>
       </c>
       <c r="W61">
-        <v>0.09458606466268336</v>
+        <v>0.0949862969183053</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.920356252388343</v>
+        <v>0.9050169815152039</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09735091198721191</v>
+        <v>0.09807891198721191</v>
       </c>
       <c r="C62">
-        <v>-4872.108995316239</v>
+        <v>-5411.317056932232</v>
       </c>
       <c r="D62">
-        <v>14101.45100468376</v>
+        <v>13905.08394306777</v>
       </c>
       <c r="E62">
-        <v>5199.260000000002</v>
+        <v>5542.101000000002</v>
       </c>
       <c r="F62">
-        <v>20570.46</v>
+        <v>20913.301</v>
       </c>
       <c r="G62">
         <v>1596.9</v>
@@ -6377,37 +6377,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M62">
-        <v>2439.656556</v>
+        <v>2480.317498600001</v>
       </c>
       <c r="N62">
-        <v>-231.725943755102</v>
+        <v>-272.3868863551024</v>
       </c>
       <c r="O62">
-        <v>-50.97970762612243</v>
+        <v>-59.92511499812254</v>
       </c>
       <c r="P62">
-        <v>-180.7462361289795</v>
+        <v>-212.4617713569799</v>
       </c>
       <c r="Q62">
-        <v>1317.85376387102</v>
+        <v>1286.13822864302</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1008978345905718</v>
+        <v>0.1023105995800737</v>
       </c>
       <c r="T62">
-        <v>1.27246731156055</v>
+        <v>1.305094678523641</v>
       </c>
       <c r="U62">
         <v>0.1186</v>
       </c>
       <c r="V62">
-        <v>0.1991037359333449</v>
+        <v>0.1958397402623064</v>
       </c>
       <c r="W62">
-        <v>0.0949862969183053</v>
+        <v>0.09537340680489047</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.9050169815152039</v>
+        <v>0.8901806375559381</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09807891198721191</v>
+        <v>0.09880691198721192</v>
       </c>
       <c r="C63">
-        <v>-5411.317056932232</v>
+        <v>-5945.131285348096</v>
       </c>
       <c r="D63">
-        <v>13905.08394306777</v>
+        <v>13714.11071465191</v>
       </c>
       <c r="E63">
-        <v>5542.101000000002</v>
+        <v>5884.942000000003</v>
       </c>
       <c r="F63">
-        <v>20913.301</v>
+        <v>21256.142</v>
       </c>
       <c r="G63">
         <v>1596.9</v>
@@ -6459,37 +6459,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M63">
-        <v>2480.317498600001</v>
+        <v>2520.978441200001</v>
       </c>
       <c r="N63">
-        <v>-272.3868863551024</v>
+        <v>-313.0478289551024</v>
       </c>
       <c r="O63">
-        <v>-59.92511499812254</v>
+        <v>-68.87052237012253</v>
       </c>
       <c r="P63">
-        <v>-212.4617713569799</v>
+        <v>-244.1773065849799</v>
       </c>
       <c r="Q63">
-        <v>1286.13822864302</v>
+        <v>1254.42269341502</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1023105995800737</v>
+        <v>0.1037977206216546</v>
       </c>
       <c r="T63">
-        <v>1.305094678523641</v>
+        <v>1.339439275326895</v>
       </c>
       <c r="U63">
         <v>0.1186</v>
       </c>
       <c r="V63">
-        <v>0.1958397402623064</v>
+        <v>0.1926810347742047</v>
       </c>
       <c r="W63">
-        <v>0.09537340680489047</v>
+        <v>0.09574802927577933</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8901806375559381</v>
+        <v>0.875822885337294</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09880691198721192</v>
+        <v>0.09953491198721191</v>
       </c>
       <c r="C64">
-        <v>-5945.131285348096</v>
+        <v>-6473.770907343469</v>
       </c>
       <c r="D64">
-        <v>13714.11071465191</v>
+        <v>13528.31209265654</v>
       </c>
       <c r="E64">
-        <v>5884.942000000003</v>
+        <v>6227.783000000003</v>
       </c>
       <c r="F64">
-        <v>21256.142</v>
+        <v>21598.983</v>
       </c>
       <c r="G64">
         <v>1596.9</v>
@@ -6541,37 +6541,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M64">
-        <v>2520.978441200001</v>
+        <v>2561.639383800001</v>
       </c>
       <c r="N64">
-        <v>-313.0478289551024</v>
+        <v>-353.7087715551024</v>
       </c>
       <c r="O64">
-        <v>-68.87052237012253</v>
+        <v>-77.81592974212253</v>
       </c>
       <c r="P64">
-        <v>-244.1773065849799</v>
+        <v>-275.8928418129799</v>
       </c>
       <c r="Q64">
-        <v>1254.42269341502</v>
+        <v>1222.70715818702</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1037977206216546</v>
+        <v>0.105365226584402</v>
       </c>
       <c r="T64">
-        <v>1.339439275326895</v>
+        <v>1.375640336822217</v>
       </c>
       <c r="U64">
         <v>0.1186</v>
       </c>
       <c r="V64">
-        <v>0.1926810347742047</v>
+        <v>0.1896226056508046</v>
       </c>
       <c r="W64">
-        <v>0.09574802927577933</v>
+        <v>0.09611075896981458</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.875822885337294</v>
+        <v>0.8619209347763845</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09953491198721191</v>
+        <v>0.1002629119872119</v>
       </c>
       <c r="C65">
-        <v>-6473.770907343469</v>
+        <v>-6997.443428173026</v>
       </c>
       <c r="D65">
-        <v>13528.31209265654</v>
+        <v>13347.48057182698</v>
       </c>
       <c r="E65">
-        <v>6227.783000000003</v>
+        <v>6570.624000000003</v>
       </c>
       <c r="F65">
-        <v>21598.983</v>
+        <v>21941.824</v>
       </c>
       <c r="G65">
         <v>1596.9</v>
@@ -6623,37 +6623,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M65">
-        <v>2561.639383800001</v>
+        <v>2602.300326400001</v>
       </c>
       <c r="N65">
-        <v>-353.7087715551024</v>
+        <v>-394.3697141551024</v>
       </c>
       <c r="O65">
-        <v>-77.81592974212253</v>
+        <v>-86.76133711412254</v>
       </c>
       <c r="P65">
-        <v>-275.8928418129799</v>
+        <v>-307.6083770409799</v>
       </c>
       <c r="Q65">
-        <v>1222.70715818702</v>
+        <v>1190.99162295902</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.105365226584402</v>
+        <v>0.1070198162117465</v>
       </c>
       <c r="T65">
-        <v>1.375640336822217</v>
+        <v>1.413852568400611</v>
       </c>
       <c r="U65">
         <v>0.1186</v>
       </c>
       <c r="V65">
-        <v>0.1896226056508046</v>
+        <v>0.1866597524375108</v>
       </c>
       <c r="W65">
-        <v>0.09611075896981458</v>
+        <v>0.09646215336091123</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8619209347763845</v>
+        <v>0.8484534201705035</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1002629119872119</v>
+        <v>0.1009909119872119</v>
       </c>
       <c r="C66">
-        <v>-6997.443428173026</v>
+        <v>-7516.345404634907</v>
       </c>
       <c r="D66">
-        <v>13347.48057182698</v>
+        <v>13171.4195953651</v>
       </c>
       <c r="E66">
-        <v>6570.624000000003</v>
+        <v>6913.465000000004</v>
       </c>
       <c r="F66">
-        <v>21941.824</v>
+        <v>22284.665</v>
       </c>
       <c r="G66">
         <v>1596.9</v>
@@ -6705,37 +6705,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M66">
-        <v>2602.300326400001</v>
+        <v>2642.961269000001</v>
       </c>
       <c r="N66">
-        <v>-394.3697141551024</v>
+        <v>-435.0306567551024</v>
       </c>
       <c r="O66">
-        <v>-86.76133711412254</v>
+        <v>-95.70674448612253</v>
       </c>
       <c r="P66">
-        <v>-307.6083770409799</v>
+        <v>-339.3239122689799</v>
       </c>
       <c r="Q66">
-        <v>1190.99162295902</v>
+        <v>1159.27608773102</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1070198162117465</v>
+        <v>0.1087689538177964</v>
       </c>
       <c r="T66">
-        <v>1.413852568400611</v>
+        <v>1.454248356069201</v>
       </c>
       <c r="U66">
         <v>0.1186</v>
       </c>
       <c r="V66">
-        <v>0.1866597524375108</v>
+        <v>0.1837880639384722</v>
       </c>
       <c r="W66">
-        <v>0.09646215336091123</v>
+        <v>0.09680273561689721</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8484534201705035</v>
+        <v>0.8354002906294189</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1009909119872119</v>
+        <v>0.1017189119872119</v>
       </c>
       <c r="C67">
-        <v>-7516.345404634907</v>
+        <v>-8030.663157752324</v>
       </c>
       <c r="D67">
-        <v>13171.4195953651</v>
+        <v>12999.94284224768</v>
       </c>
       <c r="E67">
-        <v>6913.465000000004</v>
+        <v>7256.306000000004</v>
       </c>
       <c r="F67">
-        <v>22284.665</v>
+        <v>22627.506</v>
       </c>
       <c r="G67">
         <v>1596.9</v>
@@ -6787,37 +6787,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M67">
-        <v>2642.961269000001</v>
+        <v>2683.622211600001</v>
       </c>
       <c r="N67">
-        <v>-435.0306567551024</v>
+        <v>-475.6915993551024</v>
       </c>
       <c r="O67">
-        <v>-95.70674448612253</v>
+        <v>-104.6521518581225</v>
       </c>
       <c r="P67">
-        <v>-339.3239122689799</v>
+        <v>-371.0394474969799</v>
       </c>
       <c r="Q67">
-        <v>1159.27608773102</v>
+        <v>1127.56055250302</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1087689538177964</v>
+        <v>0.110620981871261</v>
       </c>
       <c r="T67">
-        <v>1.454248356069201</v>
+        <v>1.497020366541824</v>
       </c>
       <c r="U67">
         <v>0.1186</v>
       </c>
       <c r="V67">
-        <v>0.1837880639384722</v>
+        <v>0.1810033963030408</v>
       </c>
       <c r="W67">
-        <v>0.09680273561689721</v>
+        <v>0.09713299719845937</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8354002906294189</v>
+        <v>0.8227427104683671</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1017189119872119</v>
+        <v>0.1024469119872119</v>
       </c>
       <c r="C68">
-        <v>-8030.663157752324</v>
+        <v>-8540.573430500906</v>
       </c>
       <c r="D68">
-        <v>12999.94284224768</v>
+        <v>12832.8735694991</v>
       </c>
       <c r="E68">
-        <v>7256.306000000004</v>
+        <v>7599.147000000004</v>
       </c>
       <c r="F68">
-        <v>22627.506</v>
+        <v>22970.34700000001</v>
       </c>
       <c r="G68">
         <v>1596.9</v>
@@ -6869,37 +6869,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M68">
-        <v>2683.622211600001</v>
+        <v>2724.283154200001</v>
       </c>
       <c r="N68">
-        <v>-475.6915993551024</v>
+        <v>-516.3525419551024</v>
       </c>
       <c r="O68">
-        <v>-104.6521518581225</v>
+        <v>-113.5975592301225</v>
       </c>
       <c r="P68">
-        <v>-371.0394474969799</v>
+        <v>-402.7549827249799</v>
       </c>
       <c r="Q68">
-        <v>1127.56055250302</v>
+        <v>1095.84501727502</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.110620981871261</v>
+        <v>0.112585254049178</v>
       </c>
       <c r="T68">
-        <v>1.497020366541824</v>
+        <v>1.542384620073394</v>
       </c>
       <c r="U68">
         <v>0.1186</v>
       </c>
       <c r="V68">
-        <v>0.1810033963030408</v>
+        <v>0.1783018530746372</v>
       </c>
       <c r="W68">
-        <v>0.09713299719845937</v>
+        <v>0.09745340022534804</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8227427104683671</v>
+        <v>0.810462968521078</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1024469119872119</v>
+        <v>0.160294922948553</v>
       </c>
       <c r="C69">
-        <v>-8540.573430500906</v>
+        <v>-15367.1622840844</v>
       </c>
       <c r="D69">
-        <v>12832.8735694991</v>
+        <v>6349.125715915604</v>
       </c>
       <c r="E69">
-        <v>7599.147000000004</v>
+        <v>7941.988000000005</v>
       </c>
       <c r="F69">
-        <v>22970.34700000001</v>
+        <v>23313.18800000001</v>
       </c>
       <c r="G69">
         <v>1596.9</v>
@@ -6951,45 +6951,45 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M69">
-        <v>2724.283154200001</v>
+        <v>4681.288150400002</v>
       </c>
       <c r="N69">
-        <v>-516.3525419551024</v>
+        <v>-2473.357538155103</v>
       </c>
       <c r="O69">
-        <v>-113.5975592301225</v>
+        <v>-544.1386583941227</v>
       </c>
       <c r="P69">
-        <v>-402.7549827249799</v>
+        <v>-1929.218879760981</v>
       </c>
       <c r="Q69">
-        <v>1095.84501727502</v>
+        <v>-430.6188797609807</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.112585254049178</v>
+        <v>0.1184973274924055</v>
       </c>
       <c r="T69">
-        <v>1.542384620073394</v>
+        <v>1.678922112988581</v>
       </c>
       <c r="U69">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1783018530746372</v>
+        <v>0.1037630496324761</v>
       </c>
       <c r="W69">
-        <v>0.09745340022534804</v>
+        <v>0.1799643796337988</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y69">
-        <v>0.810462968521078</v>
+        <v>0.4716502256021642</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.160294922948553</v>
+        <v>0.161844922948553</v>
       </c>
       <c r="C70">
-        <v>-15367.1622840844</v>
+        <v>-15794.80789776002</v>
       </c>
       <c r="D70">
-        <v>6349.125715915604</v>
+        <v>6264.321102239984</v>
       </c>
       <c r="E70">
-        <v>7941.988000000005</v>
+        <v>8284.829000000005</v>
       </c>
       <c r="F70">
-        <v>23313.18800000001</v>
+        <v>23656.02900000001</v>
       </c>
       <c r="G70">
         <v>1596.9</v>
@@ -7033,37 +7033,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M70">
-        <v>4681.288150400002</v>
+        <v>4750.130623200002</v>
       </c>
       <c r="N70">
-        <v>-2473.357538155103</v>
+        <v>-2542.200010955103</v>
       </c>
       <c r="O70">
-        <v>-544.1386583941227</v>
+        <v>-559.2840024101228</v>
       </c>
       <c r="P70">
-        <v>-1929.218879760981</v>
+        <v>-1982.91600854498</v>
       </c>
       <c r="Q70">
-        <v>-430.6188797609807</v>
+        <v>-484.3160085449804</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1184973274924055</v>
+        <v>0.1208424025728057</v>
       </c>
       <c r="T70">
-        <v>1.678922112988581</v>
+        <v>1.733080890826922</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1037630496324761</v>
+        <v>0.102259237318962</v>
       </c>
       <c r="W70">
-        <v>0.1799643796337988</v>
+        <v>0.1802663451463525</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4716502256021642</v>
+        <v>0.4648147150861908</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.161844922948553</v>
+        <v>0.163394922948553</v>
       </c>
       <c r="C71">
-        <v>-15794.80789776002</v>
+        <v>-16220.21791915153</v>
       </c>
       <c r="D71">
-        <v>6264.321102239984</v>
+        <v>6181.752080848476</v>
       </c>
       <c r="E71">
-        <v>8284.829000000005</v>
+        <v>8627.670000000006</v>
       </c>
       <c r="F71">
-        <v>23656.02900000001</v>
+        <v>23998.87000000001</v>
       </c>
       <c r="G71">
         <v>1596.9</v>
@@ -7115,37 +7115,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M71">
-        <v>4750.130623200002</v>
+        <v>4818.973096000002</v>
       </c>
       <c r="N71">
-        <v>-2542.200010955103</v>
+        <v>-2611.042483755103</v>
       </c>
       <c r="O71">
-        <v>-559.2840024101228</v>
+        <v>-574.4293464261227</v>
       </c>
       <c r="P71">
-        <v>-1982.91600854498</v>
+        <v>-2036.61313732898</v>
       </c>
       <c r="Q71">
-        <v>-484.3160085449804</v>
+        <v>-538.0131373289805</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1208424025728057</v>
+        <v>0.1233438159918992</v>
       </c>
       <c r="T71">
-        <v>1.733080890826922</v>
+        <v>1.790850253854486</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.102259237318962</v>
+        <v>0.1007983910715482</v>
       </c>
       <c r="W71">
-        <v>0.1802663451463525</v>
+        <v>0.1805596830728331</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4648147150861908</v>
+        <v>0.4581745048706737</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.163394922948553</v>
+        <v>0.164944922948553</v>
       </c>
       <c r="C72">
-        <v>-16220.21791915153</v>
+        <v>-16643.47959917877</v>
       </c>
       <c r="D72">
-        <v>6181.752080848476</v>
+        <v>6101.331400821241</v>
       </c>
       <c r="E72">
-        <v>8627.670000000006</v>
+        <v>8970.511000000006</v>
       </c>
       <c r="F72">
-        <v>23998.87000000001</v>
+        <v>24341.71100000001</v>
       </c>
       <c r="G72">
         <v>1596.9</v>
@@ -7197,37 +7197,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M72">
-        <v>4818.973096000002</v>
+        <v>4887.815568800002</v>
       </c>
       <c r="N72">
-        <v>-2611.042483755103</v>
+        <v>-2679.884956555103</v>
       </c>
       <c r="O72">
-        <v>-574.4293464261227</v>
+        <v>-589.5746904421227</v>
       </c>
       <c r="P72">
-        <v>-2036.61313732898</v>
+        <v>-2090.310266112981</v>
       </c>
       <c r="Q72">
-        <v>-538.0131373289805</v>
+        <v>-591.7102661129807</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1233438159918992</v>
+        <v>0.1260177406812751</v>
       </c>
       <c r="T72">
-        <v>1.790850253854486</v>
+        <v>1.852603710883951</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1007983910715482</v>
+        <v>0.09937869542265318</v>
       </c>
       <c r="W72">
-        <v>0.1805596830728331</v>
+        <v>0.1808447579591312</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4581745048706737</v>
+        <v>0.4517213428302417</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1649449229485529</v>
+        <v>0.1664949229485529</v>
       </c>
       <c r="C73">
-        <v>-16643.47959917876</v>
+        <v>-17064.67570675279</v>
       </c>
       <c r="D73">
-        <v>6101.331400821241</v>
+        <v>6022.976293247214</v>
       </c>
       <c r="E73">
-        <v>8970.511000000002</v>
+        <v>9313.352000000003</v>
       </c>
       <c r="F73">
-        <v>24341.711</v>
+        <v>24684.552</v>
       </c>
       <c r="G73">
         <v>1596.9</v>
@@ -7279,37 +7279,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M73">
-        <v>4887.815568800001</v>
+        <v>4956.658041600001</v>
       </c>
       <c r="N73">
-        <v>-2679.884956555102</v>
+        <v>-2748.727429355102</v>
       </c>
       <c r="O73">
-        <v>-589.5746904421225</v>
+        <v>-604.7200344581225</v>
       </c>
       <c r="P73">
-        <v>-2090.31026611298</v>
+        <v>-2144.00739489698</v>
       </c>
       <c r="Q73">
-        <v>-591.7102661129798</v>
+        <v>-645.4073948969799</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1260177406812751</v>
+        <v>0.1288826599913206</v>
       </c>
       <c r="T73">
-        <v>1.85260371088395</v>
+        <v>1.918768129129806</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.09937869542265319</v>
+        <v>0.09799843576400524</v>
       </c>
       <c r="W73">
-        <v>0.1808447579591312</v>
+        <v>0.1811219140985877</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4517213428302418</v>
+        <v>0.4454474352909329</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1664949229485529</v>
+        <v>0.1680449229485529</v>
       </c>
       <c r="C74">
-        <v>-17064.67570675279</v>
+        <v>-17483.88481292324</v>
       </c>
       <c r="D74">
-        <v>6022.976293247214</v>
+        <v>5946.608187076767</v>
       </c>
       <c r="E74">
-        <v>9313.352000000003</v>
+        <v>9656.193000000003</v>
       </c>
       <c r="F74">
-        <v>24684.552</v>
+        <v>25027.393</v>
       </c>
       <c r="G74">
         <v>1596.9</v>
@@ -7361,37 +7361,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M74">
-        <v>4956.658041600001</v>
+        <v>5025.500514400001</v>
       </c>
       <c r="N74">
-        <v>-2748.727429355102</v>
+        <v>-2817.569902155102</v>
       </c>
       <c r="O74">
-        <v>-604.7200344581225</v>
+        <v>-619.8653784741225</v>
       </c>
       <c r="P74">
-        <v>-2144.00739489698</v>
+        <v>-2197.70452368098</v>
       </c>
       <c r="Q74">
-        <v>-645.4073948969799</v>
+        <v>-699.10452368098</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1288826599913206</v>
+        <v>0.1319597955465547</v>
       </c>
       <c r="T74">
-        <v>1.918768129129806</v>
+        <v>1.989833615393872</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.09799843576400524</v>
+        <v>0.09665599143847092</v>
       </c>
       <c r="W74">
-        <v>0.1811219140985877</v>
+        <v>0.1813914769191551</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4454474352909329</v>
+        <v>0.4393454156294132</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1680449229485529</v>
+        <v>0.169594922948553</v>
       </c>
       <c r="C75">
-        <v>-17483.88481292324</v>
+        <v>-17901.18155367926</v>
       </c>
       <c r="D75">
-        <v>5946.608187076767</v>
+        <v>5872.152446320743</v>
       </c>
       <c r="E75">
-        <v>9656.193000000003</v>
+        <v>9999.034000000003</v>
       </c>
       <c r="F75">
-        <v>25027.393</v>
+        <v>25370.234</v>
       </c>
       <c r="G75">
         <v>1596.9</v>
@@ -7443,37 +7443,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M75">
-        <v>5025.500514400001</v>
+        <v>5094.342987200001</v>
       </c>
       <c r="N75">
-        <v>-2817.569902155102</v>
+        <v>-2886.412374955102</v>
       </c>
       <c r="O75">
-        <v>-619.8653784741225</v>
+        <v>-635.0107224901225</v>
       </c>
       <c r="P75">
-        <v>-2197.70452368098</v>
+        <v>-2251.40165246498</v>
       </c>
       <c r="Q75">
-        <v>-699.10452368098</v>
+        <v>-752.8016524649797</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1319597955465547</v>
+        <v>0.1352736338368068</v>
       </c>
       <c r="T75">
-        <v>1.989833615393872</v>
+        <v>2.066365677524406</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.09665599143847092</v>
+        <v>0.09534982939200509</v>
       </c>
       <c r="W75">
-        <v>0.1813914769191551</v>
+        <v>0.1816537542580854</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.4393454156294132</v>
+        <v>0.433408315418205</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.169594922948553</v>
+        <v>0.1711449229485529</v>
       </c>
       <c r="C76">
-        <v>-17901.18155367926</v>
+        <v>-18316.63687325192</v>
       </c>
       <c r="D76">
-        <v>5872.152446320743</v>
+        <v>5799.538126748084</v>
       </c>
       <c r="E76">
-        <v>9999.034000000003</v>
+        <v>10341.875</v>
       </c>
       <c r="F76">
-        <v>25370.234</v>
+        <v>25713.075</v>
       </c>
       <c r="G76">
         <v>1596.9</v>
@@ -7525,37 +7525,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M76">
-        <v>5094.342987200001</v>
+        <v>5163.185460000001</v>
       </c>
       <c r="N76">
-        <v>-2886.412374955102</v>
+        <v>-2955.254847755102</v>
       </c>
       <c r="O76">
-        <v>-635.0107224901225</v>
+        <v>-650.1560665061224</v>
       </c>
       <c r="P76">
-        <v>-2251.40165246498</v>
+        <v>-2305.09878124898</v>
       </c>
       <c r="Q76">
-        <v>-752.8016524649797</v>
+        <v>-806.4987812489799</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1352736338368068</v>
+        <v>0.138852579190279</v>
       </c>
       <c r="T76">
-        <v>2.066365677524406</v>
+        <v>2.149020304625382</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.09534982939200509</v>
+        <v>0.09407849833344503</v>
       </c>
       <c r="W76">
-        <v>0.1816537542580854</v>
+        <v>0.1819090375346442</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.433408315418205</v>
+        <v>0.4276295378792956</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1711449229485529</v>
+        <v>0.1726949229485529</v>
       </c>
       <c r="C77">
-        <v>-18316.63687325192</v>
+        <v>-18730.31824958521</v>
       </c>
       <c r="D77">
-        <v>5799.538126748084</v>
+        <v>5728.697750414793</v>
       </c>
       <c r="E77">
-        <v>10341.875</v>
+        <v>10684.716</v>
       </c>
       <c r="F77">
-        <v>25713.075</v>
+        <v>26055.916</v>
       </c>
       <c r="G77">
         <v>1596.9</v>
@@ -7607,37 +7607,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M77">
-        <v>5163.185460000001</v>
+        <v>5232.027932800002</v>
       </c>
       <c r="N77">
-        <v>-2955.254847755102</v>
+        <v>-3024.097320555103</v>
       </c>
       <c r="O77">
-        <v>-650.1560665061224</v>
+        <v>-665.3014105221226</v>
       </c>
       <c r="P77">
-        <v>-2305.09878124898</v>
+        <v>-2358.79591003298</v>
       </c>
       <c r="Q77">
-        <v>-806.4987812489799</v>
+        <v>-860.1959100329805</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.138852579190279</v>
+        <v>0.142729769989874</v>
       </c>
       <c r="T77">
-        <v>2.149020304625382</v>
+        <v>2.238562817318107</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.09407849833344503</v>
+        <v>0.09284062335537337</v>
       </c>
       <c r="W77">
-        <v>0.1819090375346442</v>
+        <v>0.182157602830241</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4276295378792956</v>
+        <v>0.4220028334335153</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1726949229485529</v>
+        <v>0.174244922948553</v>
       </c>
       <c r="C78">
-        <v>-18730.31824958521</v>
+        <v>-19142.2899034819</v>
       </c>
       <c r="D78">
-        <v>5728.697750414793</v>
+        <v>5659.567096518105</v>
       </c>
       <c r="E78">
-        <v>10684.716</v>
+        <v>11027.557</v>
       </c>
       <c r="F78">
-        <v>26055.916</v>
+        <v>26398.75700000001</v>
       </c>
       <c r="G78">
         <v>1596.9</v>
@@ -7689,37 +7689,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M78">
-        <v>5232.027932800002</v>
+        <v>5300.870405600002</v>
       </c>
       <c r="N78">
-        <v>-3024.097320555103</v>
+        <v>-3092.939793355103</v>
       </c>
       <c r="O78">
-        <v>-665.3014105221226</v>
+        <v>-680.4467545381227</v>
       </c>
       <c r="P78">
-        <v>-2358.79591003298</v>
+        <v>-2412.493038816981</v>
       </c>
       <c r="Q78">
-        <v>-860.1959100329805</v>
+        <v>-913.8930388169806</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.142729769989874</v>
+        <v>0.1469441078155207</v>
       </c>
       <c r="T78">
-        <v>2.238562817318107</v>
+        <v>2.335891635462373</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.09284062335537337</v>
+        <v>0.09163490097413475</v>
       </c>
       <c r="W78">
-        <v>0.182157602830241</v>
+        <v>0.1823997118843937</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4220028334335153</v>
+        <v>0.416522277155158</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.174244922948553</v>
+        <v>0.1757949229485529</v>
       </c>
       <c r="C79">
-        <v>-19142.2899034819</v>
+        <v>-19552.61299278684</v>
       </c>
       <c r="D79">
-        <v>5659.567096518105</v>
+        <v>5592.085007213164</v>
       </c>
       <c r="E79">
-        <v>11027.557</v>
+        <v>11370.398</v>
       </c>
       <c r="F79">
-        <v>26398.75700000001</v>
+        <v>26741.59800000001</v>
       </c>
       <c r="G79">
         <v>1596.9</v>
@@ -7771,37 +7771,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M79">
-        <v>5300.870405600002</v>
+        <v>5369.712878400002</v>
       </c>
       <c r="N79">
-        <v>-3092.939793355103</v>
+        <v>-3161.782266155103</v>
       </c>
       <c r="O79">
-        <v>-680.4467545381227</v>
+        <v>-695.5920985541227</v>
       </c>
       <c r="P79">
-        <v>-2412.493038816981</v>
+        <v>-2466.19016760098</v>
       </c>
       <c r="Q79">
-        <v>-913.8930388169806</v>
+        <v>-967.5901676009803</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1469441078155207</v>
+        <v>0.1515415672616807</v>
       </c>
       <c r="T79">
-        <v>2.335891635462373</v>
+        <v>2.442068527983389</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.09163490097413475</v>
+        <v>0.09046009455138944</v>
       </c>
       <c r="W79">
-        <v>0.1823997118843937</v>
+        <v>0.182635613014081</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.416522277155158</v>
+        <v>0.4111822479608611</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1757949229485529</v>
+        <v>0.177344922948553</v>
       </c>
       <c r="C80">
-        <v>-19552.61299278684</v>
+        <v>-19961.34579284187</v>
       </c>
       <c r="D80">
-        <v>5592.085007213164</v>
+        <v>5526.193207158132</v>
       </c>
       <c r="E80">
-        <v>11370.398</v>
+        <v>11713.23900000001</v>
       </c>
       <c r="F80">
-        <v>26741.59800000001</v>
+        <v>27084.43900000001</v>
       </c>
       <c r="G80">
         <v>1596.9</v>
@@ -7853,37 +7853,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M80">
-        <v>5369.712878400002</v>
+        <v>5438.555351200001</v>
       </c>
       <c r="N80">
-        <v>-3161.782266155103</v>
+        <v>-3230.624738955103</v>
       </c>
       <c r="O80">
-        <v>-695.5920985541227</v>
+        <v>-710.7374425701227</v>
       </c>
       <c r="P80">
-        <v>-2466.19016760098</v>
+        <v>-2519.88729638498</v>
       </c>
       <c r="Q80">
-        <v>-967.5901676009803</v>
+        <v>-1021.28729638498</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1515415672616807</v>
+        <v>0.1565768799884275</v>
       </c>
       <c r="T80">
-        <v>2.442068527983389</v>
+        <v>2.558357505506408</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.09046009455138944</v>
+        <v>0.08931503006339717</v>
       </c>
       <c r="W80">
-        <v>0.182635613014081</v>
+        <v>0.1828655419632699</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4111822479608611</v>
+        <v>0.405977409379078</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.177344922948553</v>
+        <v>0.178894922948553</v>
       </c>
       <c r="C81">
-        <v>-19961.34579284187</v>
+        <v>-20368.54386433142</v>
       </c>
       <c r="D81">
-        <v>5526.193207158132</v>
+        <v>5461.836135668589</v>
       </c>
       <c r="E81">
-        <v>11713.23900000001</v>
+        <v>12056.08000000001</v>
       </c>
       <c r="F81">
-        <v>27084.43900000001</v>
+        <v>27427.28000000001</v>
       </c>
       <c r="G81">
         <v>1596.9</v>
@@ -7935,37 +7935,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M81">
-        <v>5438.555351200001</v>
+        <v>5507.397824000001</v>
       </c>
       <c r="N81">
-        <v>-3230.624738955103</v>
+        <v>-3299.467211755103</v>
       </c>
       <c r="O81">
-        <v>-710.7374425701227</v>
+        <v>-725.8827865861227</v>
       </c>
       <c r="P81">
-        <v>-2519.88729638498</v>
+        <v>-2573.58442516898</v>
       </c>
       <c r="Q81">
-        <v>-1021.28729638498</v>
+        <v>-1074.984425168981</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1565768799884275</v>
+        <v>0.1621157239878488</v>
       </c>
       <c r="T81">
-        <v>2.558357505506408</v>
+        <v>2.686275380781729</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.08931503006339717</v>
+        <v>0.08819859218760469</v>
       </c>
       <c r="W81">
-        <v>0.1828655419632699</v>
+        <v>0.183089722688729</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.405977409379078</v>
+        <v>0.4009026917618396</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.178894922948553</v>
+        <v>0.180444922948553</v>
       </c>
       <c r="C82">
-        <v>-20368.54386433142</v>
+        <v>-20774.2602095349</v>
       </c>
       <c r="D82">
-        <v>5461.836135668589</v>
+        <v>5398.96079046511</v>
       </c>
       <c r="E82">
-        <v>12056.08000000001</v>
+        <v>12398.92100000001</v>
       </c>
       <c r="F82">
-        <v>27427.28000000001</v>
+        <v>27770.12100000001</v>
       </c>
       <c r="G82">
         <v>1596.9</v>
@@ -8017,37 +8017,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M82">
-        <v>5507.397824000001</v>
+        <v>5576.240296800001</v>
       </c>
       <c r="N82">
-        <v>-3299.467211755103</v>
+        <v>-3368.309684555103</v>
       </c>
       <c r="O82">
-        <v>-725.8827865861227</v>
+        <v>-741.0281306021227</v>
       </c>
       <c r="P82">
-        <v>-2573.58442516898</v>
+        <v>-2627.28155395298</v>
       </c>
       <c r="Q82">
-        <v>-1074.984425168981</v>
+        <v>-1128.68155395298</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1621157239878488</v>
+        <v>0.1682376041977356</v>
       </c>
       <c r="T82">
-        <v>2.686275380781729</v>
+        <v>2.827658295559714</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.08819859218760469</v>
+        <v>0.08710972067911575</v>
       </c>
       <c r="W82">
-        <v>0.183089722688729</v>
+        <v>0.1833083680876336</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4009026917618396</v>
+        <v>0.3959532758141625</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.180444922948553</v>
+        <v>0.1819949229485529</v>
       </c>
       <c r="C83">
-        <v>-20774.2602095349</v>
+        <v>-21178.54541790955</v>
       </c>
       <c r="D83">
-        <v>5398.96079046511</v>
+        <v>5337.516582090457</v>
       </c>
       <c r="E83">
-        <v>12398.92100000001</v>
+        <v>12741.76200000001</v>
       </c>
       <c r="F83">
-        <v>27770.12100000001</v>
+        <v>28112.96200000001</v>
       </c>
       <c r="G83">
         <v>1596.9</v>
@@ -8099,37 +8099,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M83">
-        <v>5576.240296800001</v>
+        <v>5645.082769600001</v>
       </c>
       <c r="N83">
-        <v>-3368.309684555103</v>
+        <v>-3437.152157355103</v>
       </c>
       <c r="O83">
-        <v>-741.0281306021227</v>
+        <v>-756.1734746181227</v>
       </c>
       <c r="P83">
-        <v>-2627.28155395298</v>
+        <v>-2680.97868273698</v>
       </c>
       <c r="Q83">
-        <v>-1128.68155395298</v>
+        <v>-1182.37868273698</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1682376041977356</v>
+        <v>0.175039693319832</v>
       </c>
       <c r="T83">
-        <v>2.827658295559714</v>
+        <v>2.98475042309081</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.08710972067911575</v>
+        <v>0.08604740701229727</v>
       </c>
       <c r="W83">
-        <v>0.1833083680876336</v>
+        <v>0.1835216806719307</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3959532758141625</v>
+        <v>0.3911245773286239</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1819949229485529</v>
+        <v>0.183544922948553</v>
       </c>
       <c r="C84">
-        <v>-21178.54541790955</v>
+        <v>-21581.44780184404</v>
       </c>
       <c r="D84">
-        <v>5337.516582090457</v>
+        <v>5277.455198155963</v>
       </c>
       <c r="E84">
-        <v>12741.76200000001</v>
+        <v>13084.60300000001</v>
       </c>
       <c r="F84">
-        <v>28112.96200000001</v>
+        <v>28455.80300000001</v>
       </c>
       <c r="G84">
         <v>1596.9</v>
@@ -8181,37 +8181,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M84">
-        <v>5645.082769600001</v>
+        <v>5713.925242400001</v>
       </c>
       <c r="N84">
-        <v>-3437.152157355103</v>
+        <v>-3505.994630155103</v>
       </c>
       <c r="O84">
-        <v>-756.1734746181227</v>
+        <v>-771.3188186341226</v>
       </c>
       <c r="P84">
-        <v>-2680.97868273698</v>
+        <v>-2734.67581152098</v>
       </c>
       <c r="Q84">
-        <v>-1182.37868273698</v>
+        <v>-1236.075811520981</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.175039693319832</v>
+        <v>0.1826420282209987</v>
       </c>
       <c r="T84">
-        <v>2.98475042309081</v>
+        <v>3.16032397739027</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.08604740701229727</v>
+        <v>0.08501069126516116</v>
       </c>
       <c r="W84">
-        <v>0.1835216806719307</v>
+        <v>0.1837298531939557</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3911245773286239</v>
+        <v>0.3864122330234598</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.183544922948553</v>
+        <v>0.185094922948553</v>
       </c>
       <c r="C85">
-        <v>-21581.44780184404</v>
+        <v>-21983.01352334853</v>
       </c>
       <c r="D85">
-        <v>5277.455198155963</v>
+        <v>5218.730476651483</v>
       </c>
       <c r="E85">
-        <v>13084.60300000001</v>
+        <v>13427.44400000001</v>
       </c>
       <c r="F85">
-        <v>28455.80300000001</v>
+        <v>28798.64400000001</v>
       </c>
       <c r="G85">
         <v>1596.9</v>
@@ -8263,37 +8263,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M85">
-        <v>5713.925242400001</v>
+        <v>5782.767715200001</v>
       </c>
       <c r="N85">
-        <v>-3505.994630155103</v>
+        <v>-3574.837102955103</v>
       </c>
       <c r="O85">
-        <v>-771.3188186341226</v>
+        <v>-786.4641626501227</v>
       </c>
       <c r="P85">
-        <v>-2734.67581152098</v>
+        <v>-2788.37294030498</v>
       </c>
       <c r="Q85">
-        <v>-1236.075811520981</v>
+        <v>-1289.77294030498</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1826420282209987</v>
+        <v>0.1911946549848111</v>
       </c>
       <c r="T85">
-        <v>3.16032397739027</v>
+        <v>3.357844225977162</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.08501069126516116</v>
+        <v>0.0839986592262902</v>
       </c>
       <c r="W85">
-        <v>0.1837298531939557</v>
+        <v>0.1839330692273609</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3864122330234598</v>
+        <v>0.3818120873922282</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1850949229485529</v>
+        <v>0.1866449229485529</v>
       </c>
       <c r="C86">
-        <v>-21983.01352334852</v>
+        <v>-22383.28671237932</v>
       </c>
       <c r="D86">
-        <v>5218.730476651483</v>
+        <v>5161.298287620682</v>
       </c>
       <c r="E86">
-        <v>13427.444</v>
+        <v>13770.285</v>
       </c>
       <c r="F86">
-        <v>28798.644</v>
+        <v>29141.485</v>
       </c>
       <c r="G86">
         <v>1596.9</v>
@@ -8345,37 +8345,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M86">
-        <v>5782.767715200001</v>
+        <v>5851.610188000001</v>
       </c>
       <c r="N86">
-        <v>-3574.837102955102</v>
+        <v>-3643.679575755103</v>
       </c>
       <c r="O86">
-        <v>-786.4641626501225</v>
+        <v>-801.6095066661227</v>
       </c>
       <c r="P86">
-        <v>-2788.37294030498</v>
+        <v>-2842.07006908898</v>
       </c>
       <c r="Q86">
-        <v>-1289.77294030498</v>
+        <v>-1343.47006908898</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.191194654984811</v>
+        <v>0.2008876319837984</v>
       </c>
       <c r="T86">
-        <v>3.357844225977159</v>
+        <v>3.581700507708971</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.08399865922629021</v>
+        <v>0.08301043970598089</v>
       </c>
       <c r="W86">
-        <v>0.1839330692273609</v>
+        <v>0.184131503707039</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3818120873922282</v>
+        <v>0.3773201804817313</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1866449229485529</v>
+        <v>0.188194922948553</v>
       </c>
       <c r="C87">
-        <v>-22383.28671237932</v>
+        <v>-22782.30957743572</v>
       </c>
       <c r="D87">
-        <v>5161.298287620682</v>
+        <v>5105.116422564282</v>
       </c>
       <c r="E87">
-        <v>13770.285</v>
+        <v>14113.126</v>
       </c>
       <c r="F87">
-        <v>29141.485</v>
+        <v>29484.326</v>
       </c>
       <c r="G87">
         <v>1596.9</v>
@@ -8427,37 +8427,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M87">
-        <v>5851.610188000001</v>
+        <v>5920.452660800001</v>
       </c>
       <c r="N87">
-        <v>-3643.679575755103</v>
+        <v>-3712.522048555103</v>
       </c>
       <c r="O87">
-        <v>-801.6095066661227</v>
+        <v>-816.7548506821227</v>
       </c>
       <c r="P87">
-        <v>-2842.07006908898</v>
+        <v>-2895.76719787298</v>
       </c>
       <c r="Q87">
-        <v>-1343.47006908898</v>
+        <v>-1397.167197872981</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2008876319837984</v>
+        <v>0.2119653199826411</v>
       </c>
       <c r="T87">
-        <v>3.581700507708971</v>
+        <v>3.837536258259611</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.08301043970598089</v>
+        <v>0.08204520203498111</v>
       </c>
       <c r="W87">
-        <v>0.184131503707039</v>
+        <v>0.1843253234313758</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3773201804817313</v>
+        <v>0.3729327365226415</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.188194922948553</v>
+        <v>0.1897449229485529</v>
       </c>
       <c r="C88">
-        <v>-22782.30957743572</v>
+        <v>-23180.12250901126</v>
       </c>
       <c r="D88">
-        <v>5105.116422564282</v>
+        <v>5050.14449098874</v>
       </c>
       <c r="E88">
-        <v>14113.126</v>
+        <v>14455.967</v>
       </c>
       <c r="F88">
-        <v>29484.326</v>
+        <v>29827.167</v>
       </c>
       <c r="G88">
         <v>1596.9</v>
@@ -8509,37 +8509,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M88">
-        <v>5920.452660800001</v>
+        <v>5989.295133600001</v>
       </c>
       <c r="N88">
-        <v>-3712.522048555103</v>
+        <v>-3781.364521355103</v>
       </c>
       <c r="O88">
-        <v>-816.7548506821227</v>
+        <v>-831.9001946981227</v>
       </c>
       <c r="P88">
-        <v>-2895.76719787298</v>
+        <v>-2949.46432665698</v>
       </c>
       <c r="Q88">
-        <v>-1397.167197872981</v>
+        <v>-1450.86432665698</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2119653199826411</v>
+        <v>0.2247472676736136</v>
       </c>
       <c r="T88">
-        <v>3.837536258259611</v>
+        <v>4.132731355048812</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.08204520203498111</v>
+        <v>0.08110215373572846</v>
       </c>
       <c r="W88">
-        <v>0.1843253234313758</v>
+        <v>0.1845146875298657</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3729327365226415</v>
+        <v>0.3686461533442202</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1897449229485529</v>
+        <v>0.191294922948553</v>
       </c>
       <c r="C89">
-        <v>-23180.12250901126</v>
+        <v>-23576.76417643249</v>
       </c>
       <c r="D89">
-        <v>5050.14449098874</v>
+        <v>4996.343823567511</v>
       </c>
       <c r="E89">
-        <v>14455.967</v>
+        <v>14798.808</v>
       </c>
       <c r="F89">
-        <v>29827.167</v>
+        <v>30170.00800000001</v>
       </c>
       <c r="G89">
         <v>1596.9</v>
@@ -8591,37 +8591,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M89">
-        <v>5989.295133600001</v>
+        <v>6058.137606400001</v>
       </c>
       <c r="N89">
-        <v>-3781.364521355103</v>
+        <v>-3850.206994155103</v>
       </c>
       <c r="O89">
-        <v>-831.9001946981227</v>
+        <v>-847.0455387141227</v>
       </c>
       <c r="P89">
-        <v>-2949.46432665698</v>
+        <v>-3003.16145544098</v>
       </c>
       <c r="Q89">
-        <v>-1450.86432665698</v>
+        <v>-1504.56145544098</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2247472676736136</v>
+        <v>0.2396595399797481</v>
       </c>
       <c r="T89">
-        <v>4.132731355048812</v>
+        <v>4.477125634636214</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.08110215373572846</v>
+        <v>0.08018053835236791</v>
       </c>
       <c r="W89">
-        <v>0.1845146875298657</v>
+        <v>0.1846997478988445</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3686461533442202</v>
+        <v>0.3644569925107632</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.191294922948553</v>
+        <v>0.1928449229485529</v>
       </c>
       <c r="C90">
-        <v>-23576.76417643249</v>
+        <v>-23972.27161857303</v>
       </c>
       <c r="D90">
-        <v>4996.343823567511</v>
+        <v>4943.677381426975</v>
       </c>
       <c r="E90">
-        <v>14798.808</v>
+        <v>15141.649</v>
       </c>
       <c r="F90">
-        <v>30170.00800000001</v>
+        <v>30512.84900000001</v>
       </c>
       <c r="G90">
         <v>1596.9</v>
@@ -8673,37 +8673,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M90">
-        <v>6058.137606400001</v>
+        <v>6126.980079200001</v>
       </c>
       <c r="N90">
-        <v>-3850.206994155103</v>
+        <v>-3919.049466955103</v>
       </c>
       <c r="O90">
-        <v>-847.0455387141227</v>
+        <v>-862.1908827301227</v>
       </c>
       <c r="P90">
-        <v>-3003.16145544098</v>
+        <v>-3056.85858422498</v>
       </c>
       <c r="Q90">
-        <v>-1504.56145544098</v>
+        <v>-1558.25858422498</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2396595399797481</v>
+        <v>0.2572831345233615</v>
       </c>
       <c r="T90">
-        <v>4.477125634636214</v>
+        <v>4.884137055966779</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.08018053835236791</v>
+        <v>0.07927963342706042</v>
       </c>
       <c r="W90">
-        <v>0.1846997478988445</v>
+        <v>0.1848806496078463</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3644569925107632</v>
+        <v>0.3603619701230019</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1928449229485529</v>
+        <v>0.194394922948553</v>
       </c>
       <c r="C91">
-        <v>-23972.27161857303</v>
+        <v>-24366.68032889019</v>
       </c>
       <c r="D91">
-        <v>4943.677381426975</v>
+        <v>4892.109671109813</v>
       </c>
       <c r="E91">
-        <v>15141.649</v>
+        <v>15484.49000000001</v>
       </c>
       <c r="F91">
-        <v>30512.84900000001</v>
+        <v>30855.69000000001</v>
       </c>
       <c r="G91">
         <v>1596.9</v>
@@ -8755,37 +8755,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M91">
-        <v>6126.980079200001</v>
+        <v>6195.822552000001</v>
       </c>
       <c r="N91">
-        <v>-3919.049466955103</v>
+        <v>-3987.891939755103</v>
       </c>
       <c r="O91">
-        <v>-862.1908827301227</v>
+        <v>-877.3362267461226</v>
       </c>
       <c r="P91">
-        <v>-3056.85858422498</v>
+        <v>-3110.555713008981</v>
       </c>
       <c r="Q91">
-        <v>-1558.25858422498</v>
+        <v>-1611.955713008981</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2572831345233615</v>
+        <v>0.2784314479756977</v>
       </c>
       <c r="T91">
-        <v>4.884137055966779</v>
+        <v>5.372550761563457</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.07927963342706042</v>
+        <v>0.07839874861120417</v>
       </c>
       <c r="W91">
-        <v>0.1848806496078463</v>
+        <v>0.1850575312788702</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3603619701230019</v>
+        <v>0.3563579482327462</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.194394922948553</v>
+        <v>0.195944922948553</v>
       </c>
       <c r="C92">
-        <v>-24366.68032889019</v>
+        <v>-24760.02433519443</v>
       </c>
       <c r="D92">
-        <v>4892.109671109813</v>
+        <v>4841.606664805574</v>
       </c>
       <c r="E92">
-        <v>15484.49000000001</v>
+        <v>15827.33100000001</v>
       </c>
       <c r="F92">
-        <v>30855.69000000001</v>
+        <v>31198.53100000001</v>
       </c>
       <c r="G92">
         <v>1596.9</v>
@@ -8837,37 +8837,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M92">
-        <v>6195.822552000001</v>
+        <v>6264.665024800001</v>
       </c>
       <c r="N92">
-        <v>-3987.891939755103</v>
+        <v>-4056.734412555103</v>
       </c>
       <c r="O92">
-        <v>-877.3362267461226</v>
+        <v>-892.4815707621227</v>
       </c>
       <c r="P92">
-        <v>-3110.555713008981</v>
+        <v>-3164.25284179298</v>
       </c>
       <c r="Q92">
-        <v>-1611.955713008981</v>
+        <v>-1665.65284179298</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2784314479756977</v>
+        <v>0.3042793866396641</v>
       </c>
       <c r="T92">
-        <v>5.372550761563457</v>
+        <v>5.96950084618162</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.07839874861120417</v>
+        <v>0.07753722390119094</v>
       </c>
       <c r="W92">
-        <v>0.1850575312788702</v>
+        <v>0.1852305254406409</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3563579482327462</v>
+        <v>0.3524419268235952</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.195944922948553</v>
+        <v>0.197494922948553</v>
       </c>
       <c r="C93">
-        <v>-24760.02433519443</v>
+        <v>-25152.33627452833</v>
       </c>
       <c r="D93">
-        <v>4841.606664805574</v>
+        <v>4792.135725471674</v>
       </c>
       <c r="E93">
-        <v>15827.33100000001</v>
+        <v>16170.17200000001</v>
       </c>
       <c r="F93">
-        <v>31198.53100000001</v>
+        <v>31541.37200000001</v>
       </c>
       <c r="G93">
         <v>1596.9</v>
@@ -8919,37 +8919,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M93">
-        <v>6264.665024800001</v>
+        <v>6333.507497600001</v>
       </c>
       <c r="N93">
-        <v>-4056.734412555103</v>
+        <v>-4125.576885355104</v>
       </c>
       <c r="O93">
-        <v>-892.4815707621227</v>
+        <v>-907.6269147781228</v>
       </c>
       <c r="P93">
-        <v>-3164.25284179298</v>
+        <v>-3217.949970576981</v>
       </c>
       <c r="Q93">
-        <v>-1665.65284179298</v>
+        <v>-1719.349970576981</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3042793866396641</v>
+        <v>0.3365893099696222</v>
       </c>
       <c r="T93">
-        <v>5.96950084618162</v>
+        <v>6.715688451954324</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.07753722390119094</v>
+        <v>0.07669442798922148</v>
       </c>
       <c r="W93">
-        <v>0.1852305254406409</v>
+        <v>0.1853997588597643</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3524419268235952</v>
+        <v>0.348611036314643</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.197494922948553</v>
+        <v>0.199044922948553</v>
       </c>
       <c r="C94">
-        <v>-25152.33627452833</v>
+        <v>-25543.64746350141</v>
       </c>
       <c r="D94">
-        <v>4792.135725471674</v>
+        <v>4743.665536498595</v>
       </c>
       <c r="E94">
-        <v>16170.17200000001</v>
+        <v>16513.01300000001</v>
       </c>
       <c r="F94">
-        <v>31541.37200000001</v>
+        <v>31884.21300000001</v>
       </c>
       <c r="G94">
         <v>1596.9</v>
@@ -9001,37 +9001,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M94">
-        <v>6333.507497600001</v>
+        <v>6402.349970400001</v>
       </c>
       <c r="N94">
-        <v>-4125.576885355104</v>
+        <v>-4194.419358155103</v>
       </c>
       <c r="O94">
-        <v>-907.6269147781228</v>
+        <v>-922.7722587941225</v>
       </c>
       <c r="P94">
-        <v>-3217.949970576981</v>
+        <v>-3271.64709936098</v>
       </c>
       <c r="Q94">
-        <v>-1719.349970576981</v>
+        <v>-1773.04709936098</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3365893099696222</v>
+        <v>0.3781306399652826</v>
       </c>
       <c r="T94">
-        <v>6.715688451954324</v>
+        <v>7.675072516519228</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.07669442798922148</v>
+        <v>0.07586975672052017</v>
       </c>
       <c r="W94">
-        <v>0.1853997588597643</v>
+        <v>0.1855653528505196</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.348611036314643</v>
+        <v>0.344862530547819</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.199044922948553</v>
+        <v>0.200594922948553</v>
       </c>
       <c r="C95">
-        <v>-25543.64746350141</v>
+        <v>-25933.98796439923</v>
       </c>
       <c r="D95">
-        <v>4743.665536498595</v>
+        <v>4696.166035600776</v>
       </c>
       <c r="E95">
-        <v>16513.01300000001</v>
+        <v>16855.85400000001</v>
       </c>
       <c r="F95">
-        <v>31884.21300000001</v>
+        <v>32227.05400000001</v>
       </c>
       <c r="G95">
         <v>1596.9</v>
@@ -9083,37 +9083,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M95">
-        <v>6402.349970400001</v>
+        <v>6471.192443200001</v>
       </c>
       <c r="N95">
-        <v>-4194.419358155103</v>
+        <v>-4263.261830955104</v>
       </c>
       <c r="O95">
-        <v>-922.7722587941225</v>
+        <v>-937.9176028101227</v>
       </c>
       <c r="P95">
-        <v>-3271.64709936098</v>
+        <v>-3325.344228144981</v>
       </c>
       <c r="Q95">
-        <v>-1773.04709936098</v>
+        <v>-1826.744228144981</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3781306399652826</v>
+        <v>0.4335190799594964</v>
       </c>
       <c r="T95">
-        <v>7.675072516519228</v>
+        <v>8.954251269272435</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.07586975672052017</v>
+        <v>0.07506263164902528</v>
       </c>
       <c r="W95">
-        <v>0.1855653528505196</v>
+        <v>0.1857274235648757</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.344862530547819</v>
+        <v>0.3411937802228421</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.200594922948553</v>
+        <v>0.202144922948553</v>
       </c>
       <c r="C96">
-        <v>-25933.98796439923</v>
+        <v>-26323.38664736011</v>
       </c>
       <c r="D96">
-        <v>4696.166035600776</v>
+        <v>4649.608352639901</v>
       </c>
       <c r="E96">
-        <v>16855.85400000001</v>
+        <v>17198.69500000001</v>
       </c>
       <c r="F96">
-        <v>32227.05400000001</v>
+        <v>32569.89500000001</v>
       </c>
       <c r="G96">
         <v>1596.9</v>
@@ -9165,37 +9165,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M96">
-        <v>6471.192443200001</v>
+        <v>6540.034916000001</v>
       </c>
       <c r="N96">
-        <v>-4263.261830955104</v>
+        <v>-4332.104303755103</v>
       </c>
       <c r="O96">
-        <v>-937.9176028101227</v>
+        <v>-953.0629468261226</v>
       </c>
       <c r="P96">
-        <v>-3325.344228144981</v>
+        <v>-3379.04135692898</v>
       </c>
       <c r="Q96">
-        <v>-1826.744228144981</v>
+        <v>-1880.44135692898</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4335190799594964</v>
+        <v>0.511062895951396</v>
       </c>
       <c r="T96">
-        <v>8.954251269272435</v>
+        <v>10.74510152312693</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.07506263164902528</v>
+        <v>0.07427249868429869</v>
       </c>
       <c r="W96">
-        <v>0.1857274235648757</v>
+        <v>0.1858860822641928</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3411937802228421</v>
+        <v>0.3376022667468124</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.202144922948553</v>
+        <v>0.203694922948553</v>
       </c>
       <c r="C97">
-        <v>-26323.38664736011</v>
+        <v>-26711.87124888959</v>
       </c>
       <c r="D97">
-        <v>4649.608352639901</v>
+        <v>4603.964751110419</v>
       </c>
       <c r="E97">
-        <v>17198.69500000001</v>
+        <v>17541.53600000001</v>
       </c>
       <c r="F97">
-        <v>32569.89500000001</v>
+        <v>32912.73600000001</v>
       </c>
       <c r="G97">
         <v>1596.9</v>
@@ -9247,37 +9247,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M97">
-        <v>6540.034916000001</v>
+        <v>6608.877388800002</v>
       </c>
       <c r="N97">
-        <v>-4332.104303755103</v>
+        <v>-4400.946776555103</v>
       </c>
       <c r="O97">
-        <v>-953.0629468261226</v>
+        <v>-968.2082908421228</v>
       </c>
       <c r="P97">
-        <v>-3379.04135692898</v>
+        <v>-3432.738485712981</v>
       </c>
       <c r="Q97">
-        <v>-1880.44135692898</v>
+        <v>-1934.138485712981</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.511062895951396</v>
+        <v>0.6273786199392453</v>
       </c>
       <c r="T97">
-        <v>10.74510152312693</v>
+        <v>13.43137690390867</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.07427249868429869</v>
+        <v>0.0734988268230039</v>
       </c>
       <c r="W97">
-        <v>0.1858860822641928</v>
+        <v>0.1860414355739408</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3376022667468124</v>
+        <v>0.3340855764681997</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.203694922948553</v>
+        <v>0.2052449229485529</v>
       </c>
       <c r="C98">
-        <v>-26711.87124888958</v>
+        <v>-27099.46842696196</v>
       </c>
       <c r="D98">
-        <v>4603.964751110419</v>
+        <v>4559.208573038047</v>
       </c>
       <c r="E98">
-        <v>17541.536</v>
+        <v>17884.377</v>
       </c>
       <c r="F98">
-        <v>32912.736</v>
+        <v>33255.577</v>
       </c>
       <c r="G98">
         <v>1596.9</v>
@@ -9329,37 +9329,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M98">
-        <v>6608.877388800001</v>
+        <v>6677.719861600001</v>
       </c>
       <c r="N98">
-        <v>-4400.946776555103</v>
+        <v>-4469.789249355103</v>
       </c>
       <c r="O98">
-        <v>-968.2082908421228</v>
+        <v>-983.3536348581225</v>
       </c>
       <c r="P98">
-        <v>-3432.738485712981</v>
+        <v>-3486.43561449698</v>
       </c>
       <c r="Q98">
-        <v>-1934.138485712981</v>
+        <v>-1987.83561449698</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6273786199392436</v>
+        <v>0.8212381599189915</v>
       </c>
       <c r="T98">
-        <v>13.43137690390863</v>
+        <v>17.90850253854484</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.07349882682300392</v>
+        <v>0.07274110695884924</v>
       </c>
       <c r="W98">
-        <v>0.1860414355739408</v>
+        <v>0.1861935857226631</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3340855764681996</v>
+        <v>0.3306413952674966</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2052449229485529</v>
+        <v>0.206794922948553</v>
       </c>
       <c r="C99">
-        <v>-27099.46842696196</v>
+        <v>-27486.20381293876</v>
       </c>
       <c r="D99">
-        <v>4559.208573038047</v>
+        <v>4515.314187061244</v>
       </c>
       <c r="E99">
-        <v>17884.377</v>
+        <v>18227.218</v>
       </c>
       <c r="F99">
-        <v>33255.577</v>
+        <v>33598.41800000001</v>
       </c>
       <c r="G99">
         <v>1596.9</v>
@@ -9411,37 +9411,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M99">
-        <v>6677.719861600001</v>
+        <v>6746.562334400001</v>
       </c>
       <c r="N99">
-        <v>-4469.789249355103</v>
+        <v>-4538.631722155103</v>
       </c>
       <c r="O99">
-        <v>-983.3536348581225</v>
+        <v>-998.4989788741228</v>
       </c>
       <c r="P99">
-        <v>-3486.43561449698</v>
+        <v>-3540.132743280981</v>
       </c>
       <c r="Q99">
-        <v>-1987.83561449698</v>
+        <v>-2041.532743280981</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.8212381599189915</v>
+        <v>1.208957239878487</v>
       </c>
       <c r="T99">
-        <v>17.90850253854484</v>
+        <v>26.86275380781726</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.07274110695884924</v>
+        <v>0.0719988507653916</v>
       </c>
       <c r="W99">
-        <v>0.1861935857226631</v>
+        <v>0.1863426307663094</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3306413952674966</v>
+        <v>0.3272675034790526</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.206794922948553</v>
+        <v>0.2083449229485529</v>
       </c>
       <c r="C100">
-        <v>-27486.20381293876</v>
+        <v>-27872.10206051677</v>
       </c>
       <c r="D100">
-        <v>4515.314187061244</v>
+        <v>4472.256939483234</v>
       </c>
       <c r="E100">
-        <v>18227.218</v>
+        <v>18570.059</v>
       </c>
       <c r="F100">
-        <v>33598.41800000001</v>
+        <v>33941.25900000001</v>
       </c>
       <c r="G100">
         <v>1596.9</v>
@@ -9493,37 +9493,37 @@
         <v>2207.930612244898</v>
       </c>
       <c r="M100">
-        <v>6746.562334400001</v>
+        <v>6815.404807200001</v>
       </c>
       <c r="N100">
-        <v>-4538.631722155103</v>
+        <v>-4607.474194955103</v>
       </c>
       <c r="O100">
-        <v>-998.4989788741228</v>
+        <v>-1013.644322890123</v>
       </c>
       <c r="P100">
-        <v>-3540.132743280981</v>
+        <v>-3593.82987206498</v>
       </c>
       <c r="Q100">
-        <v>-2041.532743280981</v>
+        <v>-2095.22987206498</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.208957239878487</v>
+        <v>2.372114479756974</v>
       </c>
       <c r="T100">
-        <v>26.86275380781726</v>
+        <v>53.72550761563452</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.0719988507653916</v>
+        <v>0.07127158964654925</v>
       </c>
       <c r="W100">
-        <v>0.1863426307663094</v>
+        <v>0.1864886647989729</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3272675034790526</v>
+        <v>0.3239617711206785</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2083449229485529</v>
-      </c>
-      <c r="C101">
-        <v>-27872.10206051677</v>
-      </c>
-      <c r="D101">
-        <v>4472.256939483234</v>
-      </c>
-      <c r="E101">
-        <v>18570.059</v>
-      </c>
-      <c r="F101">
-        <v>33941.25900000001</v>
-      </c>
-      <c r="G101">
-        <v>1596.9</v>
-      </c>
-      <c r="H101">
-        <v>18912.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>3706.530612244898</v>
-      </c>
-      <c r="K101">
-        <v>1498.6</v>
-      </c>
-      <c r="L101">
-        <v>2207.930612244898</v>
-      </c>
-      <c r="M101">
-        <v>6815.404807200001</v>
-      </c>
-      <c r="N101">
-        <v>-4607.474194955103</v>
-      </c>
-      <c r="O101">
-        <v>-1013.644322890123</v>
-      </c>
-      <c r="P101">
-        <v>-3593.82987206498</v>
-      </c>
-      <c r="Q101">
-        <v>-2095.22987206498</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.372114479756974</v>
-      </c>
-      <c r="T101">
-        <v>53.72550761563452</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.07127158964654925</v>
-      </c>
-      <c r="W101">
-        <v>0.1864886647989729</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3239617711206785</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
